--- a/output/yearly_population_growth_param_0.5.xlsx
+++ b/output/yearly_population_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6477</v>
+        <v>6154</v>
       </c>
       <c r="C2" t="n">
-        <v>7655</v>
+        <v>6191</v>
       </c>
       <c r="D2" t="n">
-        <v>25430</v>
+        <v>43709</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3289</v>
+        <v>3697</v>
       </c>
       <c r="C3" t="n">
-        <v>7973</v>
+        <v>3513</v>
       </c>
       <c r="D3" t="n">
-        <v>17606</v>
+        <v>18880</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2613</v>
+        <v>2813</v>
       </c>
       <c r="C4" t="n">
-        <v>5331</v>
+        <v>3326</v>
       </c>
       <c r="D4" t="n">
-        <v>9292</v>
+        <v>8728</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C5" t="n">
-        <v>4849</v>
+        <v>2956</v>
       </c>
       <c r="D5" t="n">
-        <v>3713</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>987</v>
+        <v>1005</v>
       </c>
       <c r="C6" t="n">
-        <v>3221</v>
+        <v>1948</v>
       </c>
       <c r="D6" t="n">
-        <v>1441</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="C7" t="n">
-        <v>1707</v>
+        <v>1014</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C8" t="n">
-        <v>797</v>
+        <v>445</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5935</v>
+        <v>6638</v>
       </c>
       <c r="C2" t="n">
-        <v>11398</v>
+        <v>7887</v>
       </c>
       <c r="D2" t="n">
-        <v>22157</v>
+        <v>41736</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3753</v>
+        <v>3930</v>
       </c>
       <c r="C3" t="n">
-        <v>6919</v>
+        <v>4210</v>
       </c>
       <c r="D3" t="n">
-        <v>17452</v>
+        <v>21156</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2478</v>
+        <v>2776</v>
       </c>
       <c r="C4" t="n">
-        <v>6386</v>
+        <v>3351</v>
       </c>
       <c r="D4" t="n">
-        <v>10197</v>
+        <v>10216</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1898</v>
+        <v>1986</v>
       </c>
       <c r="C5" t="n">
-        <v>4919</v>
+        <v>3075</v>
       </c>
       <c r="D5" t="n">
-        <v>4457</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1206</v>
+        <v>1238</v>
       </c>
       <c r="C6" t="n">
-        <v>3909</v>
+        <v>2383</v>
       </c>
       <c r="D6" t="n">
-        <v>1735</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>611</v>
+        <v>645</v>
       </c>
       <c r="C7" t="n">
-        <v>2342</v>
+        <v>1452</v>
       </c>
       <c r="D7" t="n">
-        <v>798</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="C8" t="n">
-        <v>1180</v>
+        <v>696</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
-        <v>527</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7820</v>
+        <v>9567</v>
       </c>
       <c r="C2" t="n">
-        <v>16890</v>
+        <v>8806</v>
       </c>
       <c r="D2" t="n">
-        <v>41330</v>
+        <v>32539</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3771</v>
+        <v>4133</v>
       </c>
       <c r="C3" t="n">
-        <v>7731</v>
+        <v>5130</v>
       </c>
       <c r="D3" t="n">
-        <v>16899</v>
+        <v>22402</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2534</v>
+        <v>2782</v>
       </c>
       <c r="C4" t="n">
-        <v>6417</v>
+        <v>3644</v>
       </c>
       <c r="D4" t="n">
-        <v>10833</v>
+        <v>11487</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1917</v>
+        <v>2060</v>
       </c>
       <c r="C5" t="n">
-        <v>5422</v>
+        <v>3106</v>
       </c>
       <c r="D5" t="n">
-        <v>5148</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1342</v>
+        <v>1417</v>
       </c>
       <c r="C6" t="n">
-        <v>4234</v>
+        <v>2665</v>
       </c>
       <c r="D6" t="n">
-        <v>2061</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>751</v>
+        <v>810</v>
       </c>
       <c r="C7" t="n">
-        <v>2932</v>
+        <v>1838</v>
       </c>
       <c r="D7" t="n">
-        <v>918</v>
+        <v>819</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="C8" t="n">
-        <v>1623</v>
+        <v>1014</v>
       </c>
       <c r="D8" t="n">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C9" t="n">
-        <v>758</v>
+        <v>476</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>354</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7131</v>
+        <v>8474</v>
       </c>
       <c r="C2" t="n">
-        <v>11755</v>
+        <v>5776</v>
       </c>
       <c r="D2" t="n">
-        <v>33875</v>
+        <v>26416</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4504</v>
+        <v>5081</v>
       </c>
       <c r="C3" t="n">
-        <v>11888</v>
+        <v>7557</v>
       </c>
       <c r="D3" t="n">
-        <v>18739</v>
+        <v>24539</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1771</v>
+        <v>1903</v>
       </c>
       <c r="C4" t="n">
-        <v>8654</v>
+        <v>5115</v>
       </c>
       <c r="D4" t="n">
-        <v>10630</v>
+        <v>10771</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1240</v>
+        <v>1309</v>
       </c>
       <c r="C5" t="n">
-        <v>4149</v>
+        <v>2611</v>
       </c>
       <c r="D5" t="n">
-        <v>3403</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>693</v>
+        <v>748</v>
       </c>
       <c r="C6" t="n">
-        <v>2873</v>
+        <v>1801</v>
       </c>
       <c r="D6" t="n">
-        <v>899</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="C7" t="n">
-        <v>1590</v>
+        <v>993</v>
       </c>
       <c r="D7" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C8" t="n">
-        <v>742</v>
+        <v>466</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4324</v>
+        <v>4958</v>
       </c>
       <c r="C2" t="n">
-        <v>5498</v>
+        <v>3095</v>
       </c>
       <c r="D2" t="n">
-        <v>23636</v>
+        <v>18633</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4795</v>
+        <v>5617</v>
       </c>
       <c r="C3" t="n">
-        <v>10750</v>
+        <v>6050</v>
       </c>
       <c r="D3" t="n">
-        <v>19898</v>
+        <v>23592</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2413</v>
+        <v>2742</v>
       </c>
       <c r="C4" t="n">
-        <v>10265</v>
+        <v>6400</v>
       </c>
       <c r="D4" t="n">
-        <v>11576</v>
+        <v>12661</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1370</v>
+        <v>1465</v>
       </c>
       <c r="C5" t="n">
-        <v>5995</v>
+        <v>3763</v>
       </c>
       <c r="D5" t="n">
-        <v>4299</v>
+        <v>4018</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>812</v>
+        <v>904</v>
       </c>
       <c r="C6" t="n">
-        <v>3477</v>
+        <v>2187</v>
       </c>
       <c r="D6" t="n">
-        <v>1130</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>2040</v>
+        <v>1317</v>
       </c>
       <c r="D7" t="n">
-        <v>532</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>992</v>
+        <v>633</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4656</v>
+        <v>5898</v>
       </c>
       <c r="C2" t="n">
-        <v>8287</v>
+        <v>3453</v>
       </c>
       <c r="D2" t="n">
-        <v>22271</v>
+        <v>24455</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3869</v>
+        <v>4512</v>
       </c>
       <c r="C3" t="n">
-        <v>7462</v>
+        <v>4008</v>
       </c>
       <c r="D3" t="n">
-        <v>19069</v>
+        <v>21254</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2929</v>
+        <v>3436</v>
       </c>
       <c r="C4" t="n">
-        <v>10279</v>
+        <v>6146</v>
       </c>
       <c r="D4" t="n">
-        <v>12582</v>
+        <v>14164</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1596</v>
+        <v>1797</v>
       </c>
       <c r="C5" t="n">
-        <v>7796</v>
+        <v>4975</v>
       </c>
       <c r="D5" t="n">
-        <v>5286</v>
+        <v>5306</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>948</v>
+        <v>1065</v>
       </c>
       <c r="C6" t="n">
-        <v>4566</v>
+        <v>2927</v>
       </c>
       <c r="D6" t="n">
-        <v>1571</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>432</v>
+        <v>491</v>
       </c>
       <c r="C7" t="n">
-        <v>2630</v>
+        <v>1721</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C8" t="n">
-        <v>1412</v>
+        <v>927</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>605</v>
+        <v>439</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2810</v>
+        <v>3408</v>
       </c>
       <c r="C2" t="n">
-        <v>4018</v>
+        <v>1541</v>
       </c>
       <c r="D2" t="n">
-        <v>15540</v>
+        <v>16881</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3906</v>
+        <v>4691</v>
       </c>
       <c r="C3" t="n">
-        <v>7523</v>
+        <v>3667</v>
       </c>
       <c r="D3" t="n">
-        <v>18974</v>
+        <v>21102</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3215</v>
+        <v>3841</v>
       </c>
       <c r="C4" t="n">
-        <v>10186</v>
+        <v>5907</v>
       </c>
       <c r="D4" t="n">
-        <v>13414</v>
+        <v>15093</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1658</v>
+        <v>1892</v>
       </c>
       <c r="C5" t="n">
-        <v>9471</v>
+        <v>5896</v>
       </c>
       <c r="D5" t="n">
-        <v>5555</v>
+        <v>5781</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>767</v>
+        <v>906</v>
       </c>
       <c r="C6" t="n">
-        <v>5337</v>
+        <v>3670</v>
       </c>
       <c r="D6" t="n">
-        <v>1519</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>2669</v>
+        <v>1789</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1008</v>
+        <v>730</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3062</v>
+        <v>5038</v>
       </c>
       <c r="C2" t="n">
-        <v>6409</v>
+        <v>7882</v>
       </c>
       <c r="D2" t="n">
-        <v>15003</v>
+        <v>19901</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2973</v>
+        <v>3530</v>
       </c>
       <c r="C3" t="n">
-        <v>5370</v>
+        <v>2366</v>
       </c>
       <c r="D3" t="n">
-        <v>17289</v>
+        <v>19244</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3039</v>
+        <v>3700</v>
       </c>
       <c r="C4" t="n">
-        <v>8870</v>
+        <v>4687</v>
       </c>
       <c r="D4" t="n">
-        <v>13860</v>
+        <v>15614</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2003</v>
+        <v>2382</v>
       </c>
       <c r="C5" t="n">
-        <v>9576</v>
+        <v>5835</v>
       </c>
       <c r="D5" t="n">
-        <v>6571</v>
+        <v>7035</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>991</v>
+        <v>1171</v>
       </c>
       <c r="C6" t="n">
-        <v>7061</v>
+        <v>4689</v>
       </c>
       <c r="D6" t="n">
-        <v>2003</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>355</v>
       </c>
       <c r="C7" t="n">
-        <v>3687</v>
+        <v>2580</v>
       </c>
       <c r="D7" t="n">
-        <v>703</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1597</v>
+        <v>1148</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>503</v>
+        <v>421</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2092</v>
+        <v>3301</v>
       </c>
       <c r="C2" t="n">
-        <v>4027</v>
+        <v>3952</v>
       </c>
       <c r="D2" t="n">
-        <v>10740</v>
+        <v>14069</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2632</v>
+        <v>3536</v>
       </c>
       <c r="C3" t="n">
-        <v>5246</v>
+        <v>4235</v>
       </c>
       <c r="D3" t="n">
-        <v>16120</v>
+        <v>18435</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2780</v>
+        <v>3358</v>
       </c>
       <c r="C4" t="n">
-        <v>7596</v>
+        <v>3699</v>
       </c>
       <c r="D4" t="n">
-        <v>13999</v>
+        <v>15777</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2165</v>
+        <v>2627</v>
       </c>
       <c r="C5" t="n">
-        <v>9507</v>
+        <v>5496</v>
       </c>
       <c r="D5" t="n">
-        <v>7267</v>
+        <v>7876</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1144</v>
+        <v>1410</v>
       </c>
       <c r="C6" t="n">
-        <v>8063</v>
+        <v>5259</v>
       </c>
       <c r="D6" t="n">
-        <v>2369</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>245</v>
+        <v>347</v>
       </c>
       <c r="C7" t="n">
-        <v>4629</v>
+        <v>3313</v>
       </c>
       <c r="D7" t="n">
-        <v>791</v>
+        <v>797</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>2058</v>
+        <v>1513</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>554</v>
+        <v>520</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2831</v>
+        <v>5701</v>
       </c>
       <c r="C2" t="n">
-        <v>13194</v>
+        <v>3790</v>
       </c>
       <c r="D2" t="n">
-        <v>17465</v>
+        <v>15521</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2065</v>
+        <v>2897</v>
       </c>
       <c r="C3" t="n">
-        <v>4274</v>
+        <v>3681</v>
       </c>
       <c r="D3" t="n">
-        <v>14511</v>
+        <v>16666</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2396</v>
+        <v>3004</v>
       </c>
       <c r="C4" t="n">
-        <v>6490</v>
+        <v>3858</v>
       </c>
       <c r="D4" t="n">
-        <v>13858</v>
+        <v>15705</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2154</v>
+        <v>2627</v>
       </c>
       <c r="C5" t="n">
-        <v>8575</v>
+        <v>4622</v>
       </c>
       <c r="D5" t="n">
-        <v>7816</v>
+        <v>8774</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1362</v>
+        <v>1713</v>
       </c>
       <c r="C6" t="n">
-        <v>8525</v>
+        <v>5308</v>
       </c>
       <c r="D6" t="n">
-        <v>2949</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>449</v>
+        <v>624</v>
       </c>
       <c r="C7" t="n">
-        <v>5884</v>
+        <v>4074</v>
       </c>
       <c r="D7" t="n">
-        <v>968</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>2888</v>
+        <v>2197</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1016</v>
+        <v>865</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5905</v>
+        <v>4364</v>
       </c>
       <c r="C2" t="n">
-        <v>6642</v>
+        <v>2072</v>
       </c>
       <c r="D2" t="n">
-        <v>19260</v>
+        <v>8361</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>3986</v>
+      </c>
+      <c r="C2" t="n">
         <v>2092</v>
       </c>
-      <c r="C2" t="n">
-        <v>7811</v>
-      </c>
       <c r="D2" t="n">
-        <v>12993</v>
+        <v>11423</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2757</v>
+        <v>3982</v>
       </c>
       <c r="C3" t="n">
-        <v>6581</v>
+        <v>4014</v>
       </c>
       <c r="D3" t="n">
-        <v>15972</v>
+        <v>17897</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3195</v>
+        <v>3944</v>
       </c>
       <c r="C4" t="n">
-        <v>9377</v>
+        <v>5494</v>
       </c>
       <c r="D4" t="n">
-        <v>14115</v>
+        <v>16193</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1278</v>
+        <v>1704</v>
       </c>
       <c r="C5" t="n">
-        <v>12285</v>
+        <v>7163</v>
       </c>
       <c r="D5" t="n">
-        <v>7101</v>
+        <v>7961</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>414</v>
+        <v>576</v>
       </c>
       <c r="C6" t="n">
-        <v>7186</v>
+        <v>5136</v>
       </c>
       <c r="D6" t="n">
-        <v>2250</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>2830</v>
+        <v>2153</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>995</v>
+        <v>847</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6318</v>
+        <v>6785</v>
       </c>
       <c r="C2" t="n">
-        <v>5707</v>
+        <v>2574</v>
       </c>
       <c r="D2" t="n">
-        <v>33120</v>
+        <v>15563</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2509</v>
+        <v>1855</v>
       </c>
       <c r="C3" t="n">
-        <v>3347</v>
+        <v>1060</v>
       </c>
       <c r="D3" t="n">
-        <v>3875</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4581</v>
+        <v>4700</v>
       </c>
       <c r="C2" t="n">
-        <v>5500</v>
+        <v>4684</v>
       </c>
       <c r="D2" t="n">
-        <v>31077</v>
+        <v>13708</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3625</v>
+        <v>3596</v>
       </c>
       <c r="C3" t="n">
-        <v>4038</v>
+        <v>1663</v>
       </c>
       <c r="D3" t="n">
-        <v>8502</v>
+        <v>4214</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1124</v>
+        <v>839</v>
       </c>
       <c r="C4" t="n">
-        <v>2006</v>
+        <v>674</v>
       </c>
       <c r="D4" t="n">
-        <v>1962</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5070</v>
+        <v>4954</v>
       </c>
       <c r="C2" t="n">
-        <v>9537</v>
+        <v>5534</v>
       </c>
       <c r="D2" t="n">
-        <v>27552</v>
+        <v>27922</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3401</v>
+        <v>3411</v>
       </c>
       <c r="C3" t="n">
-        <v>4180</v>
+        <v>2886</v>
       </c>
       <c r="D3" t="n">
-        <v>11501</v>
+        <v>5429</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1990</v>
+        <v>1903</v>
       </c>
       <c r="C4" t="n">
-        <v>3076</v>
+        <v>1229</v>
       </c>
       <c r="D4" t="n">
-        <v>3158</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>513</v>
+        <v>404</v>
       </c>
       <c r="C5" t="n">
-        <v>1194</v>
+        <v>468</v>
       </c>
       <c r="D5" t="n">
-        <v>1289</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6289</v>
+        <v>5108</v>
       </c>
       <c r="C2" t="n">
-        <v>9431</v>
+        <v>4487</v>
       </c>
       <c r="D2" t="n">
-        <v>24358</v>
+        <v>35073</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3430</v>
+        <v>3413</v>
       </c>
       <c r="C3" t="n">
-        <v>6002</v>
+        <v>3714</v>
       </c>
       <c r="D3" t="n">
-        <v>13131</v>
+        <v>8465</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2265</v>
+        <v>2270</v>
       </c>
       <c r="C4" t="n">
-        <v>3565</v>
+        <v>2098</v>
       </c>
       <c r="D4" t="n">
-        <v>4583</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1033</v>
+        <v>951</v>
       </c>
       <c r="C5" t="n">
-        <v>2144</v>
+        <v>867</v>
       </c>
       <c r="D5" t="n">
-        <v>1560</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>746</v>
+        <v>383</v>
       </c>
       <c r="D6" t="n">
-        <v>961</v>
+        <v>943</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
         <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6175</v>
+        <v>6313</v>
       </c>
       <c r="C2" t="n">
-        <v>8143</v>
+        <v>5534</v>
       </c>
       <c r="D2" t="n">
-        <v>32665</v>
+        <v>42583</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3518</v>
+        <v>3137</v>
       </c>
       <c r="C3" t="n">
-        <v>6329</v>
+        <v>3373</v>
       </c>
       <c r="D3" t="n">
-        <v>13090</v>
+        <v>11485</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1744</v>
+        <v>1763</v>
       </c>
       <c r="C4" t="n">
-        <v>3969</v>
+        <v>2480</v>
       </c>
       <c r="D4" t="n">
-        <v>5237</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>853</v>
+        <v>843</v>
       </c>
       <c r="C5" t="n">
-        <v>2103</v>
+        <v>1121</v>
       </c>
       <c r="D5" t="n">
-        <v>1635</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="C6" t="n">
-        <v>962</v>
+        <v>423</v>
       </c>
       <c r="D6" t="n">
-        <v>809</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>348</v>
+        <v>236</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5983,10 +5983,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -5997,10 +5997,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4500</v>
+        <v>5684</v>
       </c>
       <c r="C2" t="n">
-        <v>5575</v>
+        <v>3680</v>
       </c>
       <c r="D2" t="n">
-        <v>27570</v>
+        <v>36836</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4007</v>
+        <v>3956</v>
       </c>
       <c r="C3" t="n">
-        <v>6347</v>
+        <v>4011</v>
       </c>
       <c r="D3" t="n">
-        <v>15415</v>
+        <v>16094</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2301</v>
+        <v>2164</v>
       </c>
       <c r="C4" t="n">
-        <v>5291</v>
+        <v>2985</v>
       </c>
       <c r="D4" t="n">
-        <v>6660</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1144</v>
+        <v>1162</v>
       </c>
       <c r="C5" t="n">
-        <v>3113</v>
+        <v>1919</v>
       </c>
       <c r="D5" t="n">
-        <v>2261</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C6" t="n">
-        <v>1596</v>
+        <v>826</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>690</v>
+        <v>344</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>289</v>
+        <v>230</v>
       </c>
       <c r="D8" t="n">
         <v>384</v>
@@ -6168,7 +6168,7 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
         <v>284</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4598</v>
+        <v>4960</v>
       </c>
       <c r="C2" t="n">
-        <v>13330</v>
+        <v>4720</v>
       </c>
       <c r="D2" t="n">
-        <v>33440</v>
+        <v>30113</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3503</v>
+        <v>3970</v>
       </c>
       <c r="C3" t="n">
-        <v>5145</v>
+        <v>3297</v>
       </c>
       <c r="D3" t="n">
-        <v>16249</v>
+        <v>18394</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2677</v>
+        <v>2659</v>
       </c>
       <c r="C4" t="n">
-        <v>5768</v>
+        <v>3523</v>
       </c>
       <c r="D4" t="n">
-        <v>8138</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1502</v>
+        <v>1461</v>
       </c>
       <c r="C5" t="n">
-        <v>4219</v>
+        <v>2482</v>
       </c>
       <c r="D5" t="n">
-        <v>2994</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>754</v>
+        <v>781</v>
       </c>
       <c r="C6" t="n">
-        <v>2348</v>
+        <v>1406</v>
       </c>
       <c r="D6" t="n">
-        <v>1158</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C7" t="n">
-        <v>1160</v>
+        <v>608</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>489</v>
+        <v>290</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_growth_param_0.5.xlsx
+++ b/output/yearly_population_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6154</v>
+        <v>6419</v>
       </c>
       <c r="C2" t="n">
-        <v>6191</v>
+        <v>10229</v>
       </c>
       <c r="D2" t="n">
-        <v>43709</v>
+        <v>24612</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3697</v>
+        <v>3597</v>
       </c>
       <c r="C3" t="n">
-        <v>3513</v>
+        <v>7712</v>
       </c>
       <c r="D3" t="n">
-        <v>18880</v>
+        <v>13474</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2813</v>
+        <v>2973</v>
       </c>
       <c r="C4" t="n">
-        <v>3326</v>
+        <v>4813</v>
       </c>
       <c r="D4" t="n">
-        <v>8728</v>
+        <v>6541</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1798</v>
+        <v>1801</v>
       </c>
       <c r="C5" t="n">
-        <v>2956</v>
+        <v>4196</v>
       </c>
       <c r="D5" t="n">
-        <v>2937</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1005</v>
+        <v>968</v>
       </c>
       <c r="C6" t="n">
-        <v>1948</v>
+        <v>3892</v>
       </c>
       <c r="D6" t="n">
-        <v>1136</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>478</v>
+        <v>422</v>
       </c>
       <c r="C7" t="n">
-        <v>1014</v>
+        <v>2812</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>445</v>
+        <v>1396</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>521</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6638</v>
+        <v>6540</v>
       </c>
       <c r="C2" t="n">
-        <v>7887</v>
+        <v>11348</v>
       </c>
       <c r="D2" t="n">
-        <v>41736</v>
+        <v>22809</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3930</v>
+        <v>3892</v>
       </c>
       <c r="C3" t="n">
-        <v>4210</v>
+        <v>7777</v>
       </c>
       <c r="D3" t="n">
-        <v>21156</v>
+        <v>14015</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2776</v>
+        <v>2796</v>
       </c>
       <c r="C4" t="n">
-        <v>3351</v>
+        <v>6048</v>
       </c>
       <c r="D4" t="n">
-        <v>10216</v>
+        <v>7344</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1986</v>
+        <v>2010</v>
       </c>
       <c r="C5" t="n">
-        <v>3075</v>
+        <v>4340</v>
       </c>
       <c r="D5" t="n">
-        <v>3764</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1238</v>
+        <v>1188</v>
       </c>
       <c r="C6" t="n">
-        <v>2383</v>
+        <v>3986</v>
       </c>
       <c r="D6" t="n">
-        <v>1414</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>645</v>
+        <v>575</v>
       </c>
       <c r="C7" t="n">
-        <v>1452</v>
+        <v>3238</v>
       </c>
       <c r="D7" t="n">
-        <v>726</v>
+        <v>704</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="C8" t="n">
-        <v>696</v>
+        <v>1964</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>872</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>341</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
         <v>205</v>
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9567</v>
+        <v>7219</v>
       </c>
       <c r="C2" t="n">
-        <v>8806</v>
+        <v>14042</v>
       </c>
       <c r="D2" t="n">
-        <v>32539</v>
+        <v>24340</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4133</v>
+        <v>4005</v>
       </c>
       <c r="C3" t="n">
-        <v>5130</v>
+        <v>8159</v>
       </c>
       <c r="D3" t="n">
-        <v>22402</v>
+        <v>14173</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2782</v>
+        <v>2742</v>
       </c>
       <c r="C4" t="n">
-        <v>3644</v>
+        <v>6577</v>
       </c>
       <c r="D4" t="n">
-        <v>11487</v>
+        <v>8081</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="C5" t="n">
-        <v>3106</v>
+        <v>4896</v>
       </c>
       <c r="D5" t="n">
-        <v>4640</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1417</v>
+        <v>1366</v>
       </c>
       <c r="C6" t="n">
-        <v>2665</v>
+        <v>4091</v>
       </c>
       <c r="D6" t="n">
-        <v>1719</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>810</v>
+        <v>728</v>
       </c>
       <c r="C7" t="n">
-        <v>1838</v>
+        <v>3490</v>
       </c>
       <c r="D7" t="n">
-        <v>819</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>374</v>
+        <v>315</v>
       </c>
       <c r="C8" t="n">
-        <v>1014</v>
+        <v>2418</v>
       </c>
       <c r="D8" t="n">
-        <v>494</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>476</v>
+        <v>1267</v>
       </c>
       <c r="D9" t="n">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>519</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8474</v>
+        <v>6704</v>
       </c>
       <c r="C2" t="n">
-        <v>5776</v>
+        <v>9773</v>
       </c>
       <c r="D2" t="n">
-        <v>26416</v>
+        <v>20152</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5081</v>
+        <v>4827</v>
       </c>
       <c r="C3" t="n">
-        <v>7557</v>
+        <v>12134</v>
       </c>
       <c r="D3" t="n">
-        <v>24539</v>
+        <v>15408</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="C4" t="n">
-        <v>5115</v>
+        <v>8172</v>
       </c>
       <c r="D4" t="n">
-        <v>10771</v>
+        <v>7726</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1309</v>
+        <v>1262</v>
       </c>
       <c r="C5" t="n">
-        <v>2611</v>
+        <v>4009</v>
       </c>
       <c r="D5" t="n">
-        <v>2976</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>748</v>
+        <v>672</v>
       </c>
       <c r="C6" t="n">
-        <v>1801</v>
+        <v>3420</v>
       </c>
       <c r="D6" t="n">
-        <v>802</v>
+        <v>750</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>993</v>
+        <v>2369</v>
       </c>
       <c r="D7" t="n">
-        <v>484</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>466</v>
+        <v>1241</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>508</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4958</v>
+        <v>3974</v>
       </c>
       <c r="C2" t="n">
-        <v>3095</v>
+        <v>5060</v>
       </c>
       <c r="D2" t="n">
-        <v>18633</v>
+        <v>14426</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5617</v>
+        <v>4847</v>
       </c>
       <c r="C3" t="n">
-        <v>6050</v>
+        <v>10082</v>
       </c>
       <c r="D3" t="n">
-        <v>23592</v>
+        <v>15152</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2742</v>
+        <v>2588</v>
       </c>
       <c r="C4" t="n">
-        <v>6400</v>
+        <v>10103</v>
       </c>
       <c r="D4" t="n">
-        <v>12661</v>
+        <v>8745</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1465</v>
+        <v>1415</v>
       </c>
       <c r="C5" t="n">
-        <v>3763</v>
+        <v>5756</v>
       </c>
       <c r="D5" t="n">
-        <v>4018</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>904</v>
+        <v>795</v>
       </c>
       <c r="C6" t="n">
-        <v>2187</v>
+        <v>3788</v>
       </c>
       <c r="D6" t="n">
-        <v>1024</v>
+        <v>909</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>269</v>
       </c>
       <c r="C7" t="n">
-        <v>1317</v>
+        <v>2844</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>633</v>
+        <v>1584</v>
       </c>
       <c r="D8" t="n">
-        <v>345</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>545</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5898</v>
+        <v>3684</v>
       </c>
       <c r="C2" t="n">
-        <v>3453</v>
+        <v>7673</v>
       </c>
       <c r="D2" t="n">
-        <v>24455</v>
+        <v>17701</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4512</v>
+        <v>3781</v>
       </c>
       <c r="C3" t="n">
-        <v>4008</v>
+        <v>6960</v>
       </c>
       <c r="D3" t="n">
-        <v>21254</v>
+        <v>14035</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3436</v>
+        <v>3040</v>
       </c>
       <c r="C4" t="n">
-        <v>6146</v>
+        <v>9882</v>
       </c>
       <c r="D4" t="n">
-        <v>14164</v>
+        <v>9524</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1797</v>
+        <v>1678</v>
       </c>
       <c r="C5" t="n">
-        <v>4975</v>
+        <v>7597</v>
       </c>
       <c r="D5" t="n">
-        <v>5306</v>
+        <v>3814</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1065</v>
+        <v>951</v>
       </c>
       <c r="C6" t="n">
-        <v>2927</v>
+        <v>4639</v>
       </c>
       <c r="D6" t="n">
-        <v>1470</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>491</v>
+        <v>409</v>
       </c>
       <c r="C7" t="n">
-        <v>1721</v>
+        <v>3231</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>927</v>
+        <v>2092</v>
       </c>
       <c r="D8" t="n">
-        <v>366</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>439</v>
+        <v>932</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>255</v>
+        <v>340</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3408</v>
+        <v>2243</v>
       </c>
       <c r="C2" t="n">
-        <v>1541</v>
+        <v>3699</v>
       </c>
       <c r="D2" t="n">
-        <v>16881</v>
+        <v>12359</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4691</v>
+        <v>3630</v>
       </c>
       <c r="C3" t="n">
-        <v>3667</v>
+        <v>6998</v>
       </c>
       <c r="D3" t="n">
-        <v>21102</v>
+        <v>14101</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3841</v>
+        <v>3317</v>
       </c>
       <c r="C4" t="n">
-        <v>5907</v>
+        <v>9727</v>
       </c>
       <c r="D4" t="n">
-        <v>15093</v>
+        <v>10117</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1892</v>
+        <v>1719</v>
       </c>
       <c r="C5" t="n">
-        <v>5896</v>
+        <v>9216</v>
       </c>
       <c r="D5" t="n">
-        <v>5781</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>906</v>
+        <v>746</v>
       </c>
       <c r="C6" t="n">
-        <v>3670</v>
+        <v>5596</v>
       </c>
       <c r="D6" t="n">
-        <v>1436</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="C7" t="n">
-        <v>1789</v>
+        <v>3524</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>730</v>
+        <v>1528</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>249</v>
+        <v>333</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5038</v>
+        <v>2917</v>
       </c>
       <c r="C2" t="n">
-        <v>7882</v>
+        <v>4040</v>
       </c>
       <c r="D2" t="n">
-        <v>19901</v>
+        <v>16222</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3530</v>
+        <v>2635</v>
       </c>
       <c r="C3" t="n">
-        <v>2366</v>
+        <v>4913</v>
       </c>
       <c r="D3" t="n">
-        <v>19244</v>
+        <v>12952</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3700</v>
+        <v>3040</v>
       </c>
       <c r="C4" t="n">
-        <v>4687</v>
+        <v>8360</v>
       </c>
       <c r="D4" t="n">
-        <v>15614</v>
+        <v>10421</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2382</v>
+        <v>2072</v>
       </c>
       <c r="C5" t="n">
-        <v>5835</v>
+        <v>9333</v>
       </c>
       <c r="D5" t="n">
-        <v>7035</v>
+        <v>4792</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1171</v>
+        <v>986</v>
       </c>
       <c r="C6" t="n">
-        <v>4689</v>
+        <v>7061</v>
       </c>
       <c r="D6" t="n">
-        <v>2056</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>269</v>
       </c>
       <c r="C7" t="n">
-        <v>2580</v>
+        <v>4383</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1148</v>
+        <v>2241</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>421</v>
+        <v>705</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3301</v>
+        <v>1951</v>
       </c>
       <c r="C2" t="n">
-        <v>3952</v>
+        <v>2308</v>
       </c>
       <c r="D2" t="n">
-        <v>14069</v>
+        <v>12408</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3536</v>
+        <v>2387</v>
       </c>
       <c r="C3" t="n">
-        <v>4235</v>
+        <v>4219</v>
       </c>
       <c r="D3" t="n">
-        <v>18435</v>
+        <v>12634</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3358</v>
+        <v>2697</v>
       </c>
       <c r="C4" t="n">
-        <v>3699</v>
+        <v>7022</v>
       </c>
       <c r="D4" t="n">
-        <v>15777</v>
+        <v>10520</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2627</v>
+        <v>2247</v>
       </c>
       <c r="C5" t="n">
-        <v>5496</v>
+        <v>9160</v>
       </c>
       <c r="D5" t="n">
-        <v>7876</v>
+        <v>5332</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1410</v>
+        <v>1144</v>
       </c>
       <c r="C6" t="n">
-        <v>5259</v>
+        <v>8016</v>
       </c>
       <c r="D6" t="n">
-        <v>2569</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>347</v>
+        <v>240</v>
       </c>
       <c r="C7" t="n">
-        <v>3313</v>
+        <v>5285</v>
       </c>
       <c r="D7" t="n">
-        <v>797</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1513</v>
+        <v>2773</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>520</v>
+        <v>766</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5701</v>
+        <v>2629</v>
       </c>
       <c r="C2" t="n">
-        <v>3790</v>
+        <v>3746</v>
       </c>
       <c r="D2" t="n">
-        <v>15521</v>
+        <v>15870</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2897</v>
+        <v>1888</v>
       </c>
       <c r="C3" t="n">
-        <v>3681</v>
+        <v>3143</v>
       </c>
       <c r="D3" t="n">
-        <v>16666</v>
+        <v>11820</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3004</v>
+        <v>2254</v>
       </c>
       <c r="C4" t="n">
-        <v>3858</v>
+        <v>5745</v>
       </c>
       <c r="D4" t="n">
-        <v>15705</v>
+        <v>10383</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2627</v>
+        <v>2188</v>
       </c>
       <c r="C5" t="n">
-        <v>4622</v>
+        <v>8148</v>
       </c>
       <c r="D5" t="n">
-        <v>8774</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1713</v>
+        <v>1394</v>
       </c>
       <c r="C6" t="n">
-        <v>5308</v>
+        <v>8369</v>
       </c>
       <c r="D6" t="n">
-        <v>3248</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>624</v>
+        <v>453</v>
       </c>
       <c r="C7" t="n">
-        <v>4074</v>
+        <v>6246</v>
       </c>
       <c r="D7" t="n">
-        <v>1014</v>
+        <v>815</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>2197</v>
+        <v>3608</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>865</v>
+        <v>1402</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>383</v>
       </c>
       <c r="D10" t="n">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4364</v>
+        <v>5063</v>
       </c>
       <c r="C2" t="n">
-        <v>2072</v>
+        <v>16342</v>
       </c>
       <c r="D2" t="n">
-        <v>8361</v>
+        <v>7975</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3986</v>
+        <v>1922</v>
       </c>
       <c r="C2" t="n">
-        <v>2092</v>
+        <v>2188</v>
       </c>
       <c r="D2" t="n">
-        <v>11423</v>
+        <v>11807</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3982</v>
+        <v>2546</v>
       </c>
       <c r="C3" t="n">
-        <v>4014</v>
+        <v>3610</v>
       </c>
       <c r="D3" t="n">
-        <v>17897</v>
+        <v>13033</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3944</v>
+        <v>3172</v>
       </c>
       <c r="C4" t="n">
-        <v>5494</v>
+        <v>8391</v>
       </c>
       <c r="D4" t="n">
-        <v>16193</v>
+        <v>10578</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1704</v>
+        <v>1308</v>
       </c>
       <c r="C5" t="n">
-        <v>7163</v>
+        <v>11887</v>
       </c>
       <c r="D5" t="n">
-        <v>7961</v>
+        <v>5337</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>576</v>
+        <v>418</v>
       </c>
       <c r="C6" t="n">
-        <v>5136</v>
+        <v>7597</v>
       </c>
       <c r="D6" t="n">
-        <v>2477</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>2153</v>
+        <v>3535</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>847</v>
+        <v>1373</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>375</v>
       </c>
       <c r="D9" t="n">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6785</v>
+        <v>6297</v>
       </c>
       <c r="C2" t="n">
-        <v>2574</v>
+        <v>6294</v>
       </c>
       <c r="D2" t="n">
-        <v>15563</v>
+        <v>16256</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1855</v>
+        <v>2152</v>
       </c>
       <c r="C3" t="n">
-        <v>1060</v>
+        <v>8236</v>
       </c>
       <c r="D3" t="n">
-        <v>2110</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4700</v>
+        <v>4763</v>
       </c>
       <c r="C2" t="n">
-        <v>4684</v>
+        <v>10525</v>
       </c>
       <c r="D2" t="n">
-        <v>13708</v>
+        <v>22650</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3596</v>
+        <v>3467</v>
       </c>
       <c r="C3" t="n">
-        <v>1663</v>
+        <v>6155</v>
       </c>
       <c r="D3" t="n">
-        <v>4214</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>839</v>
+        <v>969</v>
       </c>
       <c r="C4" t="n">
-        <v>674</v>
+        <v>4869</v>
       </c>
       <c r="D4" t="n">
-        <v>1606</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4954</v>
+        <v>5420</v>
       </c>
       <c r="C2" t="n">
-        <v>5534</v>
+        <v>5678</v>
       </c>
       <c r="D2" t="n">
-        <v>27922</v>
+        <v>24552</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3411</v>
+        <v>3365</v>
       </c>
       <c r="C3" t="n">
-        <v>2886</v>
+        <v>7365</v>
       </c>
       <c r="D3" t="n">
-        <v>5429</v>
+        <v>6873</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1903</v>
+        <v>1855</v>
       </c>
       <c r="C4" t="n">
-        <v>1229</v>
+        <v>5483</v>
       </c>
       <c r="D4" t="n">
-        <v>2042</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>404</v>
+        <v>451</v>
       </c>
       <c r="C5" t="n">
-        <v>468</v>
+        <v>2716</v>
       </c>
       <c r="D5" t="n">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>350</v>
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5108</v>
+        <v>6339</v>
       </c>
       <c r="C2" t="n">
-        <v>4487</v>
+        <v>5648</v>
       </c>
       <c r="D2" t="n">
-        <v>35073</v>
+        <v>20969</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3413</v>
+        <v>3571</v>
       </c>
       <c r="C3" t="n">
-        <v>3714</v>
+        <v>5680</v>
       </c>
       <c r="D3" t="n">
-        <v>8465</v>
+        <v>9076</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2270</v>
+        <v>2175</v>
       </c>
       <c r="C4" t="n">
-        <v>2098</v>
+        <v>6362</v>
       </c>
       <c r="D4" t="n">
-        <v>2578</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>951</v>
+        <v>932</v>
       </c>
       <c r="C5" t="n">
-        <v>867</v>
+        <v>4067</v>
       </c>
       <c r="D5" t="n">
-        <v>1340</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="C6" t="n">
-        <v>383</v>
+        <v>1479</v>
       </c>
       <c r="D6" t="n">
-        <v>943</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>174</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6313</v>
+        <v>6999</v>
       </c>
       <c r="C2" t="n">
-        <v>5534</v>
+        <v>4745</v>
       </c>
       <c r="D2" t="n">
-        <v>42583</v>
+        <v>25434</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3137</v>
+        <v>3541</v>
       </c>
       <c r="C3" t="n">
-        <v>3373</v>
+        <v>4647</v>
       </c>
       <c r="D3" t="n">
-        <v>11485</v>
+        <v>9553</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1763</v>
+        <v>1769</v>
       </c>
       <c r="C4" t="n">
-        <v>2480</v>
+        <v>4853</v>
       </c>
       <c r="D4" t="n">
-        <v>3097</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>843</v>
+        <v>793</v>
       </c>
       <c r="C5" t="n">
-        <v>1121</v>
+        <v>3816</v>
       </c>
       <c r="D5" t="n">
-        <v>1236</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>423</v>
+        <v>1830</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>236</v>
+        <v>569</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5684</v>
+        <v>5988</v>
       </c>
       <c r="C2" t="n">
-        <v>3680</v>
+        <v>8773</v>
       </c>
       <c r="D2" t="n">
-        <v>36836</v>
+        <v>20699</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3956</v>
+        <v>4333</v>
       </c>
       <c r="C3" t="n">
-        <v>4011</v>
+        <v>4048</v>
       </c>
       <c r="D3" t="n">
-        <v>16094</v>
+        <v>11517</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2164</v>
+        <v>2292</v>
       </c>
       <c r="C4" t="n">
-        <v>2985</v>
+        <v>4629</v>
       </c>
       <c r="D4" t="n">
-        <v>4774</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1162</v>
+        <v>1134</v>
       </c>
       <c r="C5" t="n">
-        <v>1919</v>
+        <v>4333</v>
       </c>
       <c r="D5" t="n">
-        <v>1561</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>533</v>
+        <v>486</v>
       </c>
       <c r="C6" t="n">
-        <v>826</v>
+        <v>2913</v>
       </c>
       <c r="D6" t="n">
-        <v>846</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>344</v>
+        <v>1260</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>230</v>
+        <v>405</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
         <v>197</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4960</v>
+        <v>4452</v>
       </c>
       <c r="C2" t="n">
-        <v>4720</v>
+        <v>12257</v>
       </c>
       <c r="D2" t="n">
-        <v>30113</v>
+        <v>27424</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3970</v>
+        <v>4256</v>
       </c>
       <c r="C3" t="n">
-        <v>3297</v>
+        <v>5671</v>
       </c>
       <c r="D3" t="n">
-        <v>18394</v>
+        <v>12101</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2659</v>
+        <v>2789</v>
       </c>
       <c r="C4" t="n">
-        <v>3523</v>
+        <v>4214</v>
       </c>
       <c r="D4" t="n">
-        <v>6910</v>
+        <v>5585</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1461</v>
+        <v>1474</v>
       </c>
       <c r="C5" t="n">
-        <v>2482</v>
+        <v>4357</v>
       </c>
       <c r="D5" t="n">
-        <v>2130</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>781</v>
+        <v>727</v>
       </c>
       <c r="C6" t="n">
-        <v>1406</v>
+        <v>3616</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>608</v>
+        <v>2101</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>290</v>
+        <v>819</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>220</v>
+        <v>301</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_growth_param_0.5.xlsx
+++ b/output/yearly_population_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6419</v>
+        <v>1026</v>
       </c>
       <c r="C2" t="n">
-        <v>10229</v>
+        <v>2991</v>
       </c>
       <c r="D2" t="n">
-        <v>24612</v>
+        <v>16993</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3597</v>
+        <v>1957</v>
       </c>
       <c r="C3" t="n">
-        <v>7712</v>
+        <v>5780</v>
       </c>
       <c r="D3" t="n">
-        <v>13474</v>
+        <v>16010</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2973</v>
+        <v>1326</v>
       </c>
       <c r="C4" t="n">
-        <v>4813</v>
+        <v>7013</v>
       </c>
       <c r="D4" t="n">
-        <v>6541</v>
+        <v>6818</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1801</v>
+        <v>618</v>
       </c>
       <c r="C5" t="n">
-        <v>4196</v>
+        <v>3917</v>
       </c>
       <c r="D5" t="n">
-        <v>2569</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>968</v>
+        <v>264</v>
       </c>
       <c r="C6" t="n">
-        <v>3892</v>
+        <v>1491</v>
       </c>
       <c r="D6" t="n">
-        <v>1120</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>422</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>2812</v>
+        <v>576</v>
       </c>
       <c r="D7" t="n">
-        <v>641</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1396</v>
+        <v>341</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>521</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6540</v>
+        <v>1783</v>
       </c>
       <c r="C2" t="n">
-        <v>11348</v>
+        <v>5107</v>
       </c>
       <c r="D2" t="n">
-        <v>22809</v>
+        <v>23979</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3892</v>
+        <v>1277</v>
       </c>
       <c r="C3" t="n">
-        <v>7777</v>
+        <v>3718</v>
       </c>
       <c r="D3" t="n">
-        <v>14015</v>
+        <v>15168</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2796</v>
+        <v>1416</v>
       </c>
       <c r="C4" t="n">
-        <v>6048</v>
+        <v>6247</v>
       </c>
       <c r="D4" t="n">
-        <v>7344</v>
+        <v>8287</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2010</v>
+        <v>833</v>
       </c>
       <c r="C5" t="n">
-        <v>4340</v>
+        <v>5470</v>
       </c>
       <c r="D5" t="n">
-        <v>3101</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1188</v>
+        <v>387</v>
       </c>
       <c r="C6" t="n">
-        <v>3986</v>
+        <v>2723</v>
       </c>
       <c r="D6" t="n">
-        <v>1302</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>575</v>
+        <v>152</v>
       </c>
       <c r="C7" t="n">
-        <v>3238</v>
+        <v>1029</v>
       </c>
       <c r="D7" t="n">
-        <v>704</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1964</v>
+        <v>455</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>872</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>341</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7219</v>
+        <v>932</v>
       </c>
       <c r="C2" t="n">
-        <v>14042</v>
+        <v>2067</v>
       </c>
       <c r="D2" t="n">
-        <v>24340</v>
+        <v>16214</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4005</v>
+        <v>1369</v>
       </c>
       <c r="C3" t="n">
-        <v>8159</v>
+        <v>4112</v>
       </c>
       <c r="D3" t="n">
-        <v>14173</v>
+        <v>15883</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2742</v>
+        <v>1539</v>
       </c>
       <c r="C4" t="n">
-        <v>6577</v>
+        <v>5757</v>
       </c>
       <c r="D4" t="n">
-        <v>8081</v>
+        <v>9225</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2059</v>
+        <v>836</v>
       </c>
       <c r="C5" t="n">
-        <v>4896</v>
+        <v>6360</v>
       </c>
       <c r="D5" t="n">
-        <v>3547</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1366</v>
+        <v>314</v>
       </c>
       <c r="C6" t="n">
-        <v>4091</v>
+        <v>3560</v>
       </c>
       <c r="D6" t="n">
-        <v>1526</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>728</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>3490</v>
+        <v>1027</v>
       </c>
       <c r="D7" t="n">
-        <v>766</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>315</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>2418</v>
+        <v>471</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>1267</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>519</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>237</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6704</v>
+        <v>694</v>
       </c>
       <c r="C2" t="n">
-        <v>9773</v>
+        <v>4877</v>
       </c>
       <c r="D2" t="n">
-        <v>20152</v>
+        <v>16342</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4827</v>
+        <v>991</v>
       </c>
       <c r="C3" t="n">
-        <v>12134</v>
+        <v>2679</v>
       </c>
       <c r="D3" t="n">
-        <v>15408</v>
+        <v>14815</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1902</v>
+        <v>1298</v>
       </c>
       <c r="C4" t="n">
-        <v>8172</v>
+        <v>4808</v>
       </c>
       <c r="D4" t="n">
-        <v>7726</v>
+        <v>10247</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1262</v>
+        <v>1024</v>
       </c>
       <c r="C5" t="n">
-        <v>4009</v>
+        <v>5981</v>
       </c>
       <c r="D5" t="n">
-        <v>2448</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>672</v>
+        <v>483</v>
       </c>
       <c r="C6" t="n">
-        <v>3420</v>
+        <v>4936</v>
       </c>
       <c r="D6" t="n">
-        <v>750</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>2369</v>
+        <v>2188</v>
       </c>
       <c r="D7" t="n">
-        <v>464</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1241</v>
+        <v>708</v>
       </c>
       <c r="D8" t="n">
-        <v>317</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>508</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>67</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3974</v>
+        <v>372</v>
       </c>
       <c r="C2" t="n">
-        <v>5060</v>
+        <v>3132</v>
       </c>
       <c r="D2" t="n">
-        <v>14426</v>
+        <v>11414</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4847</v>
+        <v>768</v>
       </c>
       <c r="C3" t="n">
-        <v>10082</v>
+        <v>3340</v>
       </c>
       <c r="D3" t="n">
-        <v>15152</v>
+        <v>14169</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2588</v>
+        <v>1100</v>
       </c>
       <c r="C4" t="n">
-        <v>10103</v>
+        <v>3844</v>
       </c>
       <c r="D4" t="n">
-        <v>8745</v>
+        <v>10735</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1415</v>
+        <v>1085</v>
       </c>
       <c r="C5" t="n">
-        <v>5756</v>
+        <v>5590</v>
       </c>
       <c r="D5" t="n">
-        <v>3028</v>
+        <v>4963</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>795</v>
+        <v>593</v>
       </c>
       <c r="C6" t="n">
-        <v>3788</v>
+        <v>5519</v>
       </c>
       <c r="D6" t="n">
-        <v>909</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>269</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>2844</v>
+        <v>3172</v>
       </c>
       <c r="D7" t="n">
-        <v>503</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1584</v>
+        <v>1096</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>545</v>
+        <v>433</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3684</v>
+        <v>1251</v>
       </c>
       <c r="C2" t="n">
-        <v>7673</v>
+        <v>6042</v>
       </c>
       <c r="D2" t="n">
-        <v>17701</v>
+        <v>15785</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3781</v>
+        <v>507</v>
       </c>
       <c r="C3" t="n">
-        <v>6960</v>
+        <v>2874</v>
       </c>
       <c r="D3" t="n">
-        <v>14035</v>
+        <v>12933</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3040</v>
+        <v>846</v>
       </c>
       <c r="C4" t="n">
-        <v>9882</v>
+        <v>3517</v>
       </c>
       <c r="D4" t="n">
-        <v>9524</v>
+        <v>10969</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1678</v>
+        <v>1007</v>
       </c>
       <c r="C5" t="n">
-        <v>7597</v>
+        <v>4652</v>
       </c>
       <c r="D5" t="n">
-        <v>3814</v>
+        <v>5651</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>951</v>
+        <v>728</v>
       </c>
       <c r="C6" t="n">
-        <v>4639</v>
+        <v>5551</v>
       </c>
       <c r="D6" t="n">
-        <v>1202</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>287</v>
       </c>
       <c r="C7" t="n">
-        <v>3231</v>
+        <v>4182</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>834</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>2092</v>
+        <v>1960</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>505</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>932</v>
+        <v>690</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2243</v>
+        <v>830</v>
       </c>
       <c r="C2" t="n">
-        <v>3699</v>
+        <v>3093</v>
       </c>
       <c r="D2" t="n">
-        <v>12359</v>
+        <v>11366</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3630</v>
+        <v>832</v>
       </c>
       <c r="C3" t="n">
-        <v>6998</v>
+        <v>4002</v>
       </c>
       <c r="D3" t="n">
-        <v>14101</v>
+        <v>14080</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3317</v>
+        <v>1346</v>
       </c>
       <c r="C4" t="n">
-        <v>9727</v>
+        <v>5034</v>
       </c>
       <c r="D4" t="n">
-        <v>10117</v>
+        <v>11321</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1719</v>
+        <v>747</v>
       </c>
       <c r="C5" t="n">
-        <v>9216</v>
+        <v>7330</v>
       </c>
       <c r="D5" t="n">
-        <v>4040</v>
+        <v>5232</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>746</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>5596</v>
+        <v>5512</v>
       </c>
       <c r="D6" t="n">
-        <v>1172</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>3524</v>
+        <v>1920</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1528</v>
+        <v>676</v>
       </c>
       <c r="D8" t="n">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>333</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>161</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2917</v>
+        <v>411</v>
       </c>
       <c r="C2" t="n">
-        <v>4040</v>
+        <v>1764</v>
       </c>
       <c r="D2" t="n">
-        <v>16222</v>
+        <v>8504</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2635</v>
+        <v>697</v>
       </c>
       <c r="C3" t="n">
-        <v>4913</v>
+        <v>3119</v>
       </c>
       <c r="D3" t="n">
-        <v>12952</v>
+        <v>12679</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3040</v>
+        <v>929</v>
       </c>
       <c r="C4" t="n">
-        <v>8360</v>
+        <v>4269</v>
       </c>
       <c r="D4" t="n">
-        <v>10421</v>
+        <v>10980</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2072</v>
+        <v>711</v>
       </c>
       <c r="C5" t="n">
-        <v>9333</v>
+        <v>5535</v>
       </c>
       <c r="D5" t="n">
-        <v>4792</v>
+        <v>5459</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>986</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>7061</v>
+        <v>5189</v>
       </c>
       <c r="D6" t="n">
-        <v>1553</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>269</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>4383</v>
+        <v>2535</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>2241</v>
+        <v>758</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>705</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>131</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1951</v>
+        <v>743</v>
       </c>
       <c r="C2" t="n">
-        <v>2308</v>
+        <v>7754</v>
       </c>
       <c r="D2" t="n">
-        <v>12408</v>
+        <v>18097</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2387</v>
+        <v>469</v>
       </c>
       <c r="C3" t="n">
-        <v>4219</v>
+        <v>2060</v>
       </c>
       <c r="D3" t="n">
-        <v>12634</v>
+        <v>11098</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2697</v>
+        <v>712</v>
       </c>
       <c r="C4" t="n">
-        <v>7022</v>
+        <v>3528</v>
       </c>
       <c r="D4" t="n">
-        <v>10520</v>
+        <v>10972</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2247</v>
+        <v>738</v>
       </c>
       <c r="C5" t="n">
-        <v>9160</v>
+        <v>4780</v>
       </c>
       <c r="D5" t="n">
-        <v>5332</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1144</v>
+        <v>429</v>
       </c>
       <c r="C6" t="n">
-        <v>8016</v>
+        <v>5310</v>
       </c>
       <c r="D6" t="n">
-        <v>1813</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>5285</v>
+        <v>3911</v>
       </c>
       <c r="D7" t="n">
-        <v>690</v>
+        <v>829</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>2773</v>
+        <v>1618</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>766</v>
+        <v>494</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2629</v>
+        <v>894</v>
       </c>
       <c r="C2" t="n">
-        <v>3746</v>
+        <v>4771</v>
       </c>
       <c r="D2" t="n">
-        <v>15870</v>
+        <v>18123</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1888</v>
+        <v>487</v>
       </c>
       <c r="C3" t="n">
-        <v>3143</v>
+        <v>4259</v>
       </c>
       <c r="D3" t="n">
-        <v>11820</v>
+        <v>11342</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2254</v>
+        <v>525</v>
       </c>
       <c r="C4" t="n">
-        <v>5745</v>
+        <v>2693</v>
       </c>
       <c r="D4" t="n">
-        <v>10383</v>
+        <v>10554</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2188</v>
+        <v>656</v>
       </c>
       <c r="C5" t="n">
-        <v>8148</v>
+        <v>4009</v>
       </c>
       <c r="D5" t="n">
-        <v>5867</v>
+        <v>6915</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1394</v>
+        <v>524</v>
       </c>
       <c r="C6" t="n">
-        <v>8369</v>
+        <v>4994</v>
       </c>
       <c r="D6" t="n">
-        <v>2228</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>453</v>
+        <v>235</v>
       </c>
       <c r="C7" t="n">
-        <v>6246</v>
+        <v>4581</v>
       </c>
       <c r="D7" t="n">
-        <v>815</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>3608</v>
+        <v>2673</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>1402</v>
+        <v>989</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>383</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5063</v>
+        <v>3396</v>
       </c>
       <c r="C2" t="n">
-        <v>16342</v>
+        <v>6149</v>
       </c>
       <c r="D2" t="n">
-        <v>7975</v>
+        <v>11991</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1922</v>
+        <v>759</v>
       </c>
       <c r="C2" t="n">
-        <v>2188</v>
+        <v>7905</v>
       </c>
       <c r="D2" t="n">
-        <v>11807</v>
+        <v>15641</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2546</v>
+        <v>538</v>
       </c>
       <c r="C3" t="n">
-        <v>3610</v>
+        <v>3952</v>
       </c>
       <c r="D3" t="n">
-        <v>13033</v>
+        <v>11502</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3172</v>
+        <v>438</v>
       </c>
       <c r="C4" t="n">
-        <v>8391</v>
+        <v>3388</v>
       </c>
       <c r="D4" t="n">
-        <v>10578</v>
+        <v>10361</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1308</v>
+        <v>554</v>
       </c>
       <c r="C5" t="n">
-        <v>11887</v>
+        <v>3319</v>
       </c>
       <c r="D5" t="n">
-        <v>5337</v>
+        <v>7197</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>418</v>
+        <v>535</v>
       </c>
       <c r="C6" t="n">
-        <v>7597</v>
+        <v>4462</v>
       </c>
       <c r="D6" t="n">
-        <v>1764</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="C7" t="n">
-        <v>3535</v>
+        <v>4761</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>1373</v>
+        <v>3475</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>375</v>
+        <v>1655</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>581</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6297</v>
+        <v>4692</v>
       </c>
       <c r="C2" t="n">
-        <v>6294</v>
+        <v>7345</v>
       </c>
       <c r="D2" t="n">
-        <v>16256</v>
+        <v>23365</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2152</v>
+        <v>1123</v>
       </c>
       <c r="C3" t="n">
-        <v>8236</v>
+        <v>2428</v>
       </c>
       <c r="D3" t="n">
-        <v>1979</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4763</v>
+        <v>2200</v>
       </c>
       <c r="C2" t="n">
-        <v>10525</v>
+        <v>5820</v>
       </c>
       <c r="D2" t="n">
-        <v>22650</v>
+        <v>22998</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3467</v>
+        <v>2467</v>
       </c>
       <c r="C3" t="n">
-        <v>6155</v>
+        <v>4635</v>
       </c>
       <c r="D3" t="n">
-        <v>4231</v>
+        <v>5797</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>969</v>
+        <v>546</v>
       </c>
       <c r="C4" t="n">
-        <v>4869</v>
+        <v>1562</v>
       </c>
       <c r="D4" t="n">
-        <v>1580</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5420</v>
+        <v>2989</v>
       </c>
       <c r="C2" t="n">
-        <v>5678</v>
+        <v>4806</v>
       </c>
       <c r="D2" t="n">
-        <v>24552</v>
+        <v>26010</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3365</v>
+        <v>1924</v>
       </c>
       <c r="C3" t="n">
-        <v>7365</v>
+        <v>4579</v>
       </c>
       <c r="D3" t="n">
-        <v>6873</v>
+        <v>8260</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1855</v>
+        <v>1325</v>
       </c>
       <c r="C4" t="n">
-        <v>5483</v>
+        <v>3388</v>
       </c>
       <c r="D4" t="n">
-        <v>2040</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>451</v>
+        <v>279</v>
       </c>
       <c r="C5" t="n">
-        <v>2716</v>
+        <v>995</v>
       </c>
       <c r="D5" t="n">
-        <v>1231</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>335</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6339</v>
+        <v>2289</v>
       </c>
       <c r="C2" t="n">
-        <v>5648</v>
+        <v>4775</v>
       </c>
       <c r="D2" t="n">
-        <v>20969</v>
+        <v>27398</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3571</v>
+        <v>2015</v>
       </c>
       <c r="C3" t="n">
-        <v>5680</v>
+        <v>4065</v>
       </c>
       <c r="D3" t="n">
-        <v>9076</v>
+        <v>10505</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2175</v>
+        <v>1406</v>
       </c>
       <c r="C4" t="n">
-        <v>6362</v>
+        <v>4003</v>
       </c>
       <c r="D4" t="n">
-        <v>2859</v>
+        <v>3409</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>932</v>
+        <v>681</v>
       </c>
       <c r="C5" t="n">
-        <v>4067</v>
+        <v>2306</v>
       </c>
       <c r="D5" t="n">
-        <v>1333</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>259</v>
+        <v>174</v>
       </c>
       <c r="C6" t="n">
-        <v>1479</v>
+        <v>651</v>
       </c>
       <c r="D6" t="n">
-        <v>930</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>311</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6999</v>
+        <v>2096</v>
       </c>
       <c r="C2" t="n">
-        <v>4745</v>
+        <v>8517</v>
       </c>
       <c r="D2" t="n">
-        <v>25434</v>
+        <v>28054</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3541</v>
+        <v>1770</v>
       </c>
       <c r="C3" t="n">
-        <v>4647</v>
+        <v>3855</v>
       </c>
       <c r="D3" t="n">
-        <v>9553</v>
+        <v>12333</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1769</v>
+        <v>1453</v>
       </c>
       <c r="C4" t="n">
-        <v>4853</v>
+        <v>3953</v>
       </c>
       <c r="D4" t="n">
-        <v>3328</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>793</v>
+        <v>903</v>
       </c>
       <c r="C5" t="n">
-        <v>3816</v>
+        <v>3154</v>
       </c>
       <c r="D5" t="n">
-        <v>1260</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>276</v>
+        <v>368</v>
       </c>
       <c r="C6" t="n">
-        <v>1830</v>
+        <v>1485</v>
       </c>
       <c r="D6" t="n">
-        <v>749</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="C7" t="n">
-        <v>569</v>
+        <v>472</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5988</v>
+        <v>2371</v>
       </c>
       <c r="C2" t="n">
-        <v>8773</v>
+        <v>8148</v>
       </c>
       <c r="D2" t="n">
-        <v>20699</v>
+        <v>32066</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4333</v>
+        <v>1583</v>
       </c>
       <c r="C3" t="n">
-        <v>4048</v>
+        <v>5381</v>
       </c>
       <c r="D3" t="n">
-        <v>11517</v>
+        <v>13748</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2292</v>
+        <v>1384</v>
       </c>
       <c r="C4" t="n">
-        <v>4629</v>
+        <v>3819</v>
       </c>
       <c r="D4" t="n">
-        <v>4481</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1134</v>
+        <v>1016</v>
       </c>
       <c r="C5" t="n">
-        <v>4333</v>
+        <v>3487</v>
       </c>
       <c r="D5" t="n">
-        <v>1606</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>486</v>
+        <v>554</v>
       </c>
       <c r="C6" t="n">
-        <v>2913</v>
+        <v>2270</v>
       </c>
       <c r="D6" t="n">
-        <v>836</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="C7" t="n">
-        <v>1260</v>
+        <v>943</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>405</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>206</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4452</v>
+        <v>2139</v>
       </c>
       <c r="C2" t="n">
-        <v>12257</v>
+        <v>4953</v>
       </c>
       <c r="D2" t="n">
-        <v>27424</v>
+        <v>25147</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4256</v>
+        <v>2285</v>
       </c>
       <c r="C3" t="n">
-        <v>5671</v>
+        <v>7976</v>
       </c>
       <c r="D3" t="n">
-        <v>12101</v>
+        <v>15297</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2789</v>
+        <v>938</v>
       </c>
       <c r="C4" t="n">
-        <v>4214</v>
+        <v>5767</v>
       </c>
       <c r="D4" t="n">
-        <v>5585</v>
+        <v>5297</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1474</v>
+        <v>511</v>
       </c>
       <c r="C5" t="n">
-        <v>4357</v>
+        <v>2224</v>
       </c>
       <c r="D5" t="n">
-        <v>2081</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>727</v>
+        <v>191</v>
       </c>
       <c r="C6" t="n">
-        <v>3616</v>
+        <v>924</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>2101</v>
+        <v>370</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>819</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_growth_param_0.5.xlsx
+++ b/output/yearly_population_growth_param_0.5.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="year_0" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="year_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="year_2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="year_3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="year_4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="year_5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="year_6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="year_7" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="year_8" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="year_9" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="year_10" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="year_11" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="year_12" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="year_13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="year_14" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="year_15" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="year_16" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="year_17" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="year_18" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="year_19" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_8" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_9" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_10" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_11" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_12" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_13" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_14" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_15" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_16" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_17" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_18" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_19" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1026</v>
+        <v>593</v>
       </c>
       <c r="C2" t="n">
-        <v>2991</v>
+        <v>2797</v>
       </c>
       <c r="D2" t="n">
-        <v>16993</v>
+        <v>14511</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1957</v>
+        <v>1258</v>
       </c>
       <c r="C3" t="n">
-        <v>5780</v>
+        <v>5335</v>
       </c>
       <c r="D3" t="n">
-        <v>16010</v>
+        <v>14531</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1326</v>
+        <v>916</v>
       </c>
       <c r="C4" t="n">
-        <v>7013</v>
+        <v>5873</v>
       </c>
       <c r="D4" t="n">
-        <v>6818</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>618</v>
+        <v>409</v>
       </c>
       <c r="C5" t="n">
-        <v>3917</v>
+        <v>3251</v>
       </c>
       <c r="D5" t="n">
-        <v>2151</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>1491</v>
+        <v>990</v>
       </c>
       <c r="D6" t="n">
-        <v>749</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>576</v>
+        <v>429</v>
       </c>
       <c r="D7" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D8" t="n">
         <v>371</v>
@@ -881,10 +881,10 @@
         <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1783</v>
+        <v>791</v>
       </c>
       <c r="C2" t="n">
-        <v>5107</v>
+        <v>3725</v>
       </c>
       <c r="D2" t="n">
-        <v>23979</v>
+        <v>14993</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1277</v>
+        <v>777</v>
       </c>
       <c r="C3" t="n">
-        <v>3718</v>
+        <v>3362</v>
       </c>
       <c r="D3" t="n">
-        <v>15168</v>
+        <v>13597</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1416</v>
+        <v>957</v>
       </c>
       <c r="C4" t="n">
-        <v>6247</v>
+        <v>5492</v>
       </c>
       <c r="D4" t="n">
-        <v>8287</v>
+        <v>7476</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>833</v>
+        <v>578</v>
       </c>
       <c r="C5" t="n">
-        <v>5470</v>
+        <v>4705</v>
       </c>
       <c r="D5" t="n">
-        <v>2892</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>387</v>
+        <v>264</v>
       </c>
       <c r="C6" t="n">
-        <v>2723</v>
+        <v>2170</v>
       </c>
       <c r="D6" t="n">
-        <v>967</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>1029</v>
+        <v>707</v>
       </c>
       <c r="D7" t="n">
-        <v>528</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>455</v>
+        <v>390</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
         <v>274</v>
@@ -1220,10 +1220,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>932</v>
+        <v>392</v>
       </c>
       <c r="C2" t="n">
-        <v>2067</v>
+        <v>1435</v>
       </c>
       <c r="D2" t="n">
-        <v>16214</v>
+        <v>9998</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1369</v>
+        <v>750</v>
       </c>
       <c r="C3" t="n">
-        <v>4112</v>
+        <v>3354</v>
       </c>
       <c r="D3" t="n">
-        <v>15883</v>
+        <v>13395</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1539</v>
+        <v>1037</v>
       </c>
       <c r="C4" t="n">
-        <v>5757</v>
+        <v>5037</v>
       </c>
       <c r="D4" t="n">
-        <v>9225</v>
+        <v>8371</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>836</v>
+        <v>586</v>
       </c>
       <c r="C5" t="n">
-        <v>6360</v>
+        <v>5571</v>
       </c>
       <c r="D5" t="n">
-        <v>3338</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>314</v>
+        <v>236</v>
       </c>
       <c r="C6" t="n">
-        <v>3560</v>
+        <v>2939</v>
       </c>
       <c r="D6" t="n">
-        <v>981</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>1027</v>
+        <v>753</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>694</v>
+        <v>558</v>
       </c>
       <c r="C2" t="n">
-        <v>4877</v>
+        <v>2897</v>
       </c>
       <c r="D2" t="n">
-        <v>16342</v>
+        <v>8306</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>991</v>
+        <v>492</v>
       </c>
       <c r="C3" t="n">
-        <v>2679</v>
+        <v>2008</v>
       </c>
       <c r="D3" t="n">
-        <v>14815</v>
+        <v>11887</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1298</v>
+        <v>803</v>
       </c>
       <c r="C4" t="n">
-        <v>4808</v>
+        <v>4027</v>
       </c>
       <c r="D4" t="n">
-        <v>10247</v>
+        <v>9161</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1024</v>
+        <v>715</v>
       </c>
       <c r="C5" t="n">
-        <v>5981</v>
+        <v>5275</v>
       </c>
       <c r="D5" t="n">
-        <v>4197</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>483</v>
+        <v>351</v>
       </c>
       <c r="C6" t="n">
-        <v>4936</v>
+        <v>4307</v>
       </c>
       <c r="D6" t="n">
-        <v>1329</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>2188</v>
+        <v>1774</v>
       </c>
       <c r="D7" t="n">
-        <v>618</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>708</v>
+        <v>598</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
         <v>227</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D16" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="C2" t="n">
-        <v>3132</v>
+        <v>1504</v>
       </c>
       <c r="D2" t="n">
-        <v>11414</v>
+        <v>6586</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>768</v>
+        <v>452</v>
       </c>
       <c r="C3" t="n">
-        <v>3340</v>
+        <v>2203</v>
       </c>
       <c r="D3" t="n">
-        <v>14169</v>
+        <v>10734</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1100</v>
+        <v>635</v>
       </c>
       <c r="C4" t="n">
-        <v>3844</v>
+        <v>3070</v>
       </c>
       <c r="D4" t="n">
-        <v>10735</v>
+        <v>9415</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1085</v>
+        <v>740</v>
       </c>
       <c r="C5" t="n">
-        <v>5590</v>
+        <v>4804</v>
       </c>
       <c r="D5" t="n">
-        <v>4963</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>593</v>
+        <v>436</v>
       </c>
       <c r="C6" t="n">
-        <v>5519</v>
+        <v>4946</v>
       </c>
       <c r="D6" t="n">
-        <v>1641</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>3172</v>
+        <v>2689</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1096</v>
+        <v>927</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="D9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1251</v>
+        <v>257</v>
       </c>
       <c r="C2" t="n">
-        <v>6042</v>
+        <v>5441</v>
       </c>
       <c r="D2" t="n">
-        <v>15785</v>
+        <v>7243</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>507</v>
+        <v>344</v>
       </c>
       <c r="C3" t="n">
-        <v>2874</v>
+        <v>1625</v>
       </c>
       <c r="D3" t="n">
-        <v>12933</v>
+        <v>9347</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>846</v>
+        <v>487</v>
       </c>
       <c r="C4" t="n">
-        <v>3517</v>
+        <v>2577</v>
       </c>
       <c r="D4" t="n">
-        <v>10969</v>
+        <v>9369</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1007</v>
+        <v>644</v>
       </c>
       <c r="C5" t="n">
-        <v>4652</v>
+        <v>3884</v>
       </c>
       <c r="D5" t="n">
-        <v>5651</v>
+        <v>5333</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>728</v>
+        <v>528</v>
       </c>
       <c r="C6" t="n">
-        <v>5551</v>
+        <v>4877</v>
       </c>
       <c r="D6" t="n">
-        <v>2129</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="C7" t="n">
-        <v>4182</v>
+        <v>3731</v>
       </c>
       <c r="D7" t="n">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1960</v>
+        <v>1687</v>
       </c>
       <c r="D8" t="n">
-        <v>505</v>
+        <v>517</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>690</v>
+        <v>620</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>830</v>
+        <v>164</v>
       </c>
       <c r="C2" t="n">
-        <v>3093</v>
+        <v>2611</v>
       </c>
       <c r="D2" t="n">
-        <v>11366</v>
+        <v>5157</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>832</v>
+        <v>454</v>
       </c>
       <c r="C3" t="n">
-        <v>4002</v>
+        <v>2957</v>
       </c>
       <c r="D3" t="n">
-        <v>14080</v>
+        <v>9700</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1346</v>
+        <v>824</v>
       </c>
       <c r="C4" t="n">
-        <v>5034</v>
+        <v>3674</v>
       </c>
       <c r="D4" t="n">
-        <v>11321</v>
+        <v>9979</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>747</v>
+        <v>553</v>
       </c>
       <c r="C5" t="n">
-        <v>7330</v>
+        <v>6312</v>
       </c>
       <c r="D5" t="n">
-        <v>5232</v>
+        <v>4991</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>265</v>
+        <v>215</v>
       </c>
       <c r="C6" t="n">
-        <v>5512</v>
+        <v>4994</v>
       </c>
       <c r="D6" t="n">
-        <v>1779</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>1920</v>
+        <v>1653</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>676</v>
+        <v>607</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>411</v>
+        <v>119</v>
       </c>
       <c r="C2" t="n">
-        <v>1764</v>
+        <v>1476</v>
       </c>
       <c r="D2" t="n">
-        <v>8504</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>697</v>
+        <v>271</v>
       </c>
       <c r="C3" t="n">
-        <v>3119</v>
+        <v>2448</v>
       </c>
       <c r="D3" t="n">
-        <v>12679</v>
+        <v>8341</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>929</v>
+        <v>544</v>
       </c>
       <c r="C4" t="n">
-        <v>4269</v>
+        <v>3120</v>
       </c>
       <c r="D4" t="n">
-        <v>10980</v>
+        <v>9244</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>711</v>
+        <v>497</v>
       </c>
       <c r="C5" t="n">
-        <v>5535</v>
+        <v>4433</v>
       </c>
       <c r="D5" t="n">
-        <v>5459</v>
+        <v>5186</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="C6" t="n">
-        <v>5189</v>
+        <v>4704</v>
       </c>
       <c r="D6" t="n">
-        <v>1932</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>2535</v>
+        <v>2277</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>758</v>
+        <v>678</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D10" t="n">
         <v>141</v>
@@ -3086,10 +3086,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>743</v>
+        <v>146</v>
       </c>
       <c r="C2" t="n">
-        <v>7754</v>
+        <v>5017</v>
       </c>
       <c r="D2" t="n">
-        <v>18097</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>469</v>
+        <v>160</v>
       </c>
       <c r="C3" t="n">
-        <v>2060</v>
+        <v>1613</v>
       </c>
       <c r="D3" t="n">
-        <v>11098</v>
+        <v>7037</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>712</v>
+        <v>361</v>
       </c>
       <c r="C4" t="n">
-        <v>3528</v>
+        <v>2678</v>
       </c>
       <c r="D4" t="n">
-        <v>10972</v>
+        <v>8780</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>738</v>
+        <v>475</v>
       </c>
       <c r="C5" t="n">
-        <v>4780</v>
+        <v>3669</v>
       </c>
       <c r="D5" t="n">
-        <v>6300</v>
+        <v>5807</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>429</v>
+        <v>322</v>
       </c>
       <c r="C6" t="n">
-        <v>5310</v>
+        <v>4549</v>
       </c>
       <c r="D6" t="n">
-        <v>2514</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>3911</v>
+        <v>3581</v>
       </c>
       <c r="D7" t="n">
-        <v>829</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1618</v>
+        <v>1452</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="D9" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>64</v>
+      </c>
+      <c r="D12" t="n">
         <v>62</v>
-      </c>
-      <c r="D12" t="n">
-        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>894</v>
+        <v>172</v>
       </c>
       <c r="C2" t="n">
-        <v>4771</v>
+        <v>8093</v>
       </c>
       <c r="D2" t="n">
-        <v>18123</v>
+        <v>9517</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>487</v>
+        <v>126</v>
       </c>
       <c r="C3" t="n">
-        <v>4259</v>
+        <v>3002</v>
       </c>
       <c r="D3" t="n">
-        <v>11342</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>525</v>
+        <v>232</v>
       </c>
       <c r="C4" t="n">
-        <v>2693</v>
+        <v>2044</v>
       </c>
       <c r="D4" t="n">
-        <v>10554</v>
+        <v>8178</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>656</v>
+        <v>387</v>
       </c>
       <c r="C5" t="n">
-        <v>4009</v>
+        <v>3095</v>
       </c>
       <c r="D5" t="n">
-        <v>6915</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>524</v>
+        <v>368</v>
       </c>
       <c r="C6" t="n">
-        <v>4994</v>
+        <v>4051</v>
       </c>
       <c r="D6" t="n">
-        <v>3097</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="C7" t="n">
-        <v>4581</v>
+        <v>4098</v>
       </c>
       <c r="D7" t="n">
-        <v>1076</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>2673</v>
+        <v>2467</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>989</v>
+        <v>895</v>
       </c>
       <c r="D9" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
         <v>153</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3725,7 +3725,7 @@
         <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3396</v>
+        <v>1547</v>
       </c>
       <c r="C2" t="n">
-        <v>6149</v>
+        <v>2097</v>
       </c>
       <c r="D2" t="n">
-        <v>11991</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="3">
@@ -3932,10 +3932,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C5" t="n">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D5" t="n">
         <v>1139</v>
@@ -3949,10 +3949,10 @@
         <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D6" t="n">
-        <v>898</v>
+        <v>907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10">
@@ -4002,10 +4002,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D10" t="n">
         <v>485</v>
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D12" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13">
@@ -4047,10 +4047,10 @@
         <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D13" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14">
@@ -4061,7 +4061,7 @@
         <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D14" t="n">
         <v>207</v>
@@ -4078,7 +4078,7 @@
         <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
@@ -4089,10 +4089,10 @@
         <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D16" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -4103,10 +4103,10 @@
         <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D17" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18">
@@ -4117,7 +4117,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D18" t="n">
         <v>85</v>
@@ -4134,7 +4134,7 @@
         <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -4145,10 +4145,10 @@
         <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C21" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>759</v>
+        <v>682</v>
       </c>
       <c r="C2" t="n">
-        <v>7905</v>
+        <v>14344</v>
       </c>
       <c r="D2" t="n">
-        <v>15641</v>
+        <v>10519</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>538</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
-        <v>3952</v>
+        <v>4821</v>
       </c>
       <c r="D3" t="n">
-        <v>11502</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>438</v>
+        <v>160</v>
       </c>
       <c r="C4" t="n">
-        <v>3388</v>
+        <v>2498</v>
       </c>
       <c r="D4" t="n">
-        <v>10361</v>
+        <v>7524</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>554</v>
+        <v>295</v>
       </c>
       <c r="C5" t="n">
-        <v>3319</v>
+        <v>2505</v>
       </c>
       <c r="D5" t="n">
-        <v>7197</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>535</v>
+        <v>354</v>
       </c>
       <c r="C6" t="n">
-        <v>4462</v>
+        <v>3589</v>
       </c>
       <c r="D6" t="n">
-        <v>3641</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="C7" t="n">
-        <v>4761</v>
+        <v>4074</v>
       </c>
       <c r="D7" t="n">
-        <v>1351</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>3475</v>
+        <v>3209</v>
       </c>
       <c r="D8" t="n">
-        <v>524</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1655</v>
+        <v>1541</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>581</v>
+        <v>534</v>
       </c>
       <c r="D10" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4692</v>
+        <v>2694</v>
       </c>
       <c r="C2" t="n">
-        <v>7345</v>
+        <v>5277</v>
       </c>
       <c r="D2" t="n">
-        <v>23365</v>
+        <v>14795</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1123</v>
+        <v>515</v>
       </c>
       <c r="C3" t="n">
-        <v>2428</v>
+        <v>828</v>
       </c>
       <c r="D3" t="n">
-        <v>2251</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C5" t="n">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D5" t="n">
         <v>986</v>
@@ -4571,10 +4571,10 @@
         <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D6" t="n">
-        <v>712</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
         <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -4613,10 +4613,10 @@
         <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D9" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -4627,10 +4627,10 @@
         <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
         <v>182</v>
@@ -4672,7 +4672,7 @@
         <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
@@ -4683,10 +4683,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -4697,10 +4697,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16">
@@ -4711,10 +4711,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -4728,7 +4728,7 @@
         <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -4778,10 +4778,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2200</v>
+        <v>1986</v>
       </c>
       <c r="C2" t="n">
-        <v>5820</v>
+        <v>4998</v>
       </c>
       <c r="D2" t="n">
-        <v>22998</v>
+        <v>18234</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2467</v>
+        <v>1382</v>
       </c>
       <c r="C3" t="n">
-        <v>4635</v>
+        <v>3056</v>
       </c>
       <c r="D3" t="n">
-        <v>5797</v>
+        <v>3694</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>546</v>
+        <v>270</v>
       </c>
       <c r="C4" t="n">
-        <v>1562</v>
+        <v>572</v>
       </c>
       <c r="D4" t="n">
-        <v>1572</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D5" t="n">
-        <v>1039</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C6" t="n">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
         <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -4938,10 +4938,10 @@
         <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D10" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11">
@@ -4952,10 +4952,10 @@
         <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12">
@@ -4966,7 +4966,7 @@
         <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
         <v>187</v>
@@ -4980,7 +4980,7 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
         <v>155</v>
@@ -4994,10 +4994,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5008,10 +5008,10 @@
         <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -5022,10 +5022,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -5053,7 +5053,7 @@
         <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -5089,10 +5089,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2989</v>
+        <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>4806</v>
+        <v>5368</v>
       </c>
       <c r="D2" t="n">
-        <v>26010</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1924</v>
+        <v>1395</v>
       </c>
       <c r="C3" t="n">
-        <v>4579</v>
+        <v>3615</v>
       </c>
       <c r="D3" t="n">
-        <v>8260</v>
+        <v>5975</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1325</v>
+        <v>736</v>
       </c>
       <c r="C4" t="n">
-        <v>3388</v>
+        <v>2091</v>
       </c>
       <c r="D4" t="n">
-        <v>2375</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>279</v>
+        <v>164</v>
       </c>
       <c r="C5" t="n">
-        <v>995</v>
+        <v>418</v>
       </c>
       <c r="D5" t="n">
-        <v>1099</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C6" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D6" t="n">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
@@ -5280,7 +5280,7 @@
         <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D13" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
@@ -5308,7 +5308,7 @@
         <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -5378,7 +5378,7 @@
         <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5400,10 +5400,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2289</v>
+        <v>1291</v>
       </c>
       <c r="C2" t="n">
-        <v>4775</v>
+        <v>4252</v>
       </c>
       <c r="D2" t="n">
-        <v>27398</v>
+        <v>28614</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2015</v>
+        <v>1400</v>
       </c>
       <c r="C3" t="n">
-        <v>4065</v>
+        <v>3981</v>
       </c>
       <c r="D3" t="n">
-        <v>10505</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1406</v>
+        <v>937</v>
       </c>
       <c r="C4" t="n">
-        <v>4003</v>
+        <v>2974</v>
       </c>
       <c r="D4" t="n">
-        <v>3409</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>681</v>
+        <v>387</v>
       </c>
       <c r="C5" t="n">
-        <v>2306</v>
+        <v>1356</v>
       </c>
       <c r="D5" t="n">
-        <v>1310</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="C6" t="n">
-        <v>651</v>
+        <v>349</v>
       </c>
       <c r="D6" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D8" t="n">
         <v>427</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
         <v>257</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
         <v>159</v>
@@ -5616,10 +5616,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2096</v>
+        <v>1495</v>
       </c>
       <c r="C2" t="n">
-        <v>8517</v>
+        <v>3790</v>
       </c>
       <c r="D2" t="n">
-        <v>28054</v>
+        <v>27213</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1770</v>
+        <v>1124</v>
       </c>
       <c r="C3" t="n">
-        <v>3855</v>
+        <v>3573</v>
       </c>
       <c r="D3" t="n">
-        <v>12333</v>
+        <v>10638</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1453</v>
+        <v>1007</v>
       </c>
       <c r="C4" t="n">
-        <v>3953</v>
+        <v>3482</v>
       </c>
       <c r="D4" t="n">
-        <v>4566</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>903</v>
+        <v>571</v>
       </c>
       <c r="C5" t="n">
-        <v>3154</v>
+        <v>2226</v>
       </c>
       <c r="D5" t="n">
-        <v>1653</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>368</v>
+        <v>228</v>
       </c>
       <c r="C6" t="n">
-        <v>1485</v>
+        <v>867</v>
       </c>
       <c r="D6" t="n">
-        <v>911</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>472</v>
+        <v>330</v>
       </c>
       <c r="D7" t="n">
-        <v>613</v>
+        <v>627</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>262</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
         <v>203</v>
@@ -5913,10 +5913,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>114</v>
@@ -5955,10 +5955,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5983,10 +5983,10 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -5997,10 +5997,10 @@
         <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -6011,10 +6011,10 @@
         <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2371</v>
+        <v>1409</v>
       </c>
       <c r="C2" t="n">
-        <v>8148</v>
+        <v>9861</v>
       </c>
       <c r="D2" t="n">
-        <v>32066</v>
+        <v>28044</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1583</v>
+        <v>1069</v>
       </c>
       <c r="C3" t="n">
-        <v>5381</v>
+        <v>3203</v>
       </c>
       <c r="D3" t="n">
-        <v>13748</v>
+        <v>12408</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1384</v>
+        <v>921</v>
       </c>
       <c r="C4" t="n">
-        <v>3819</v>
+        <v>3492</v>
       </c>
       <c r="D4" t="n">
-        <v>5725</v>
+        <v>4736</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1016</v>
+        <v>686</v>
       </c>
       <c r="C5" t="n">
-        <v>3487</v>
+        <v>2830</v>
       </c>
       <c r="D5" t="n">
-        <v>2106</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>554</v>
+        <v>351</v>
       </c>
       <c r="C6" t="n">
-        <v>2270</v>
+        <v>1536</v>
       </c>
       <c r="D6" t="n">
-        <v>1019</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>207</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>943</v>
+        <v>596</v>
       </c>
       <c r="D7" t="n">
-        <v>647</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>318</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C9" t="n">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
         <v>355</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D10" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>136</v>
@@ -6252,10 +6252,10 @@
         <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D15" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2139</v>
+        <v>1263</v>
       </c>
       <c r="C2" t="n">
-        <v>4953</v>
+        <v>5679</v>
       </c>
       <c r="D2" t="n">
-        <v>25147</v>
+        <v>21537</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2285</v>
+        <v>1558</v>
       </c>
       <c r="C3" t="n">
-        <v>7976</v>
+        <v>6322</v>
       </c>
       <c r="D3" t="n">
-        <v>15297</v>
+        <v>14082</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>938</v>
+        <v>633</v>
       </c>
       <c r="C4" t="n">
-        <v>5767</v>
+        <v>5029</v>
       </c>
       <c r="D4" t="n">
-        <v>5297</v>
+        <v>4404</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>511</v>
+        <v>324</v>
       </c>
       <c r="C5" t="n">
-        <v>2224</v>
+        <v>1505</v>
       </c>
       <c r="D5" t="n">
-        <v>1625</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>924</v>
+        <v>584</v>
       </c>
       <c r="D6" t="n">
-        <v>634</v>
+        <v>649</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="D7" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D8" t="n">
         <v>347</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
         <v>133</v>
@@ -6549,10 +6549,10 @@
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D17" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">

--- a/output/yearly_population_growth_param_0.5.xlsx
+++ b/output/yearly_population_growth_param_0.5.xlsx
@@ -475,7 +475,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>732.732</v>
+        <v>719.3159999999999</v>
       </c>
     </row>
     <row r="3">
@@ -483,13 +483,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.6</v>
+        <v>30.27</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>948.794</v>
+        <v>931.422</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>387.6</v>
+        <v>383.42</v>
       </c>
       <c r="C4" t="n">
-        <v>703.725</v>
+        <v>710.985</v>
       </c>
       <c r="D4" t="n">
-        <v>2198.196</v>
+        <v>2157.948</v>
       </c>
     </row>
     <row r="5">
@@ -511,13 +511,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>322.32</v>
+        <v>318.844</v>
       </c>
       <c r="C5" t="n">
-        <v>511.8</v>
+        <v>517.08</v>
       </c>
       <c r="D5" t="n">
-        <v>967.5820000000001</v>
+        <v>949.8660000000001</v>
       </c>
     </row>
     <row r="6">
@@ -525,13 +525,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>238.68</v>
+        <v>236.106</v>
       </c>
       <c r="C6" t="n">
-        <v>477.68</v>
+        <v>482.6079999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>911.2179999999998</v>
+        <v>894.534</v>
       </c>
     </row>
     <row r="7">
@@ -539,13 +539,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>201.8</v>
       </c>
       <c r="C7" t="n">
-        <v>315.61</v>
+        <v>318.866</v>
       </c>
       <c r="D7" t="n">
-        <v>544.852</v>
+        <v>534.876</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>169.32</v>
+        <v>167.494</v>
       </c>
       <c r="C8" t="n">
-        <v>307.08</v>
+        <v>310.248</v>
       </c>
       <c r="D8" t="n">
-        <v>535.4580000000001</v>
+        <v>525.654</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +567,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134.64</v>
+        <v>133.188</v>
       </c>
       <c r="C9" t="n">
-        <v>255.9</v>
+        <v>258.54</v>
       </c>
       <c r="D9" t="n">
-        <v>441.518</v>
+        <v>433.434</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +581,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>99.95999999999999</v>
+        <v>98.88200000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>272.96</v>
+        <v>275.776</v>
       </c>
       <c r="D10" t="n">
-        <v>497.8819999999999</v>
+        <v>488.766</v>
       </c>
     </row>
     <row r="11">
@@ -595,13 +595,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>65.28</v>
+        <v>64.57600000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>183.395</v>
+        <v>185.287</v>
       </c>
       <c r="D11" t="n">
-        <v>310.002</v>
+        <v>304.326</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>50.45</v>
       </c>
       <c r="C12" t="n">
-        <v>162.07</v>
+        <v>163.742</v>
       </c>
       <c r="D12" t="n">
-        <v>272.426</v>
+        <v>267.438</v>
       </c>
     </row>
     <row r="13">
@@ -623,13 +623,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>42.84</v>
+        <v>42.378</v>
       </c>
       <c r="C13" t="n">
-        <v>132.215</v>
+        <v>133.579</v>
       </c>
       <c r="D13" t="n">
-        <v>234.85</v>
+        <v>230.55</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +637,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>40.8</v>
+        <v>40.36</v>
       </c>
       <c r="C14" t="n">
-        <v>127.95</v>
+        <v>129.27</v>
       </c>
       <c r="D14" t="n">
-        <v>206.668</v>
+        <v>202.884</v>
       </c>
     </row>
     <row r="15">
@@ -651,13 +651,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>40.8</v>
+        <v>40.36</v>
       </c>
       <c r="C15" t="n">
-        <v>127.95</v>
+        <v>129.27</v>
       </c>
       <c r="D15" t="n">
-        <v>169.092</v>
+        <v>165.996</v>
       </c>
     </row>
     <row r="16">
@@ -665,13 +665,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>38.76</v>
+        <v>38.342</v>
       </c>
       <c r="C16" t="n">
-        <v>123.685</v>
+        <v>124.961</v>
       </c>
       <c r="D16" t="n">
-        <v>140.91</v>
+        <v>138.33</v>
       </c>
     </row>
     <row r="17">
@@ -679,13 +679,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>38.76</v>
+        <v>38.342</v>
       </c>
       <c r="C17" t="n">
-        <v>119.42</v>
+        <v>120.652</v>
       </c>
       <c r="D17" t="n">
-        <v>112.728</v>
+        <v>110.664</v>
       </c>
     </row>
     <row r="18">
@@ -693,13 +693,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36.72</v>
+        <v>36.324</v>
       </c>
       <c r="C18" t="n">
-        <v>115.155</v>
+        <v>116.343</v>
       </c>
       <c r="D18" t="n">
-        <v>84.54600000000001</v>
+        <v>82.998</v>
       </c>
     </row>
     <row r="19">
@@ -707,13 +707,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>36.72</v>
+        <v>36.324</v>
       </c>
       <c r="C19" t="n">
-        <v>110.89</v>
+        <v>112.034</v>
       </c>
       <c r="D19" t="n">
-        <v>56.364</v>
+        <v>55.332</v>
       </c>
     </row>
     <row r="20">
@@ -721,13 +721,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>32.64</v>
+        <v>32.288</v>
       </c>
       <c r="C20" t="n">
-        <v>110.89</v>
+        <v>112.034</v>
       </c>
       <c r="D20" t="n">
-        <v>28.182</v>
+        <v>27.666</v>
       </c>
     </row>
     <row r="21">
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>30.6</v>
+        <v>30.27</v>
       </c>
       <c r="C21" t="n">
-        <v>106.625</v>
+        <v>107.725</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>341</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3">
@@ -800,7 +800,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1049</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
         <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>1515</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C5" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>1380</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="C6" t="n">
-        <v>257</v>
+        <v>220</v>
       </c>
       <c r="D6" t="n">
-        <v>1045</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="C7" t="n">
-        <v>428</v>
+        <v>374</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="C8" t="n">
-        <v>509</v>
+        <v>456</v>
       </c>
       <c r="D8" t="n">
-        <v>592</v>
+        <v>566</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C9" t="n">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="D9" t="n">
-        <v>523</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C10" t="n">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="D10" t="n">
-        <v>452</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C11" t="n">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D11" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12">
@@ -920,7 +920,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C12" t="n">
         <v>276</v>
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C13" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D13" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C14" t="n">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D14" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D15" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C16" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D16" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D17" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -1032,13 +1032,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C20" t="n">
-        <v>236</v>
+        <v>363</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>286</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>935</v>
+        <v>961</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>1455</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
-        <v>1414</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="C6" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="D6" t="n">
-        <v>1091</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="C7" t="n">
-        <v>368</v>
+        <v>309</v>
       </c>
       <c r="D7" t="n">
-        <v>801</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>488</v>
+        <v>426</v>
       </c>
       <c r="D8" t="n">
-        <v>618</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C9" t="n">
-        <v>490</v>
+        <v>451</v>
       </c>
       <c r="D9" t="n">
-        <v>531</v>
+        <v>509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C10" t="n">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="D10" t="n">
-        <v>465</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C11" t="n">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D11" t="n">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C12" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D12" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C13" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="D13" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C14" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D14" t="n">
         <v>212</v>
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C15" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D15" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C16" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D16" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C17" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D17" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
@@ -1329,13 +1329,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
@@ -1343,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C20" t="n">
-        <v>253</v>
+        <v>400</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>837</v>
+        <v>868</v>
       </c>
     </row>
     <row r="4">
@@ -1436,7 +1436,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1377</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>1434</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="C6" t="n">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="D6" t="n">
-        <v>1147</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="C7" t="n">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="D7" t="n">
-        <v>838</v>
+        <v>805</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="C8" t="n">
-        <v>453</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>647</v>
+        <v>613</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="C9" t="n">
-        <v>494</v>
+        <v>445</v>
       </c>
       <c r="D9" t="n">
-        <v>541</v>
+        <v>525</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C10" t="n">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="D10" t="n">
-        <v>477</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C11" t="n">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="D11" t="n">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D12" t="n">
         <v>310</v>
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C13" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D13" t="n">
         <v>260</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C14" t="n">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="D14" t="n">
         <v>217</v>
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C15" t="n">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D15" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D16" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C17" t="n">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D17" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D18" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +1640,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -1654,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="C20" t="n">
-        <v>272</v>
+        <v>429</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C21" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>206</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3">
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>747</v>
+        <v>782</v>
       </c>
     </row>
     <row r="4">
@@ -1747,7 +1747,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1309</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>1426</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="C6" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D6" t="n">
-        <v>1198</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>251</v>
+        <v>199</v>
       </c>
       <c r="D7" t="n">
-        <v>886</v>
+        <v>841</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="C8" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D8" t="n">
-        <v>669</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="C9" t="n">
-        <v>485</v>
+        <v>419</v>
       </c>
       <c r="D9" t="n">
-        <v>559</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C10" t="n">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="D10" t="n">
-        <v>484</v>
+        <v>464</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C11" t="n">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="D11" t="n">
-        <v>401</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C12" t="n">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D12" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="C13" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D13" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C14" t="n">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="D14" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C15" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="D15" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>46</v>
       </c>
       <c r="C16" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="D16" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C17" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D17" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D18" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="C20" t="n">
-        <v>288</v>
+        <v>462</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C21" t="n">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3">
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>671</v>
+        <v>709</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1230</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>1423</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C6" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D6" t="n">
-        <v>1227</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>201</v>
+        <v>157</v>
       </c>
       <c r="D7" t="n">
-        <v>935</v>
+        <v>877</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>258</v>
+        <v>216</v>
       </c>
       <c r="C8" t="n">
-        <v>361</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>701</v>
+        <v>663</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="C9" t="n">
-        <v>464</v>
+        <v>391</v>
       </c>
       <c r="D9" t="n">
-        <v>571</v>
+        <v>554</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="C10" t="n">
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="D10" t="n">
-        <v>497</v>
+        <v>472</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C11" t="n">
-        <v>443</v>
+        <v>408</v>
       </c>
       <c r="D11" t="n">
-        <v>409</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C12" t="n">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="D12" t="n">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C13" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D13" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C14" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="D14" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C15" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D15" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16">
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" t="n">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D16" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -2276,13 +2276,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C20" t="n">
-        <v>304</v>
+        <v>495</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>152</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>601</v>
+        <v>641</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1164</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>1397</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C6" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D6" t="n">
-        <v>1264</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="D7" t="n">
-        <v>970</v>
+        <v>909</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>243</v>
+        <v>198</v>
       </c>
       <c r="C8" t="n">
-        <v>313</v>
+        <v>239</v>
       </c>
       <c r="D8" t="n">
-        <v>736</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="C9" t="n">
-        <v>435</v>
+        <v>352</v>
       </c>
       <c r="D9" t="n">
-        <v>585</v>
+        <v>567</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="C10" t="n">
-        <v>491</v>
+        <v>416</v>
       </c>
       <c r="D10" t="n">
-        <v>510</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C11" t="n">
-        <v>465</v>
+        <v>419</v>
       </c>
       <c r="D11" t="n">
-        <v>421</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C12" t="n">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="D12" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C13" t="n">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D13" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C14" t="n">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="D14" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C15" t="n">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="D15" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16">
@@ -2531,13 +2531,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C16" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="D16" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17">
@@ -2545,13 +2545,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D17" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C18" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -2573,13 +2573,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -2587,13 +2587,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="C20" t="n">
-        <v>324</v>
+        <v>524</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>36</v>
+        <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>538</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4">
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1096</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1380</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>1279</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="D7" t="n">
-        <v>1014</v>
+        <v>940</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="C8" t="n">
-        <v>265</v>
+        <v>199</v>
       </c>
       <c r="D8" t="n">
-        <v>761</v>
+        <v>714</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>269</v>
+        <v>223</v>
       </c>
       <c r="C9" t="n">
-        <v>404</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>607</v>
+        <v>581</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="C10" t="n">
-        <v>484</v>
+        <v>398</v>
       </c>
       <c r="D10" t="n">
-        <v>517</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="C11" t="n">
-        <v>476</v>
+        <v>418</v>
       </c>
       <c r="D11" t="n">
-        <v>434</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C12" t="n">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="D12" t="n">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="C13" t="n">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D13" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C14" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D14" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C15" t="n">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="D15" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16">
@@ -2842,13 +2842,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C16" t="n">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="D16" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D17" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18">
@@ -2870,13 +2870,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C18" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D19" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -2898,13 +2898,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="C20" t="n">
-        <v>341</v>
+        <v>553</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C21" t="n">
-        <v>38</v>
+        <v>157</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>484</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1023</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1356</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>1291</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D7" t="n">
-        <v>1055</v>
+        <v>979</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>165</v>
       </c>
       <c r="D8" t="n">
-        <v>788</v>
+        <v>738</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>262</v>
+        <v>211</v>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>630</v>
+        <v>595</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="C10" t="n">
-        <v>470</v>
+        <v>373</v>
       </c>
       <c r="D10" t="n">
-        <v>531</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="C11" t="n">
-        <v>482</v>
+        <v>411</v>
       </c>
       <c r="D11" t="n">
-        <v>441</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C12" t="n">
-        <v>443</v>
+        <v>398</v>
       </c>
       <c r="D12" t="n">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C13" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D13" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14">
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C14" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D14" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C15" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D15" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C16" t="n">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="D16" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="D17" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18">
@@ -3181,13 +3181,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C18" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D18" t="n">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
@@ -3209,13 +3209,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="C20" t="n">
-        <v>356</v>
+        <v>583</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
+        <v>32</v>
+      </c>
+      <c r="C21" t="n">
+        <v>160</v>
+      </c>
+      <c r="D21" t="n">
         <v>7</v>
-      </c>
-      <c r="C21" t="n">
-        <v>40</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>435</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4">
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>963</v>
+        <v>959</v>
       </c>
     </row>
     <row r="5">
@@ -3316,7 +3316,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1316</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>1311</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="D7" t="n">
-        <v>1080</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>186</v>
+        <v>136</v>
       </c>
       <c r="D8" t="n">
-        <v>825</v>
+        <v>764</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>250</v>
+        <v>199</v>
       </c>
       <c r="C9" t="n">
-        <v>331</v>
+        <v>242</v>
       </c>
       <c r="D9" t="n">
-        <v>645</v>
+        <v>610</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="C10" t="n">
-        <v>446</v>
+        <v>342</v>
       </c>
       <c r="D10" t="n">
-        <v>546</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C11" t="n">
-        <v>488</v>
+        <v>399</v>
       </c>
       <c r="D11" t="n">
-        <v>449</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C12" t="n">
-        <v>457</v>
+        <v>406</v>
       </c>
       <c r="D12" t="n">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C13" t="n">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="D13" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14">
@@ -3436,13 +3436,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C14" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D14" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C15" t="n">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="D15" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C16" t="n">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="D16" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C17" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18">
@@ -3492,13 +3492,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C18" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D18" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
@@ -3520,13 +3520,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
+        <v>149</v>
+      </c>
+      <c r="C20" t="n">
+        <v>613</v>
+      </c>
+      <c r="D20" t="n">
         <v>85</v>
-      </c>
-      <c r="C20" t="n">
-        <v>376</v>
-      </c>
-      <c r="D20" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
+        <v>32</v>
+      </c>
+      <c r="C21" t="n">
+        <v>163</v>
+      </c>
+      <c r="D21" t="n">
         <v>7</v>
-      </c>
-      <c r="C21" t="n">
-        <v>39</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>391</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4">
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="5">
@@ -3627,7 +3627,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1273</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>1324</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D7" t="n">
-        <v>1105</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="D8" t="n">
-        <v>861</v>
+        <v>790</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="C9" t="n">
-        <v>292</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>663</v>
+        <v>633</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="C10" t="n">
-        <v>422</v>
+        <v>312</v>
       </c>
       <c r="D10" t="n">
-        <v>561</v>
+        <v>523</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="C11" t="n">
-        <v>481</v>
+        <v>381</v>
       </c>
       <c r="D11" t="n">
-        <v>457</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C12" t="n">
-        <v>473</v>
+        <v>407</v>
       </c>
       <c r="D12" t="n">
-        <v>378</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C13" t="n">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="D13" t="n">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C14" t="n">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D14" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C15" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="D15" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C16" t="n">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="D16" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
@@ -3789,13 +3789,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C17" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="D17" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18">
@@ -3803,13 +3803,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C18" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19">
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C19" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
@@ -3831,13 +3831,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="C20" t="n">
-        <v>391</v>
+        <v>644</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
+        <v>34</v>
+      </c>
+      <c r="C21" t="n">
+        <v>165</v>
+      </c>
+      <c r="D21" t="n">
         <v>7</v>
-      </c>
-      <c r="C21" t="n">
-        <v>41</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1681</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C3" t="n">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="D3" t="n">
-        <v>2198</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C4" t="n">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="D4" t="n">
-        <v>967</v>
+        <v>949</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C5" t="n">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D5" t="n">
-        <v>911</v>
+        <v>894</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C6" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D6" t="n">
-        <v>544</v>
+        <v>534</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>497</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12">
@@ -4033,10 +4033,10 @@
         <v>42</v>
       </c>
       <c r="C12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13">
@@ -4047,10 +4047,10 @@
         <v>40</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D13" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14">
@@ -4061,10 +4061,10 @@
         <v>40</v>
       </c>
       <c r="C14" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D14" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15">
@@ -4075,10 +4075,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D15" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16">
@@ -4089,10 +4089,10 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D16" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17">
@@ -4103,10 +4103,10 @@
         <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D17" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18">
@@ -4117,10 +4117,10 @@
         <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -4131,10 +4131,10 @@
         <v>32</v>
       </c>
       <c r="C19" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -4145,7 +4145,7 @@
         <v>30</v>
       </c>
       <c r="C20" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>354</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>841</v>
+        <v>855</v>
       </c>
     </row>
     <row r="5">
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1241</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>1318</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>1140</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="D8" t="n">
-        <v>885</v>
+        <v>813</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>223</v>
+        <v>174</v>
       </c>
       <c r="C9" t="n">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="D9" t="n">
-        <v>689</v>
+        <v>648</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>263</v>
+        <v>209</v>
       </c>
       <c r="C10" t="n">
-        <v>395</v>
+        <v>282</v>
       </c>
       <c r="D10" t="n">
-        <v>570</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="C11" t="n">
-        <v>471</v>
+        <v>360</v>
       </c>
       <c r="D11" t="n">
-        <v>470</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C12" t="n">
-        <v>484</v>
+        <v>403</v>
       </c>
       <c r="D12" t="n">
-        <v>384</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C13" t="n">
-        <v>429</v>
+        <v>388</v>
       </c>
       <c r="D13" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C14" t="n">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D14" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D15" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C16" t="n">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="D16" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17">
@@ -4411,13 +4411,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C17" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D17" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18">
@@ -4428,10 +4428,10 @@
         <v>44</v>
       </c>
       <c r="C18" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D18" t="n">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19">
@@ -4439,13 +4439,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C19" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -4453,13 +4453,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="C20" t="n">
-        <v>407</v>
+        <v>675</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C21" t="n">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1344</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C3" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D3" t="n">
-        <v>2094</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C4" t="n">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="D4" t="n">
-        <v>1222</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C5" t="n">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D5" t="n">
-        <v>930</v>
+        <v>913</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C6" t="n">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>615</v>
+        <v>602</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C7" t="n">
         <v>317</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C8" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -4613,10 +4613,10 @@
         <v>114</v>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>493</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -4641,10 +4641,10 @@
         <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12">
@@ -4655,10 +4655,10 @@
         <v>45</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13">
@@ -4669,10 +4669,10 @@
         <v>41</v>
       </c>
       <c r="C13" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D13" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
@@ -4683,10 +4683,10 @@
         <v>40</v>
       </c>
       <c r="C14" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
@@ -4697,10 +4697,10 @@
         <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D15" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
@@ -4711,10 +4711,10 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D16" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17">
@@ -4739,7 +4739,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
         <v>112</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -4764,13 +4764,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -4778,10 +4778,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1088</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C3" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D3" t="n">
-        <v>1951</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C4" t="n">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="D4" t="n">
-        <v>1399</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="D5" t="n">
-        <v>982</v>
+        <v>965</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C6" t="n">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="D6" t="n">
-        <v>677</v>
+        <v>661</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C7" t="n">
         <v>371</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>488</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C10" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D10" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C11" t="n">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D12" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D14" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D15" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D16" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D17" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18">
@@ -5053,7 +5053,7 @@
         <v>117</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
@@ -5064,10 +5064,10 @@
         <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -5075,13 +5075,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -5089,10 +5089,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>881</v>
+        <v>876</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>1787</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C4" t="n">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D4" t="n">
-        <v>1517</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="C5" t="n">
-        <v>535</v>
+        <v>511</v>
       </c>
       <c r="D5" t="n">
-        <v>1066</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C6" t="n">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="D6" t="n">
-        <v>735</v>
+        <v>715</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C7" t="n">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D7" t="n">
-        <v>573</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D8" t="n">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>491</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C10" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D10" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C11" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D11" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C12" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="D12" t="n">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>45</v>
       </c>
       <c r="C13" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D13" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14">
@@ -5302,10 +5302,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D14" t="n">
         <v>183</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D15" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D16" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D17" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
@@ -5375,10 +5375,10 @@
         <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5386,13 +5386,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C20" t="n">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5451,7 +5451,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>1623</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C4" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D4" t="n">
-        <v>1580</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="C5" t="n">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="D5" t="n">
-        <v>1142</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="C6" t="n">
-        <v>546</v>
+        <v>517</v>
       </c>
       <c r="D6" t="n">
-        <v>798</v>
+        <v>769</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C7" t="n">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>590</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C8" t="n">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>510</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C9" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>491</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C11" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D11" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D12" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D13" t="n">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D14" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D15" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D16" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D17" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -5697,13 +5697,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C20" t="n">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5762,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>1460</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C4" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" t="n">
-        <v>1603</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="C5" t="n">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="D5" t="n">
-        <v>1227</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="C6" t="n">
-        <v>496</v>
+        <v>455</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>828</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="D7" t="n">
-        <v>633</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C8" t="n">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="D8" t="n">
-        <v>529</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>175</v>
       </c>
       <c r="C9" t="n">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D9" t="n">
-        <v>498</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11">
@@ -5882,10 +5882,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C11" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D11" t="n">
         <v>328</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C12" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="D12" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D13" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>44</v>
       </c>
       <c r="C14" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D14" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D15" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D16" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D17" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C20" t="n">
-        <v>184</v>
+        <v>262</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>1312</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C4" t="n">
         <v>56</v>
       </c>
       <c r="D4" t="n">
-        <v>1594</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="C5" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="D5" t="n">
-        <v>1287</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="C6" t="n">
-        <v>418</v>
+        <v>372</v>
       </c>
       <c r="D6" t="n">
-        <v>928</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="C7" t="n">
-        <v>521</v>
+        <v>479</v>
       </c>
       <c r="D7" t="n">
-        <v>673</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="C8" t="n">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="D8" t="n">
-        <v>543</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C9" t="n">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="D9" t="n">
-        <v>507</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D10" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C11" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D11" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C12" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="D12" t="n">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C13" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D13" t="n">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C14" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D14" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D15" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D16" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D17" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D18" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C20" t="n">
-        <v>200</v>
+        <v>295</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3">
@@ -6398,7 +6398,7 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1172</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>1562</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C5" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="D5" t="n">
-        <v>1348</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="C6" t="n">
-        <v>333</v>
+        <v>293</v>
       </c>
       <c r="D6" t="n">
-        <v>981</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="C7" t="n">
-        <v>487</v>
+        <v>430</v>
       </c>
       <c r="D7" t="n">
-        <v>717</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="C8" t="n">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="D8" t="n">
-        <v>566</v>
+        <v>544</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C9" t="n">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="D9" t="n">
-        <v>511</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="D10" t="n">
-        <v>444</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C11" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D11" t="n">
         <v>352</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C12" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D12" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C13" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D13" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C14" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D14" t="n">
         <v>203</v>
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D15" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C16" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D16" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D17" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C20" t="n">
-        <v>217</v>
+        <v>332</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_growth_param_0.5.xlsx
+++ b/output/yearly_population_growth_param_0.5.xlsx
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>356</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1068</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1435</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>1312</v>
+        <v>908</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>191</v>
+        <v>41</v>
       </c>
       <c r="C6" t="n">
-        <v>220</v>
+        <v>64</v>
       </c>
       <c r="D6" t="n">
-        <v>999</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>374</v>
+        <v>171</v>
       </c>
       <c r="D7" t="n">
-        <v>730</v>
+        <v>789</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>252</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>456</v>
+        <v>296</v>
       </c>
       <c r="D8" t="n">
-        <v>566</v>
+        <v>599</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>222</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>448</v>
+        <v>372</v>
       </c>
       <c r="D9" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="C10" t="n">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D10" t="n">
-        <v>440</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="C11" t="n">
         <v>324</v>
       </c>
       <c r="D11" t="n">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="C12" t="n">
         <v>276</v>
       </c>
       <c r="D12" t="n">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D13" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D14" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D15" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D16" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D17" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -1032,13 +1032,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>363</v>
+        <v>105</v>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="C21" t="n">
-        <v>126</v>
+        <v>413</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>302</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>961</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1379</v>
+        <v>545</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>1343</v>
+        <v>833</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>159</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>163</v>
+        <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>1042</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>229</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>309</v>
+        <v>126</v>
       </c>
       <c r="D7" t="n">
-        <v>767</v>
+        <v>795</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>426</v>
+        <v>243</v>
       </c>
       <c r="D8" t="n">
-        <v>588</v>
+        <v>618</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="C9" t="n">
-        <v>451</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>509</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="D10" t="n">
-        <v>448</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="C11" t="n">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D11" t="n">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D12" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="C13" t="n">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D13" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D14" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D15" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D16" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D17" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D18" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -1329,13 +1329,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1343,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>400</v>
+        <v>105</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="C21" t="n">
-        <v>130</v>
+        <v>443</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>259</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>868</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1320</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1348</v>
+        <v>760</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>1084</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>207</v>
+        <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>250</v>
+        <v>91</v>
       </c>
       <c r="D7" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>613</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>238</v>
+        <v>99</v>
       </c>
       <c r="C9" t="n">
-        <v>445</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>525</v>
+        <v>492</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>208</v>
+        <v>98</v>
       </c>
       <c r="C10" t="n">
-        <v>426</v>
+        <v>349</v>
       </c>
       <c r="D10" t="n">
-        <v>455</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="C11" t="n">
-        <v>374</v>
+        <v>341</v>
       </c>
       <c r="D11" t="n">
-        <v>382</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="D12" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="D13" t="n">
-        <v>260</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D14" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D15" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D16" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D17" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +1640,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D19" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1654,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>429</v>
+        <v>105</v>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C21" t="n">
-        <v>140</v>
+        <v>472</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>222</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>782</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1256</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1357</v>
+        <v>691</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>1118</v>
+        <v>862</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>183</v>
+        <v>35</v>
       </c>
       <c r="C7" t="n">
-        <v>199</v>
+        <v>65</v>
       </c>
       <c r="D7" t="n">
-        <v>841</v>
+        <v>799</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>232</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>332</v>
+        <v>152</v>
       </c>
       <c r="D8" t="n">
         <v>637</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>240</v>
+        <v>86</v>
       </c>
       <c r="C9" t="n">
-        <v>419</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
-        <v>536</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>219</v>
+        <v>91</v>
       </c>
       <c r="C10" t="n">
-        <v>437</v>
+        <v>326</v>
       </c>
       <c r="D10" t="n">
-        <v>464</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="C11" t="n">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="D11" t="n">
-        <v>391</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>142</v>
+        <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>336</v>
+        <v>309</v>
       </c>
       <c r="D12" t="n">
-        <v>319</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D13" t="n">
-        <v>269</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="D14" t="n">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="D15" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D16" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>116</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>462</v>
+        <v>105</v>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="C21" t="n">
-        <v>145</v>
+        <v>501</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>193</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>709</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1194</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1343</v>
+        <v>632</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>1149</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="D7" t="n">
-        <v>877</v>
+        <v>791</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>216</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="D8" t="n">
-        <v>663</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>239</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>391</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>554</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="C10" t="n">
-        <v>430</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>472</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>408</v>
+        <v>328</v>
       </c>
       <c r="D11" t="n">
-        <v>399</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>359</v>
+        <v>316</v>
       </c>
       <c r="D12" t="n">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="D13" t="n">
-        <v>275</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="D14" t="n">
-        <v>227</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="D15" t="n">
-        <v>189</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="D16" t="n">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="D17" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D18" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2276,13 +2276,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>495</v>
+        <v>105</v>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="C21" t="n">
-        <v>147</v>
+        <v>529</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>167</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>641</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1130</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1337</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1172</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>909</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>198</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="D8" t="n">
-        <v>688</v>
+        <v>656</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>234</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>178</v>
       </c>
       <c r="D9" t="n">
-        <v>567</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="C10" t="n">
-        <v>416</v>
+        <v>262</v>
       </c>
       <c r="D10" t="n">
-        <v>481</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>200</v>
+        <v>74</v>
       </c>
       <c r="C11" t="n">
-        <v>419</v>
+        <v>314</v>
       </c>
       <c r="D11" t="n">
-        <v>407</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>375</v>
+        <v>316</v>
       </c>
       <c r="D12" t="n">
-        <v>335</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="D13" t="n">
-        <v>281</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="D14" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="D15" t="n">
-        <v>193</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -2531,13 +2531,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D16" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17">
@@ -2545,13 +2545,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="D17" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="D18" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19">
@@ -2573,13 +2573,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D19" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -2587,13 +2587,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>524</v>
+        <v>104</v>
       </c>
       <c r="D20" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="C21" t="n">
-        <v>153</v>
+        <v>557</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>584</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1071</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1312</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1191</v>
+        <v>734</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>940</v>
+        <v>770</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>199</v>
+        <v>68</v>
       </c>
       <c r="D8" t="n">
-        <v>714</v>
+        <v>657</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>223</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>313</v>
+        <v>144</v>
       </c>
       <c r="D9" t="n">
-        <v>581</v>
+        <v>522</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
+        <v>65</v>
+      </c>
+      <c r="C10" t="n">
         <v>230</v>
       </c>
-      <c r="C10" t="n">
-        <v>398</v>
-      </c>
       <c r="D10" t="n">
-        <v>496</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>208</v>
+        <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>418</v>
+        <v>293</v>
       </c>
       <c r="D11" t="n">
-        <v>415</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>177</v>
+        <v>62</v>
       </c>
       <c r="C12" t="n">
-        <v>389</v>
+        <v>309</v>
       </c>
       <c r="D12" t="n">
-        <v>342</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
-        <v>342</v>
+        <v>292</v>
       </c>
       <c r="D13" t="n">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="D14" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="D15" t="n">
-        <v>197</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
@@ -2842,13 +2842,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="D16" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="D17" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -2870,13 +2870,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="D18" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -2898,13 +2898,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>553</v>
+        <v>105</v>
       </c>
       <c r="D20" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="C21" t="n">
-        <v>157</v>
+        <v>584</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>531</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1012</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1283</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1205</v>
+        <v>692</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>979</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>738</v>
+        <v>657</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>116</v>
       </c>
       <c r="D9" t="n">
-        <v>595</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>228</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>373</v>
+        <v>198</v>
       </c>
       <c r="D10" t="n">
-        <v>505</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>213</v>
+        <v>62</v>
       </c>
       <c r="C11" t="n">
-        <v>411</v>
+        <v>266</v>
       </c>
       <c r="D11" t="n">
-        <v>423</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>187</v>
+        <v>58</v>
       </c>
       <c r="C12" t="n">
-        <v>398</v>
+        <v>300</v>
       </c>
       <c r="D12" t="n">
-        <v>350</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>360</v>
+        <v>294</v>
       </c>
       <c r="D13" t="n">
-        <v>292</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14">
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
-        <v>306</v>
+        <v>263</v>
       </c>
       <c r="D14" t="n">
-        <v>245</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="D15" t="n">
-        <v>201</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="D16" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="D17" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -3181,13 +3181,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="D18" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D19" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -3209,13 +3209,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>143</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>583</v>
+        <v>106</v>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C21" t="n">
-        <v>160</v>
+        <v>610</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>486</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>959</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1253</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1213</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>1003</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>764</v>
+        <v>654</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>199</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>242</v>
+        <v>92</v>
       </c>
       <c r="D9" t="n">
-        <v>610</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>223</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>342</v>
+        <v>167</v>
       </c>
       <c r="D10" t="n">
-        <v>514</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>216</v>
+        <v>55</v>
       </c>
       <c r="C11" t="n">
-        <v>399</v>
+        <v>241</v>
       </c>
       <c r="D11" t="n">
-        <v>432</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>195</v>
+        <v>55</v>
       </c>
       <c r="C12" t="n">
-        <v>406</v>
+        <v>286</v>
       </c>
       <c r="D12" t="n">
-        <v>361</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="C13" t="n">
-        <v>371</v>
+        <v>289</v>
       </c>
       <c r="D13" t="n">
-        <v>297</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14">
@@ -3436,13 +3436,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>121</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="D14" t="n">
-        <v>249</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="D15" t="n">
-        <v>205</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="D16" t="n">
-        <v>173</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="D17" t="n">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18">
@@ -3492,13 +3492,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="D18" t="n">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="D19" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -3520,13 +3520,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>149</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>613</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="C21" t="n">
-        <v>163</v>
+        <v>637</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>444</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>906</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1220</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1217</v>
+        <v>609</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1026</v>
+        <v>704</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>790</v>
+        <v>656</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>187</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v>633</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>217</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>312</v>
+        <v>140</v>
       </c>
       <c r="D10" t="n">
-        <v>523</v>
+        <v>436</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>217</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>381</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>440</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n">
-        <v>407</v>
+        <v>266</v>
       </c>
       <c r="D12" t="n">
-        <v>368</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>168</v>
+        <v>45</v>
       </c>
       <c r="C13" t="n">
-        <v>381</v>
+        <v>285</v>
       </c>
       <c r="D13" t="n">
-        <v>303</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>129</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>336</v>
+        <v>272</v>
       </c>
       <c r="D14" t="n">
-        <v>253</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="D15" t="n">
-        <v>209</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="D16" t="n">
-        <v>176</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
@@ -3789,13 +3789,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="D17" t="n">
-        <v>144</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -3803,13 +3803,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="D18" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -3831,13 +3831,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>153</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>644</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>91</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="C21" t="n">
-        <v>165</v>
+        <v>663</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1650</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>383</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>710</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2157</v>
+        <v>839</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>318</v>
+        <v>209</v>
       </c>
       <c r="C4" t="n">
-        <v>517</v>
+        <v>341</v>
       </c>
       <c r="D4" t="n">
-        <v>949</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>236</v>
+        <v>313</v>
       </c>
       <c r="C5" t="n">
-        <v>482</v>
+        <v>594</v>
       </c>
       <c r="D5" t="n">
-        <v>894</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="C6" t="n">
-        <v>318</v>
+        <v>493</v>
       </c>
       <c r="D6" t="n">
-        <v>534</v>
+        <v>890</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="C7" t="n">
-        <v>310</v>
+        <v>391</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="C8" t="n">
-        <v>258</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>488</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>304</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="D11" t="n">
-        <v>267</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D12" t="n">
-        <v>230</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D13" t="n">
-        <v>202</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" t="n">
-        <v>165</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15">
@@ -4075,10 +4075,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16">
@@ -4089,10 +4089,10 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D16" t="n">
-        <v>110</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D17" t="n">
-        <v>82</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>406</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>855</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1197</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1217</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1045</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>813</v>
+        <v>648</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>182</v>
+        <v>57</v>
       </c>
       <c r="D9" t="n">
-        <v>648</v>
+        <v>539</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>209</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>282</v>
+        <v>117</v>
       </c>
       <c r="D10" t="n">
-        <v>534</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>217</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>360</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>448</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="C12" t="n">
-        <v>403</v>
+        <v>247</v>
       </c>
       <c r="D12" t="n">
-        <v>375</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>177</v>
+        <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>388</v>
+        <v>276</v>
       </c>
       <c r="D13" t="n">
-        <v>309</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>348</v>
+        <v>270</v>
       </c>
       <c r="D14" t="n">
-        <v>258</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>305</v>
+        <v>246</v>
       </c>
       <c r="D15" t="n">
-        <v>215</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="D16" t="n">
-        <v>178</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -4411,13 +4411,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="D17" t="n">
-        <v>146</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -4425,13 +4425,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="D18" t="n">
-        <v>114</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
@@ -4439,13 +4439,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="D19" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -4453,13 +4453,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>159</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>675</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C21" t="n">
-        <v>167</v>
+        <v>689</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>210</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>298</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2055</v>
+        <v>733</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>353</v>
+        <v>108</v>
       </c>
       <c r="C4" t="n">
-        <v>628</v>
+        <v>163</v>
       </c>
       <c r="D4" t="n">
-        <v>1190</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="C5" t="n">
-        <v>507</v>
+        <v>454</v>
       </c>
       <c r="D5" t="n">
-        <v>913</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>530</v>
       </c>
       <c r="D6" t="n">
-        <v>602</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C7" t="n">
-        <v>317</v>
+        <v>434</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C8" t="n">
-        <v>287</v>
+        <v>344</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>477</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="D11" t="n">
-        <v>273</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="D12" t="n">
-        <v>236</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13">
@@ -4669,10 +4669,10 @@
         <v>41</v>
       </c>
       <c r="C13" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="D13" t="n">
-        <v>207</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D14" t="n">
-        <v>171</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C15" t="n">
         <v>126</v>
       </c>
       <c r="D15" t="n">
-        <v>142</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C16" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D16" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D17" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C18" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20">
@@ -4764,13 +4764,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C21" t="n">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1069</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>118</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1915</v>
+        <v>627</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>285</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>443</v>
+        <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>1354</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>314</v>
+        <v>173</v>
       </c>
       <c r="C5" t="n">
-        <v>579</v>
+        <v>303</v>
       </c>
       <c r="D5" t="n">
-        <v>965</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C6" t="n">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="D6" t="n">
-        <v>661</v>
+        <v>934</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C7" t="n">
-        <v>371</v>
+        <v>473</v>
       </c>
       <c r="D7" t="n">
-        <v>545</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C8" t="n">
-        <v>303</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C9" t="n">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>472</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C10" t="n">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="D10" t="n">
-        <v>366</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C12" t="n">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="D12" t="n">
-        <v>242</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="D13" t="n">
-        <v>214</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D14" t="n">
-        <v>177</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C15" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D17" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C18" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D18" t="n">
-        <v>64</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C19" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -5075,13 +5075,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C20" t="n">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C21" t="n">
-        <v>51</v>
+        <v>212</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>876</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1762</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>209</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
-        <v>274</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>1454</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>304</v>
+        <v>116</v>
       </c>
       <c r="C5" t="n">
-        <v>511</v>
+        <v>190</v>
       </c>
       <c r="D5" t="n">
-        <v>1035</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>274</v>
+        <v>194</v>
       </c>
       <c r="C6" t="n">
-        <v>524</v>
+        <v>392</v>
       </c>
       <c r="D6" t="n">
-        <v>715</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="C7" t="n">
-        <v>423</v>
+        <v>473</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>338</v>
+        <v>417</v>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>533</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>475</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>110</v>
       </c>
       <c r="C10" t="n">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="D10" t="n">
-        <v>384</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C11" t="n">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="D11" t="n">
-        <v>298</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C12" t="n">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="D12" t="n">
-        <v>249</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="D13" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D14" t="n">
-        <v>183</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
         <v>130</v>
       </c>
       <c r="D15" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C16" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D16" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C17" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D17" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C18" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C19" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
@@ -5386,13 +5386,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C20" t="n">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C21" t="n">
-        <v>74</v>
+        <v>248</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>718</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1602</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>149</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>1509</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>263</v>
+        <v>76</v>
       </c>
       <c r="C5" t="n">
-        <v>392</v>
+        <v>116</v>
       </c>
       <c r="D5" t="n">
-        <v>1120</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>289</v>
+        <v>151</v>
       </c>
       <c r="C6" t="n">
-        <v>517</v>
+        <v>295</v>
       </c>
       <c r="D6" t="n">
-        <v>769</v>
+        <v>982</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="C7" t="n">
-        <v>478</v>
+        <v>432</v>
       </c>
       <c r="D7" t="n">
-        <v>590</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>432</v>
       </c>
       <c r="D8" t="n">
-        <v>491</v>
+        <v>544</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="C9" t="n">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="D9" t="n">
-        <v>475</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>399</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C11" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="D11" t="n">
-        <v>315</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C12" t="n">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="D12" t="n">
-        <v>256</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="D13" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="D14" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D15" t="n">
-        <v>156</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C16" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D16" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C17" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -5697,13 +5697,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>228</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="C21" t="n">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -5762,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>595</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1451</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>1524</v>
+        <v>948</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>217</v>
+        <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>280</v>
+        <v>69</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>278</v>
+        <v>114</v>
       </c>
       <c r="C6" t="n">
-        <v>455</v>
+        <v>212</v>
       </c>
       <c r="D6" t="n">
-        <v>828</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>501</v>
+        <v>364</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>214</v>
+        <v>162</v>
       </c>
       <c r="C8" t="n">
         <v>427</v>
       </c>
       <c r="D8" t="n">
-        <v>506</v>
+        <v>557</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>350</v>
+        <v>389</v>
       </c>
       <c r="D9" t="n">
-        <v>477</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="C10" t="n">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="D10" t="n">
-        <v>411</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C11" t="n">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="D11" t="n">
-        <v>328</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="D12" t="n">
-        <v>265</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C13" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D13" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D14" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D15" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D16" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>262</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C21" t="n">
-        <v>95</v>
+        <v>316</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>499</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1314</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1512</v>
+        <v>830</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>171</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>1240</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>256</v>
+        <v>83</v>
       </c>
       <c r="C6" t="n">
-        <v>372</v>
+        <v>147</v>
       </c>
       <c r="D6" t="n">
-        <v>885</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>268</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>479</v>
+        <v>292</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>233</v>
+        <v>150</v>
       </c>
       <c r="C8" t="n">
-        <v>466</v>
+        <v>396</v>
       </c>
       <c r="D8" t="n">
-        <v>525</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>191</v>
+        <v>137</v>
       </c>
       <c r="C9" t="n">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>481</v>
+        <v>466</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="C10" t="n">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="D10" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="D11" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D12" t="n">
-        <v>274</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C13" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="D13" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D14" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D15" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D16" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D17" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D19" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>295</v>
+        <v>106</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>349</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>419</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1183</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1480</v>
+        <v>721</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>1283</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>223</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>293</v>
+        <v>98</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>977</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>266</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>430</v>
+        <v>227</v>
       </c>
       <c r="D7" t="n">
-        <v>692</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>245</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>476</v>
+        <v>349</v>
       </c>
       <c r="D8" t="n">
-        <v>544</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="D9" t="n">
-        <v>487</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="C10" t="n">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="D10" t="n">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D11" t="n">
-        <v>352</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D12" t="n">
-        <v>283</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D13" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D14" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D15" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D16" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D17" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="C21" t="n">
-        <v>115</v>
+        <v>381</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_growth_param_0.5.xlsx
+++ b/output/yearly_population_growth_param_0.5.xlsx
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +814,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D7" t="n">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C9" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D9" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C10" t="n">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="D10" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D11" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D12" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" t="n">
         <v>237</v>
       </c>
       <c r="D13" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D14" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D15" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D16" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>124</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C21" t="n">
-        <v>413</v>
+        <v>366</v>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4">
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>545</v>
+        <v>535</v>
       </c>
     </row>
     <row r="5">
@@ -1139,7 +1139,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="6">
@@ -1150,10 +1150,10 @@
         <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="n">
-        <v>926</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D7" t="n">
-        <v>795</v>
+        <v>799</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="D8" t="n">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C9" t="n">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="D10" t="n">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D11" t="n">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D12" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13">
@@ -1245,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
         <v>248</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
         <v>209</v>
       </c>
       <c r="D14" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D15" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D16" t="n">
         <v>144</v>
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C21" t="n">
-        <v>443</v>
+        <v>393</v>
       </c>
       <c r="D21" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4">
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>473</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5">
@@ -1450,7 +1450,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>760</v>
+        <v>768</v>
       </c>
     </row>
     <row r="6">
@@ -1461,10 +1461,10 @@
         <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>892</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>810</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D8" t="n">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C10" t="n">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="D10" t="n">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C11" t="n">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="D11" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D12" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D13" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D14" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D15" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D16" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D18" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C21" t="n">
-        <v>472</v>
+        <v>420</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4">
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>409</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -1761,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>691</v>
+        <v>696</v>
       </c>
     </row>
     <row r="6">
@@ -1775,7 +1775,7 @@
         <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D7" t="n">
-        <v>799</v>
+        <v>814</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D8" t="n">
-        <v>637</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C10" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="D10" t="n">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C11" t="n">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D11" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D12" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D13" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D14" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D15" t="n">
         <v>173</v>
@@ -1912,10 +1912,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D16" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D17" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>120</v>
       </c>
       <c r="D18" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C21" t="n">
-        <v>501</v>
+        <v>446</v>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>353</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5">
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="6">
@@ -2086,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>821</v>
+        <v>830</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" t="n">
-        <v>791</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D8" t="n">
-        <v>644</v>
+        <v>651</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D9" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C10" t="n">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C11" t="n">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="D11" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="D12" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D13" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D14" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D15" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D16" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D17" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
         <v>122</v>
       </c>
       <c r="D18" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -2279,10 +2279,10 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C21" t="n">
-        <v>529</v>
+        <v>471</v>
       </c>
       <c r="D21" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5">
@@ -2383,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6">
@@ -2394,10 +2394,10 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>786</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>779</v>
+        <v>791</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D8" t="n">
-        <v>656</v>
+        <v>663</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D9" t="n">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C10" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D10" t="n">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C11" t="n">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="D11" t="n">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D12" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D13" t="n">
         <v>253</v>
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D14" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D15" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D16" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D17" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D18" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -2573,13 +2573,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -2590,10 +2590,10 @@
         <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D20" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C21" t="n">
-        <v>557</v>
+        <v>495</v>
       </c>
       <c r="D21" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>266</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5">
@@ -2708,7 +2708,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>734</v>
+        <v>741</v>
       </c>
     </row>
     <row r="7">
@@ -2722,7 +2722,7 @@
         <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D8" t="n">
-        <v>657</v>
+        <v>672</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D9" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="D11" t="n">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" t="n">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="D12" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13">
@@ -2800,10 +2800,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" t="n">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="D13" t="n">
         <v>254</v>
@@ -2814,10 +2814,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D14" t="n">
         <v>210</v>
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D15" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D16" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D17" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
@@ -2870,13 +2870,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D18" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -2901,10 +2901,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C21" t="n">
-        <v>584</v>
+        <v>519</v>
       </c>
       <c r="D21" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6">
@@ -3019,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>692</v>
+        <v>696</v>
       </c>
     </row>
     <row r="7">
@@ -3033,7 +3033,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>657</v>
+        <v>670</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D9" t="n">
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C11" t="n">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="D11" t="n">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" t="n">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D12" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D13" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14">
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D14" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D15" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D16" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D17" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
@@ -3187,7 +3187,7 @@
         <v>133</v>
       </c>
       <c r="D18" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
         <v>116</v>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -3215,7 +3215,7 @@
         <v>106</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C21" t="n">
-        <v>610</v>
+        <v>543</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>421</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6">
@@ -3344,7 +3344,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>728</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>654</v>
+        <v>667</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D9" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C11" t="n">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="D11" t="n">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C12" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="D12" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="D13" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D14" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
         <v>236</v>
       </c>
       <c r="D15" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>198</v>
       </c>
       <c r="D16" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D17" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
@@ -3492,13 +3492,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D18" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
         <v>118</v>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -3526,7 +3526,7 @@
         <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C21" t="n">
-        <v>637</v>
+        <v>566</v>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
@@ -3627,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>378</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6">
@@ -3641,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7">
@@ -3655,7 +3655,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>704</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
         <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" t="n">
-        <v>538</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>436</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D11" t="n">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="D12" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" t="n">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="D13" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="D14" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D15" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>206</v>
       </c>
       <c r="D16" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -3792,10 +3792,10 @@
         <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D17" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
@@ -3803,10 +3803,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D18" t="n">
         <v>93</v>
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -3837,7 +3837,7 @@
         <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C21" t="n">
-        <v>663</v>
+        <v>590</v>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3921,7 +3921,7 @@
         <v>209</v>
       </c>
       <c r="C4" t="n">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="D4" t="n">
         <v>1892</v>
@@ -3935,7 +3935,7 @@
         <v>313</v>
       </c>
       <c r="C5" t="n">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D5" t="n">
         <v>1106</v>
@@ -3946,7 +3946,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C6" t="n">
         <v>493</v>
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D7" t="n">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -3974,10 +3974,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C8" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D8" t="n">
         <v>521</v>
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D10" t="n">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11">
@@ -4019,10 +4019,10 @@
         <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D11" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12">
@@ -4030,10 +4030,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D12" t="n">
         <v>267</v>
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
         <v>144</v>
       </c>
       <c r="D13" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
@@ -4058,7 +4058,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
         <v>130</v>
@@ -4072,7 +4072,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C15" t="n">
         <v>127</v>
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" t="n">
         <v>126</v>
       </c>
       <c r="D16" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4103,10 +4103,10 @@
         <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D17" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18">
@@ -4145,10 +4145,10 @@
         <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6">
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7">
@@ -4277,7 +4277,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8">
@@ -4291,7 +4291,7 @@
         <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>648</v>
+        <v>655</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
         <v>57</v>
       </c>
       <c r="D9" t="n">
-        <v>539</v>
+        <v>554</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D10" t="n">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C12" t="n">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="D12" t="n">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="D13" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="D14" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D15" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>213</v>
       </c>
       <c r="D16" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17">
@@ -4417,7 +4417,7 @@
         <v>178</v>
       </c>
       <c r="D17" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
@@ -4428,10 +4428,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D18" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19">
@@ -4439,13 +4439,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -4459,7 +4459,7 @@
         <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C21" t="n">
-        <v>689</v>
+        <v>613</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -4540,10 +4540,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C4" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D4" t="n">
         <v>1644</v>
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C5" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="D5" t="n">
-        <v>1190</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6">
@@ -4571,10 +4571,10 @@
         <v>257</v>
       </c>
       <c r="C6" t="n">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D6" t="n">
-        <v>913</v>
+        <v>902</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>206</v>
       </c>
       <c r="C7" t="n">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D7" t="n">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C8" t="n">
         <v>344</v>
       </c>
       <c r="D8" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D9" t="n">
-        <v>452</v>
+        <v>442</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D10" t="n">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D11" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12">
@@ -4655,7 +4655,7 @@
         <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D12" t="n">
         <v>271</v>
@@ -4672,7 +4672,7 @@
         <v>153</v>
       </c>
       <c r="D13" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D14" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" t="n">
         <v>126</v>
       </c>
       <c r="D15" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16">
@@ -4714,7 +4714,7 @@
         <v>125</v>
       </c>
       <c r="D16" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4728,7 +4728,7 @@
         <v>121</v>
       </c>
       <c r="D17" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -4739,10 +4739,10 @@
         <v>33</v>
       </c>
       <c r="C18" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" t="n">
         <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>29</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -4778,10 +4778,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -4851,10 +4851,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D4" t="n">
         <v>1429</v>
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C5" t="n">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D5" t="n">
-        <v>1227</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>235</v>
       </c>
       <c r="C6" t="n">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D6" t="n">
-        <v>934</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C7" t="n">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>138</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D10" t="n">
-        <v>451</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11">
@@ -4952,10 +4952,10 @@
         <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D11" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D12" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13">
@@ -4980,10 +4980,10 @@
         <v>41</v>
       </c>
       <c r="C13" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D13" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D15" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16">
@@ -5025,7 +5025,7 @@
         <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -5033,7 +5033,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" t="n">
         <v>121</v>
@@ -5050,10 +5050,10 @@
         <v>31</v>
       </c>
       <c r="C18" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
@@ -5064,10 +5064,10 @@
         <v>29</v>
       </c>
       <c r="C19" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>27</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C21" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5162,10 +5162,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
         <v>1254</v>
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C5" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C6" t="n">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="D6" t="n">
-        <v>957</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D7" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" t="n">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D8" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>139</v>
       </c>
       <c r="C9" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D11" t="n">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D12" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D13" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D14" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D15" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>29</v>
       </c>
       <c r="C17" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>28</v>
       </c>
       <c r="C18" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D18" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -5375,10 +5375,10 @@
         <v>27</v>
       </c>
       <c r="C19" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>25</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C21" t="n">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5476,7 +5476,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>1092</v>
@@ -5490,10 +5490,10 @@
         <v>76</v>
       </c>
       <c r="C5" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D5" t="n">
-        <v>1166</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C6" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>982</v>
+        <v>987</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C7" t="n">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="D7" t="n">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="D8" t="n">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D9" t="n">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>112</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D11" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12">
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12" t="n">
         <v>232</v>
@@ -5602,10 +5602,10 @@
         <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D13" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D14" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>135</v>
       </c>
       <c r="D15" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16">
@@ -5641,10 +5641,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D16" t="n">
         <v>142</v>
@@ -5658,10 +5658,10 @@
         <v>27</v>
       </c>
       <c r="C17" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D18" t="n">
         <v>87</v>
@@ -5686,10 +5686,10 @@
         <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5787,7 +5787,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>948</v>
@@ -5801,10 +5801,10 @@
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D5" t="n">
-        <v>1119</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C6" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D6" t="n">
-        <v>985</v>
+        <v>990</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="D7" t="n">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D8" t="n">
-        <v>557</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D9" t="n">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>113</v>
       </c>
       <c r="C10" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D10" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>87</v>
       </c>
       <c r="C11" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D11" t="n">
         <v>367</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" t="n">
         <v>242</v>
       </c>
       <c r="D12" t="n">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>45</v>
       </c>
       <c r="C13" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D13" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D14" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D15" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -5952,10 +5952,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D16" t="n">
         <v>142</v>
@@ -5969,10 +5969,10 @@
         <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
         <v>88</v>
@@ -5997,10 +5997,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
@@ -6011,10 +6011,10 @@
         <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C21" t="n">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -6098,10 +6098,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>830</v>
+        <v>821</v>
       </c>
     </row>
     <row r="5">
@@ -6112,10 +6112,10 @@
         <v>30</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" t="n">
-        <v>1049</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C6" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>981</v>
+        <v>986</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="D7" t="n">
         <v>764</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="D8" t="n">
-        <v>570</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C9" t="n">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D9" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D10" t="n">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D11" t="n">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12">
@@ -6207,10 +6207,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D12" t="n">
         <v>294</v>
@@ -6238,10 +6238,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D14" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D15" t="n">
         <v>172</v>
@@ -6280,10 +6280,10 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C21" t="n">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4">
@@ -6412,7 +6412,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>721</v>
+        <v>716</v>
       </c>
     </row>
     <row r="5">
@@ -6423,10 +6423,10 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>975</v>
+        <v>984</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>977</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D7" t="n">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C8" t="n">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="D8" t="n">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" t="n">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C10" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D10" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D11" t="n">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D12" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>227</v>
       </c>
       <c r="D13" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D14" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D15" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -6574,10 +6574,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D16" t="n">
         <v>142</v>
@@ -6594,7 +6594,7 @@
         <v>122</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -6633,10 +6633,10 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C21" t="n">
-        <v>381</v>
+        <v>339</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_growth_param_0.5.xlsx
+++ b/output/yearly_population_growth_param_0.5.xlsx
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>207</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +814,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>620</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>906</v>
+        <v>924</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D7" t="n">
-        <v>791</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="D8" t="n">
-        <v>604</v>
+        <v>627</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C9" t="n">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="D9" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C10" t="n">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="D10" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="D11" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D12" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C13" t="n">
+        <v>236</v>
+      </c>
+      <c r="D13" t="n">
         <v>237</v>
-      </c>
-      <c r="D13" t="n">
-        <v>242</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D14" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D16" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D18" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -1032,13 +1032,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C21" t="n">
-        <v>366</v>
+        <v>230</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>535</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5">
@@ -1139,7 +1139,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>837</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D6" t="n">
-        <v>939</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D7" t="n">
-        <v>799</v>
+        <v>814</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>623</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>383</v>
       </c>
       <c r="D9" t="n">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C10" t="n">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="D11" t="n">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12">
@@ -1231,10 +1231,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D12" t="n">
         <v>304</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C13" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D13" t="n">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C14" t="n">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D14" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D16" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D18" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -1329,13 +1329,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -1343,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C21" t="n">
-        <v>393</v>
+        <v>244</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4">
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>461</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5">
@@ -1450,7 +1450,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D7" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="D8" t="n">
-        <v>632</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="D9" t="n">
-        <v>497</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="D10" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="D11" t="n">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="D12" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C13" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D13" t="n">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D14" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D15" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D16" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D18" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +1640,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -1654,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C21" t="n">
-        <v>420</v>
+        <v>258</v>
       </c>
       <c r="D21" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5">
@@ -1761,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C7" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D7" t="n">
-        <v>814</v>
+        <v>830</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="D8" t="n">
-        <v>642</v>
+        <v>661</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>504</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C10" t="n">
-        <v>337</v>
+        <v>377</v>
       </c>
       <c r="D10" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C11" t="n">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="D11" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" t="n">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="D12" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D13" t="n">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D14" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D15" t="n">
         <v>173</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D16" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>134</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="C21" t="n">
-        <v>446</v>
+        <v>272</v>
       </c>
       <c r="D21" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>345</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5">
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>628</v>
+        <v>621</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>830</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>830</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D8" t="n">
-        <v>651</v>
+        <v>669</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="D9" t="n">
-        <v>516</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C10" t="n">
-        <v>308</v>
+        <v>351</v>
       </c>
       <c r="D10" t="n">
-        <v>431</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C11" t="n">
-        <v>341</v>
+        <v>376</v>
       </c>
       <c r="D11" t="n">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="n">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="D12" t="n">
         <v>314</v>
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="D13" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
         <v>241</v>
       </c>
       <c r="D14" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D15" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D16" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -2276,13 +2276,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>471</v>
+        <v>286</v>
       </c>
       <c r="D21" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>297</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5">
@@ -2383,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>570</v>
+        <v>554</v>
       </c>
     </row>
     <row r="6">
@@ -2397,7 +2397,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>786</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
-        <v>791</v>
+        <v>824</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D8" t="n">
-        <v>663</v>
+        <v>676</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>521</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C10" t="n">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>432</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C11" t="n">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="D11" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" t="n">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="D12" t="n">
         <v>313</v>
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="D13" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D14" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16">
@@ -2531,13 +2531,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D16" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -2545,13 +2545,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -2573,13 +2573,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -2587,13 +2587,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="C21" t="n">
-        <v>495</v>
+        <v>300</v>
       </c>
       <c r="D21" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5">
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>515</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6">
@@ -2705,10 +2705,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>741</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>774</v>
+        <v>813</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>672</v>
+        <v>687</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="D9" t="n">
-        <v>527</v>
+        <v>551</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D10" t="n">
-        <v>433</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C11" t="n">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="D11" t="n">
         <v>377</v>
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>324</v>
+        <v>357</v>
       </c>
       <c r="D12" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="D13" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D14" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15">
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16">
@@ -2842,13 +2842,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D16" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -2870,13 +2870,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -2898,13 +2898,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>519</v>
+        <v>314</v>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>221</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>461</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6">
@@ -3019,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>696</v>
+        <v>703</v>
       </c>
     </row>
     <row r="7">
@@ -3033,7 +3033,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>761</v>
+        <v>796</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D8" t="n">
-        <v>670</v>
+        <v>696</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D9" t="n">
-        <v>533</v>
+        <v>555</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>439</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>281</v>
+        <v>329</v>
       </c>
       <c r="D11" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C12" t="n">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="D12" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>51</v>
       </c>
       <c r="C13" t="n">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="D13" t="n">
         <v>257</v>
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="D14" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
         <v>228</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D16" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -3181,13 +3181,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -3209,13 +3209,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="C21" t="n">
-        <v>543</v>
+        <v>328</v>
       </c>
       <c r="D21" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>191</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5">
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6">
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7">
@@ -3341,10 +3341,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>744</v>
+        <v>775</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
-        <v>667</v>
+        <v>701</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D9" t="n">
-        <v>538</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>445</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C11" t="n">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="D11" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C12" t="n">
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="D12" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="D13" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14">
@@ -3436,13 +3436,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="D14" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D16" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -3495,10 +3495,10 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D18" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -3520,13 +3520,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="C21" t="n">
-        <v>566</v>
+        <v>341</v>
       </c>
       <c r="D21" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>164</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5">
@@ -3627,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>367</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6">
@@ -3641,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="7">
@@ -3652,10 +3652,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>662</v>
+        <v>703</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>547</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>446</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C11" t="n">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="D11" t="n">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C12" t="n">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="D12" t="n">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="D13" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="D14" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D15" t="n">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D16" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -3789,13 +3789,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -3803,13 +3803,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D18" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -3831,13 +3831,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="C21" t="n">
-        <v>590</v>
+        <v>354</v>
       </c>
       <c r="D21" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3918,10 +3918,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C4" t="n">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="D4" t="n">
         <v>1892</v>
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C5" t="n">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D5" t="n">
-        <v>1106</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="6">
@@ -3946,7 +3946,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C6" t="n">
         <v>493</v>
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -3980,7 +3980,7 @@
         <v>313</v>
       </c>
       <c r="D8" t="n">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9">
@@ -3991,10 +3991,10 @@
         <v>135</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D10" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D11" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" t="n">
         <v>171</v>
       </c>
       <c r="D12" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13">
@@ -4047,10 +4047,10 @@
         <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D13" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D14" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D15" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16">
@@ -4089,10 +4089,10 @@
         <v>37</v>
       </c>
       <c r="C16" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D16" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17">
@@ -4103,7 +4103,7 @@
         <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D17" t="n">
         <v>109</v>
@@ -4117,10 +4117,10 @@
         <v>35</v>
       </c>
       <c r="C18" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
@@ -4134,7 +4134,7 @@
         <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
@@ -4145,10 +4145,10 @@
         <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>330</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6">
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>569</v>
+        <v>554</v>
       </c>
     </row>
     <row r="7">
@@ -4274,10 +4274,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>691</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
         <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>655</v>
+        <v>701</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>554</v>
+        <v>569</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="D10" t="n">
-        <v>447</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="D11" t="n">
-        <v>374</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C12" t="n">
-        <v>260</v>
+        <v>315</v>
       </c>
       <c r="D12" t="n">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C13" t="n">
-        <v>289</v>
+        <v>336</v>
       </c>
       <c r="D13" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="D14" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="D15" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D16" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -4411,13 +4411,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -4425,13 +4425,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -4445,7 +4445,7 @@
         <v>124</v>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4453,13 +4453,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="C21" t="n">
-        <v>613</v>
+        <v>367</v>
       </c>
       <c r="D21" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4540,10 +4540,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C4" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D4" t="n">
         <v>1644</v>
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C5" t="n">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="D5" t="n">
-        <v>1200</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C6" t="n">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D6" t="n">
-        <v>902</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -4582,10 +4582,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C7" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D7" t="n">
         <v>615</v>
@@ -4599,10 +4599,10 @@
         <v>169</v>
       </c>
       <c r="C8" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D8" t="n">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9">
@@ -4613,10 +4613,10 @@
         <v>137</v>
       </c>
       <c r="C9" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D10" t="n">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D11" t="n">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D12" t="n">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13">
@@ -4669,10 +4669,10 @@
         <v>41</v>
       </c>
       <c r="C13" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D13" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D14" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -4697,10 +4697,10 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D15" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16">
@@ -4711,10 +4711,10 @@
         <v>35</v>
       </c>
       <c r="C16" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D16" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17">
@@ -4725,10 +4725,10 @@
         <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D17" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
@@ -4739,10 +4739,10 @@
         <v>33</v>
       </c>
       <c r="C18" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
         <v>113</v>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>29</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4851,10 +4851,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D4" t="n">
         <v>1429</v>
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C5" t="n">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="D5" t="n">
-        <v>1235</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C6" t="n">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="D6" t="n">
-        <v>926</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C7" t="n">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="D7" t="n">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D8" t="n">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C11" t="n">
         <v>250</v>
       </c>
       <c r="D11" t="n">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D12" t="n">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D13" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D14" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -5008,10 +5008,10 @@
         <v>33</v>
       </c>
       <c r="C15" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D15" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D16" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D17" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
@@ -5050,10 +5050,10 @@
         <v>31</v>
       </c>
       <c r="C18" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>27</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5165,7 +5165,7 @@
         <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
         <v>1254</v>
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C5" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C6" t="n">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="D6" t="n">
-        <v>961</v>
+        <v>977</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C7" t="n">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="D7" t="n">
-        <v>680</v>
+        <v>688</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C8" t="n">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="D8" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>139</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D9" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D10" t="n">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C11" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D11" t="n">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C12" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D12" t="n">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C13" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D13" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>31</v>
       </c>
       <c r="C15" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D15" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D16" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D17" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>25</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5451,7 +5451,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
@@ -5465,7 +5465,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4">
@@ -5479,7 +5479,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>1092</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D5" t="n">
-        <v>1172</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="D6" t="n">
-        <v>987</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C7" t="n">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C8" t="n">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D8" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C9" t="n">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D9" t="n">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C11" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D11" t="n">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C12" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D12" t="n">
-        <v>283</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D13" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D14" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -5644,10 +5644,10 @@
         <v>28</v>
       </c>
       <c r="C16" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D16" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>27</v>
       </c>
       <c r="C17" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D17" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D18" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" t="n">
         <v>114</v>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5762,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -5776,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>369</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4">
@@ -5790,7 +5790,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>948</v>
+        <v>956</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>1124</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C6" t="n">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="D6" t="n">
-        <v>990</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>756</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="D8" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C9" t="n">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="D9" t="n">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>113</v>
       </c>
       <c r="C10" t="n">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="D10" t="n">
-        <v>437</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D11" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C12" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D12" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C13" t="n">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D13" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D14" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>128</v>
       </c>
       <c r="D16" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D17" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D18" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>283</v>
+        <v>188</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -6087,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>305</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4">
@@ -6101,7 +6101,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>821</v>
+        <v>829</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>1062</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C6" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D6" t="n">
-        <v>986</v>
+        <v>997</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="D7" t="n">
-        <v>764</v>
+        <v>784</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C8" t="n">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="D8" t="n">
-        <v>578</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C9" t="n">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="D9" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>113</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="D10" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D11" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C12" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D12" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D13" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D14" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D15" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>130</v>
       </c>
       <c r="D16" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D17" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D18" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D19" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C21" t="n">
-        <v>311</v>
+        <v>202</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>984</v>
+        <v>998</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C6" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D6" t="n">
-        <v>983</v>
+        <v>993</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="D7" t="n">
-        <v>779</v>
+        <v>797</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C8" t="n">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="D8" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C9" t="n">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="D9" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C10" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="D10" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C11" t="n">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D11" t="n">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C12" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D12" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C13" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D13" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D16" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D18" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D19" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>339</v>
+        <v>216</v>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_growth_param_0.5.xlsx
+++ b/output/yearly_population_growth_param_0.5.xlsx
@@ -475,7 +475,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>719.3159999999999</v>
+        <v>359.658</v>
       </c>
     </row>
     <row r="3">
@@ -483,13 +483,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.27</v>
+        <v>11.64</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>931.422</v>
+        <v>465.711</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>383.42</v>
+        <v>147.44</v>
       </c>
       <c r="C4" t="n">
-        <v>710.985</v>
+        <v>292.215</v>
       </c>
       <c r="D4" t="n">
-        <v>2157.948</v>
+        <v>1078.974</v>
       </c>
     </row>
     <row r="5">
@@ -511,13 +511,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>318.844</v>
+        <v>122.608</v>
       </c>
       <c r="C5" t="n">
-        <v>517.08</v>
+        <v>212.52</v>
       </c>
       <c r="D5" t="n">
-        <v>949.8660000000001</v>
+        <v>474.933</v>
       </c>
     </row>
     <row r="6">
@@ -525,13 +525,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>236.106</v>
+        <v>90.79199999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>482.6079999999999</v>
+        <v>198.352</v>
       </c>
       <c r="D6" t="n">
-        <v>894.534</v>
+        <v>447.267</v>
       </c>
     </row>
     <row r="7">
@@ -539,13 +539,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>201.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>318.866</v>
+        <v>131.054</v>
       </c>
       <c r="D7" t="n">
-        <v>534.876</v>
+        <v>267.438</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>167.494</v>
+        <v>64.408</v>
       </c>
       <c r="C8" t="n">
-        <v>310.248</v>
+        <v>127.512</v>
       </c>
       <c r="D8" t="n">
-        <v>525.654</v>
+        <v>262.827</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +567,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>133.188</v>
+        <v>51.21599999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>258.54</v>
+        <v>106.26</v>
       </c>
       <c r="D9" t="n">
-        <v>433.434</v>
+        <v>216.717</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +581,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>98.88200000000001</v>
+        <v>38.024</v>
       </c>
       <c r="C10" t="n">
-        <v>275.776</v>
+        <v>113.344</v>
       </c>
       <c r="D10" t="n">
-        <v>488.766</v>
+        <v>244.383</v>
       </c>
     </row>
     <row r="11">
@@ -595,13 +595,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>64.57600000000001</v>
+        <v>24.832</v>
       </c>
       <c r="C11" t="n">
-        <v>185.287</v>
+        <v>76.15299999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>304.326</v>
+        <v>152.163</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>50.45</v>
+        <v>19.4</v>
       </c>
       <c r="C12" t="n">
-        <v>163.742</v>
+        <v>67.29799999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>267.438</v>
+        <v>133.719</v>
       </c>
     </row>
     <row r="13">
@@ -623,13 +623,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>42.378</v>
+        <v>16.296</v>
       </c>
       <c r="C13" t="n">
-        <v>133.579</v>
+        <v>54.901</v>
       </c>
       <c r="D13" t="n">
-        <v>230.55</v>
+        <v>115.275</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +637,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>40.36</v>
+        <v>15.52</v>
       </c>
       <c r="C14" t="n">
-        <v>129.27</v>
+        <v>53.13</v>
       </c>
       <c r="D14" t="n">
-        <v>202.884</v>
+        <v>101.442</v>
       </c>
     </row>
     <row r="15">
@@ -651,13 +651,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>40.36</v>
+        <v>15.52</v>
       </c>
       <c r="C15" t="n">
-        <v>129.27</v>
+        <v>53.13</v>
       </c>
       <c r="D15" t="n">
-        <v>165.996</v>
+        <v>82.998</v>
       </c>
     </row>
     <row r="16">
@@ -665,13 +665,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>38.342</v>
+        <v>14.744</v>
       </c>
       <c r="C16" t="n">
-        <v>124.961</v>
+        <v>51.35899999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>138.33</v>
+        <v>69.16500000000001</v>
       </c>
     </row>
     <row r="17">
@@ -679,13 +679,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>38.342</v>
+        <v>14.744</v>
       </c>
       <c r="C17" t="n">
-        <v>120.652</v>
+        <v>49.58799999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>110.664</v>
+        <v>55.332</v>
       </c>
     </row>
     <row r="18">
@@ -693,13 +693,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>36.324</v>
+        <v>13.968</v>
       </c>
       <c r="C18" t="n">
-        <v>116.343</v>
+        <v>47.81700000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>82.998</v>
+        <v>41.499</v>
       </c>
     </row>
     <row r="19">
@@ -707,13 +707,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>36.324</v>
+        <v>13.968</v>
       </c>
       <c r="C19" t="n">
-        <v>112.034</v>
+        <v>46.04600000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>55.332</v>
+        <v>27.666</v>
       </c>
     </row>
     <row r="20">
@@ -721,13 +721,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>32.288</v>
+        <v>12.416</v>
       </c>
       <c r="C20" t="n">
-        <v>112.034</v>
+        <v>46.04600000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>27.666</v>
+        <v>13.833</v>
       </c>
     </row>
     <row r="21">
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>30.27</v>
+        <v>11.64</v>
       </c>
       <c r="C21" t="n">
-        <v>107.725</v>
+        <v>44.275</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>46236</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>145469</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>384258</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>20929</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>83334</v>
       </c>
       <c r="D3" t="n">
-        <v>197</v>
+        <v>121736</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10384</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>43482</v>
       </c>
       <c r="D4" t="n">
-        <v>614</v>
+        <v>32348</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>4566</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>22538</v>
       </c>
       <c r="D5" t="n">
-        <v>924</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>1499</v>
       </c>
       <c r="C6" t="n">
-        <v>73</v>
+        <v>9217</v>
       </c>
       <c r="D6" t="n">
-        <v>980</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>375</v>
       </c>
       <c r="C7" t="n">
-        <v>198</v>
+        <v>2388</v>
       </c>
       <c r="D7" t="n">
-        <v>807</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -867,10 +867,10 @@
         <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>338</v>
+        <v>486</v>
       </c>
       <c r="D8" t="n">
-        <v>627</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>206</v>
       </c>
       <c r="D9" t="n">
-        <v>487</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>395</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>427</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>337</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>376</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>283</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>299</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>236</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>237</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>202</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>157</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>173</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>137</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>106</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -1032,13 +1032,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C21" t="n">
-        <v>230</v>
+        <v>135</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>47105</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>148045</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>385889</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>21435</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>84576</v>
       </c>
       <c r="D3" t="n">
-        <v>160</v>
+        <v>124361</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10594</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44279</v>
       </c>
       <c r="D4" t="n">
-        <v>525</v>
+        <v>33241</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>4682</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>22956</v>
       </c>
       <c r="D5" t="n">
-        <v>848</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>1560</v>
       </c>
       <c r="C6" t="n">
-        <v>47</v>
+        <v>9483</v>
       </c>
       <c r="D6" t="n">
-        <v>959</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>71</v>
+        <v>397</v>
       </c>
       <c r="C7" t="n">
-        <v>146</v>
+        <v>2524</v>
       </c>
       <c r="D7" t="n">
-        <v>814</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>282</v>
+        <v>524</v>
       </c>
       <c r="D8" t="n">
-        <v>645</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>383</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>499</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>429</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>356</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>373</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>299</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>304</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>240</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>201</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>173</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>138</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>106</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1329,13 +1329,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -1343,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C21" t="n">
-        <v>244</v>
+        <v>135</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>47688</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>149416</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>401636</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>21691</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>85210</v>
       </c>
       <c r="D3" t="n">
-        <v>130</v>
+        <v>126976</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10702</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44681</v>
       </c>
       <c r="D4" t="n">
-        <v>447</v>
+        <v>34152</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4741</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>23169</v>
       </c>
       <c r="D5" t="n">
-        <v>772</v>
+        <v>6679</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>1591</v>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>9617</v>
       </c>
       <c r="D6" t="n">
-        <v>930</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>408</v>
       </c>
       <c r="C7" t="n">
-        <v>106</v>
+        <v>2593</v>
       </c>
       <c r="D7" t="n">
-        <v>825</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>229</v>
+        <v>544</v>
       </c>
       <c r="D8" t="n">
-        <v>653</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>214</v>
       </c>
       <c r="D9" t="n">
-        <v>512</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>394</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>432</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>370</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>371</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>316</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>308</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>265</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>243</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>200</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>173</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>173</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>139</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>107</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +1640,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -1654,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1668,10 +1668,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C21" t="n">
-        <v>258</v>
+        <v>135</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>47968</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>153930</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>404633</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>21581</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>84804</v>
       </c>
       <c r="D3" t="n">
-        <v>105</v>
+        <v>126047</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10642</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44465</v>
       </c>
       <c r="D4" t="n">
-        <v>384</v>
+        <v>33877</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>4709</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>23033</v>
       </c>
       <c r="D5" t="n">
-        <v>694</v>
+        <v>6625</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>1579</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>9546</v>
       </c>
       <c r="D6" t="n">
-        <v>894</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39</v>
+        <v>405</v>
       </c>
       <c r="C7" t="n">
-        <v>75</v>
+        <v>2572</v>
       </c>
       <c r="D7" t="n">
-        <v>830</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>181</v>
+        <v>540</v>
       </c>
       <c r="D8" t="n">
-        <v>661</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>213</v>
       </c>
       <c r="D9" t="n">
-        <v>524</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>377</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>437</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="C11" t="n">
-        <v>377</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>370</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C12" t="n">
-        <v>332</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>311</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>279</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>246</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>199</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>183</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>173</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>140</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>108</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C21" t="n">
-        <v>272</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>49543</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>157393</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>409449</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>21471</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>84400</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>125125</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10582</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44250</v>
       </c>
       <c r="D4" t="n">
-        <v>329</v>
+        <v>33604</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4677</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>22898</v>
       </c>
       <c r="D5" t="n">
-        <v>621</v>
+        <v>6571</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>1567</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>9476</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>402</v>
       </c>
       <c r="C7" t="n">
-        <v>52</v>
+        <v>2551</v>
       </c>
       <c r="D7" t="n">
-        <v>830</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>140</v>
+        <v>536</v>
       </c>
       <c r="D8" t="n">
-        <v>669</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>536</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>157</v>
       </c>
       <c r="D10" t="n">
-        <v>442</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="C11" t="n">
-        <v>376</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>369</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n">
-        <v>345</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>314</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
-        <v>293</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>249</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>241</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>201</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>193</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>137</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>109</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -2279,10 +2279,10 @@
         <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>286</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>50986</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>164490</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>412313</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>21751</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>85129</v>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>127968</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10690</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44651</v>
       </c>
       <c r="D4" t="n">
-        <v>281</v>
+        <v>34519</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4736</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>23111</v>
       </c>
       <c r="D5" t="n">
-        <v>554</v>
+        <v>6841</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>1598</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>9610</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="C7" t="n">
-        <v>35</v>
+        <v>2620</v>
       </c>
       <c r="D7" t="n">
-        <v>824</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>106</v>
+        <v>556</v>
       </c>
       <c r="D8" t="n">
-        <v>676</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
         <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>547</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>157</v>
       </c>
       <c r="D10" t="n">
-        <v>448</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="C11" t="n">
-        <v>367</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>373</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n">
-        <v>354</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>313</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
-        <v>307</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>252</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>203</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>169</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
@@ -2531,13 +2531,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>110</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -2587,13 +2587,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>300</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>51463</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>168084</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>413369</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>21640</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>84724</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>127033</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10630</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44435</v>
       </c>
       <c r="D4" t="n">
-        <v>239</v>
+        <v>34242</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4704</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>22975</v>
       </c>
       <c r="D5" t="n">
-        <v>497</v>
+        <v>6785</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1586</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>9540</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>410</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>2599</v>
       </c>
       <c r="D7" t="n">
-        <v>813</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>78</v>
+        <v>552</v>
       </c>
       <c r="D8" t="n">
-        <v>687</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C9" t="n">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="D9" t="n">
-        <v>551</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>282</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>455</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C11" t="n">
-        <v>351</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>377</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>357</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>312</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>320</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>255</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>205</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>216</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>168</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
@@ -2842,13 +2842,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>173</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>141</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>145</v>
+        <v>51</v>
       </c>
       <c r="D17" t="n">
-        <v>111</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
@@ -2898,13 +2898,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>314</v>
+        <v>129</v>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>51763</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>171114</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>421478</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>21529</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>84321</v>
       </c>
       <c r="D3" t="n">
-        <v>43</v>
+        <v>126105</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10570</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44220</v>
       </c>
       <c r="D4" t="n">
-        <v>203</v>
+        <v>33967</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4672</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>22840</v>
       </c>
       <c r="D5" t="n">
-        <v>444</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>1574</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>9470</v>
       </c>
       <c r="D6" t="n">
-        <v>703</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>407</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>2578</v>
       </c>
       <c r="D7" t="n">
-        <v>796</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>57</v>
+        <v>548</v>
       </c>
       <c r="D8" t="n">
-        <v>696</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>140</v>
+        <v>213</v>
       </c>
       <c r="D9" t="n">
-        <v>555</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" t="n">
-        <v>246</v>
+        <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>461</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n">
-        <v>329</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>381</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="C12" t="n">
-        <v>355</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>312</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>330</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>257</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>207</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>228</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>167</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>182</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>141</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D17" t="n">
-        <v>111</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -3181,13 +3181,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -3209,13 +3209,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>328</v>
+        <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>52140</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>174523</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>429062</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>21831</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>85188</v>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>129058</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10679</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44621</v>
       </c>
       <c r="D4" t="n">
-        <v>172</v>
+        <v>34888</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4730</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>23053</v>
       </c>
       <c r="D5" t="n">
-        <v>395</v>
+        <v>7002</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1604</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>9603</v>
       </c>
       <c r="D6" t="n">
-        <v>652</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>418</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>2646</v>
       </c>
       <c r="D7" t="n">
-        <v>775</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>568</v>
       </c>
       <c r="D8" t="n">
-        <v>701</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>110</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>560</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>467</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>385</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C12" t="n">
-        <v>347</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>312</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>336</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>259</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -3436,13 +3436,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>209</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>239</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>166</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>141</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="D17" t="n">
-        <v>111</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -3492,13 +3492,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>134</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -3520,13 +3520,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>341</v>
+        <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>52350</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>177419</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>430581</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>21719</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>84782</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>128116</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10619</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44405</v>
       </c>
       <c r="D4" t="n">
-        <v>145</v>
+        <v>34609</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4698</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>22918</v>
       </c>
       <c r="D5" t="n">
-        <v>350</v>
+        <v>6945</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1592</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>9533</v>
       </c>
       <c r="D6" t="n">
-        <v>602</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>415</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2625</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>564</v>
       </c>
       <c r="D8" t="n">
-        <v>703</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>85</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>565</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>473</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>273</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>389</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>333</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>312</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>338</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>261</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>301</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>211</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>166</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>201</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>141</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -3789,13 +3789,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>162</v>
+        <v>49</v>
       </c>
       <c r="D17" t="n">
-        <v>111</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -3803,13 +3803,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -3831,13 +3831,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>354</v>
+        <v>125</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>11886</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>49272</v>
       </c>
       <c r="D2" t="n">
-        <v>477</v>
+        <v>95944</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>839</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>213</v>
+        <v>66</v>
       </c>
       <c r="C4" t="n">
-        <v>354</v>
+        <v>81</v>
       </c>
       <c r="D4" t="n">
-        <v>1892</v>
+        <v>936</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>315</v>
+        <v>138</v>
       </c>
       <c r="C5" t="n">
-        <v>595</v>
+        <v>274</v>
       </c>
       <c r="D5" t="n">
-        <v>1115</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>251</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>493</v>
+        <v>212</v>
       </c>
       <c r="D6" t="n">
-        <v>890</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>392</v>
+        <v>178</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>313</v>
+        <v>132</v>
       </c>
       <c r="D8" t="n">
-        <v>526</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>280</v>
+        <v>122</v>
       </c>
       <c r="D9" t="n">
-        <v>438</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="D10" t="n">
-        <v>483</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>313</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>269</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>231</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>206</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>164</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>136</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="D17" t="n">
-        <v>109</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="D19" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -4159,10 +4159,10 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>53334</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>178545</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>435111</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>21608</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>84378</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>127180</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>10559</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44190</v>
       </c>
       <c r="D4" t="n">
-        <v>122</v>
+        <v>34332</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4666</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>22784</v>
       </c>
       <c r="D5" t="n">
-        <v>309</v>
+        <v>6889</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1580</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>9463</v>
       </c>
       <c r="D6" t="n">
-        <v>554</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>412</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>2604</v>
       </c>
       <c r="D7" t="n">
-        <v>722</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>560</v>
       </c>
       <c r="D8" t="n">
-        <v>701</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="C9" t="n">
-        <v>64</v>
+        <v>214</v>
       </c>
       <c r="D9" t="n">
-        <v>569</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>478</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>394</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>315</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>313</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>336</v>
+        <v>95</v>
       </c>
       <c r="D13" t="n">
-        <v>263</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>310</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>213</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>261</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>166</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>211</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>141</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -4411,13 +4411,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>169</v>
+        <v>48</v>
       </c>
       <c r="D17" t="n">
-        <v>111</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
@@ -4425,13 +4425,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -4439,13 +4439,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -4453,13 +4453,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>367</v>
+        <v>123</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>9842</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>23144</v>
       </c>
       <c r="D2" t="n">
-        <v>316</v>
+        <v>134616</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>6776</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33504</v>
       </c>
       <c r="D3" t="n">
-        <v>733</v>
+        <v>22405</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>173</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>1644</v>
+        <v>831</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>251</v>
+        <v>99</v>
       </c>
       <c r="C5" t="n">
-        <v>469</v>
+        <v>149</v>
       </c>
       <c r="D5" t="n">
-        <v>1207</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>259</v>
+        <v>126</v>
       </c>
       <c r="C6" t="n">
-        <v>534</v>
+        <v>256</v>
       </c>
       <c r="D6" t="n">
-        <v>912</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>208</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>436</v>
+        <v>201</v>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>349</v>
+        <v>163</v>
       </c>
       <c r="D8" t="n">
-        <v>522</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>292</v>
+        <v>130</v>
       </c>
       <c r="D9" t="n">
-        <v>445</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v>472</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>235</v>
+        <v>107</v>
       </c>
       <c r="D11" t="n">
-        <v>329</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>186</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>268</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>232</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="D14" t="n">
-        <v>206</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>166</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>135</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -4764,13 +4764,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>12501</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>39060</v>
       </c>
       <c r="D2" t="n">
-        <v>209</v>
+        <v>156781</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>8278</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>27391</v>
       </c>
       <c r="D3" t="n">
-        <v>627</v>
+        <v>44847</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>58</v>
+        <v>3336</v>
       </c>
       <c r="C4" t="n">
-        <v>84</v>
+        <v>19778</v>
       </c>
       <c r="D4" t="n">
-        <v>1429</v>
+        <v>5145</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="C5" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="D5" t="n">
-        <v>1241</v>
+        <v>723</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>241</v>
+        <v>114</v>
       </c>
       <c r="C6" t="n">
-        <v>500</v>
+        <v>198</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>534</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>478</v>
+        <v>233</v>
       </c>
       <c r="D7" t="n">
-        <v>652</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>384</v>
+        <v>186</v>
       </c>
       <c r="D8" t="n">
-        <v>524</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>314</v>
+        <v>148</v>
       </c>
       <c r="D9" t="n">
-        <v>451</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>125</v>
       </c>
       <c r="D10" t="n">
-        <v>463</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>250</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>342</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>201</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>269</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>233</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>138</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>206</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>167</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>134</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>110</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="D19" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -5075,13 +5075,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>18937</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>85677</v>
       </c>
       <c r="D2" t="n">
-        <v>138</v>
+        <v>245217</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>10009</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33108</v>
       </c>
       <c r="D3" t="n">
-        <v>528</v>
+        <v>63875</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>5395</v>
       </c>
       <c r="C4" t="n">
-        <v>41</v>
+        <v>23706</v>
       </c>
       <c r="D4" t="n">
-        <v>1254</v>
+        <v>11945</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>122</v>
+        <v>1375</v>
       </c>
       <c r="C5" t="n">
-        <v>206</v>
+        <v>9537</v>
       </c>
       <c r="D5" t="n">
-        <v>1220</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>203</v>
+        <v>96</v>
       </c>
       <c r="C6" t="n">
-        <v>417</v>
+        <v>146</v>
       </c>
       <c r="D6" t="n">
-        <v>977</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>210</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>487</v>
+        <v>219</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>422</v>
+        <v>208</v>
       </c>
       <c r="D8" t="n">
-        <v>536</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="C9" t="n">
-        <v>344</v>
+        <v>165</v>
       </c>
       <c r="D9" t="n">
-        <v>451</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>291</v>
+        <v>135</v>
       </c>
       <c r="D10" t="n">
-        <v>456</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>259</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>352</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>216</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>271</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>234</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>206</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>168</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>133</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>110</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -5386,13 +5386,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C21" t="n">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>32258</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>114938</v>
       </c>
       <c r="D2" t="n">
-        <v>91</v>
+        <v>242970</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>12687</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>52032</v>
       </c>
       <c r="D3" t="n">
-        <v>439</v>
+        <v>85636</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>6833</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>27327</v>
       </c>
       <c r="D4" t="n">
-        <v>1097</v>
+        <v>18176</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>2540</v>
       </c>
       <c r="C5" t="n">
-        <v>125</v>
+        <v>14591</v>
       </c>
       <c r="D5" t="n">
-        <v>1176</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>162</v>
+        <v>467</v>
       </c>
       <c r="C6" t="n">
-        <v>323</v>
+        <v>3340</v>
       </c>
       <c r="D6" t="n">
-        <v>1001</v>
+        <v>678</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>193</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>457</v>
+        <v>197</v>
       </c>
       <c r="D7" t="n">
-        <v>723</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>447</v>
+        <v>211</v>
       </c>
       <c r="D8" t="n">
-        <v>551</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="C9" t="n">
-        <v>373</v>
+        <v>180</v>
       </c>
       <c r="D9" t="n">
-        <v>452</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="C10" t="n">
-        <v>310</v>
+        <v>145</v>
       </c>
       <c r="D10" t="n">
-        <v>450</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n">
-        <v>269</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>360</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>229</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>276</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>185</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
-        <v>232</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>206</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>169</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>133</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>110</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -5697,13 +5697,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>30775</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>127815</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>290123</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>16796</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>67758</v>
       </c>
       <c r="D3" t="n">
-        <v>362</v>
+        <v>99796</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8130</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>33776</v>
       </c>
       <c r="D4" t="n">
-        <v>956</v>
+        <v>24429</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>3398</v>
       </c>
       <c r="C5" t="n">
-        <v>75</v>
+        <v>17647</v>
       </c>
       <c r="D5" t="n">
-        <v>1128</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>123</v>
+        <v>886</v>
       </c>
       <c r="C6" t="n">
-        <v>234</v>
+        <v>6073</v>
       </c>
       <c r="D6" t="n">
-        <v>1003</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>921</v>
       </c>
       <c r="D7" t="n">
-        <v>756</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>450</v>
+        <v>207</v>
       </c>
       <c r="D8" t="n">
-        <v>568</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>86</v>
       </c>
       <c r="C9" t="n">
-        <v>401</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>455</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>332</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>445</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="C11" t="n">
-        <v>282</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>366</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C12" t="n">
-        <v>244</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>282</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
-        <v>197</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>231</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>206</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>170</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>134</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>109</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" t="n">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>37802</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>134131</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>350545</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>18613</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>76766</v>
       </c>
       <c r="D3" t="n">
-        <v>296</v>
+        <v>109312</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>9337</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>38873</v>
       </c>
       <c r="D4" t="n">
-        <v>829</v>
+        <v>28197</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>3965</v>
       </c>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>20242</v>
       </c>
       <c r="D5" t="n">
-        <v>1067</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>89</v>
+        <v>1187</v>
       </c>
       <c r="C6" t="n">
-        <v>163</v>
+        <v>7693</v>
       </c>
       <c r="D6" t="n">
-        <v>997</v>
+        <v>993</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>329</v>
+        <v>1642</v>
       </c>
       <c r="D7" t="n">
-        <v>784</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>429</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>588</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="C9" t="n">
-        <v>423</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>464</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>356</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>437</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>298</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>371</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>255</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>288</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>210</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>231</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>206</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>135</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" t="n">
+        <v>48</v>
+      </c>
+      <c r="D20" t="n">
         <v>20</v>
-      </c>
-      <c r="C20" t="n">
-        <v>113</v>
-      </c>
-      <c r="D20" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" t="n">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>44293</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>130851</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>375992</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>19956</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>81355</v>
       </c>
       <c r="D3" t="n">
-        <v>241</v>
+        <v>116548</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>9986</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>41904</v>
       </c>
       <c r="D4" t="n">
-        <v>716</v>
+        <v>30630</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>4341</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>21732</v>
       </c>
       <c r="D5" t="n">
-        <v>998</v>
+        <v>5651</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>1381</v>
       </c>
       <c r="C6" t="n">
-        <v>111</v>
+        <v>8696</v>
       </c>
       <c r="D6" t="n">
-        <v>993</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>117</v>
+        <v>330</v>
       </c>
       <c r="C7" t="n">
-        <v>260</v>
+        <v>2126</v>
       </c>
       <c r="D7" t="n">
-        <v>797</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="D8" t="n">
-        <v>608</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>425</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>475</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>379</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>431</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>317</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>374</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>268</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>294</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>223</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>234</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>204</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>172</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>136</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>107</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C21" t="n">
-        <v>216</v>
+        <v>134</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_growth_param_0.5.xlsx
+++ b/output/yearly_population_growth_param_0.5.xlsx
@@ -475,7 +475,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>359.658</v>
+        <v>736.788</v>
       </c>
     </row>
     <row r="3">
@@ -483,13 +483,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.64</v>
+        <v>30.93</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>465.711</v>
+        <v>954.0459999999999</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>147.44</v>
+        <v>391.78</v>
       </c>
       <c r="C4" t="n">
-        <v>292.215</v>
+        <v>695.145</v>
       </c>
       <c r="D4" t="n">
-        <v>1078.974</v>
+        <v>2210.364</v>
       </c>
     </row>
     <row r="5">
@@ -511,13 +511,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>122.608</v>
+        <v>325.796</v>
       </c>
       <c r="C5" t="n">
-        <v>212.52</v>
+        <v>505.56</v>
       </c>
       <c r="D5" t="n">
-        <v>474.933</v>
+        <v>972.938</v>
       </c>
     </row>
     <row r="6">
@@ -525,13 +525,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>90.79199999999999</v>
+        <v>241.254</v>
       </c>
       <c r="C6" t="n">
-        <v>198.352</v>
+        <v>471.856</v>
       </c>
       <c r="D6" t="n">
-        <v>447.267</v>
+        <v>916.2619999999999</v>
       </c>
     </row>
     <row r="7">
@@ -539,13 +539,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>77.59999999999999</v>
+        <v>206.2</v>
       </c>
       <c r="C7" t="n">
-        <v>131.054</v>
+        <v>311.762</v>
       </c>
       <c r="D7" t="n">
-        <v>267.438</v>
+        <v>547.8679999999999</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64.408</v>
+        <v>171.146</v>
       </c>
       <c r="C8" t="n">
-        <v>127.512</v>
+        <v>303.336</v>
       </c>
       <c r="D8" t="n">
-        <v>262.827</v>
+        <v>538.422</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +567,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51.21599999999999</v>
+        <v>136.092</v>
       </c>
       <c r="C9" t="n">
-        <v>106.26</v>
+        <v>252.78</v>
       </c>
       <c r="D9" t="n">
-        <v>216.717</v>
+        <v>443.962</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +581,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38.024</v>
+        <v>101.038</v>
       </c>
       <c r="C10" t="n">
-        <v>113.344</v>
+        <v>269.632</v>
       </c>
       <c r="D10" t="n">
-        <v>244.383</v>
+        <v>500.638</v>
       </c>
     </row>
     <row r="11">
@@ -595,13 +595,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24.832</v>
+        <v>65.98400000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>76.15299999999999</v>
+        <v>181.159</v>
       </c>
       <c r="D11" t="n">
-        <v>152.163</v>
+        <v>311.718</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19.4</v>
+        <v>51.55</v>
       </c>
       <c r="C12" t="n">
-        <v>67.29799999999999</v>
+        <v>160.094</v>
       </c>
       <c r="D12" t="n">
-        <v>133.719</v>
+        <v>273.934</v>
       </c>
     </row>
     <row r="13">
@@ -623,13 +623,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>16.296</v>
+        <v>43.302</v>
       </c>
       <c r="C13" t="n">
-        <v>54.901</v>
+        <v>130.603</v>
       </c>
       <c r="D13" t="n">
-        <v>115.275</v>
+        <v>236.15</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +637,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15.52</v>
+        <v>41.24</v>
       </c>
       <c r="C14" t="n">
-        <v>53.13</v>
+        <v>126.39</v>
       </c>
       <c r="D14" t="n">
-        <v>101.442</v>
+        <v>207.812</v>
       </c>
     </row>
     <row r="15">
@@ -651,13 +651,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15.52</v>
+        <v>41.24</v>
       </c>
       <c r="C15" t="n">
-        <v>53.13</v>
+        <v>126.39</v>
       </c>
       <c r="D15" t="n">
-        <v>82.998</v>
+        <v>170.028</v>
       </c>
     </row>
     <row r="16">
@@ -665,13 +665,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14.744</v>
+        <v>39.178</v>
       </c>
       <c r="C16" t="n">
-        <v>51.35899999999999</v>
+        <v>122.177</v>
       </c>
       <c r="D16" t="n">
-        <v>69.16500000000001</v>
+        <v>141.69</v>
       </c>
     </row>
     <row r="17">
@@ -679,13 +679,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14.744</v>
+        <v>39.178</v>
       </c>
       <c r="C17" t="n">
-        <v>49.58799999999999</v>
+        <v>117.964</v>
       </c>
       <c r="D17" t="n">
-        <v>55.332</v>
+        <v>113.352</v>
       </c>
     </row>
     <row r="18">
@@ -693,13 +693,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13.968</v>
+        <v>37.116</v>
       </c>
       <c r="C18" t="n">
-        <v>47.81700000000001</v>
+        <v>113.751</v>
       </c>
       <c r="D18" t="n">
-        <v>41.499</v>
+        <v>85.014</v>
       </c>
     </row>
     <row r="19">
@@ -707,13 +707,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13.968</v>
+        <v>37.116</v>
       </c>
       <c r="C19" t="n">
-        <v>46.04600000000001</v>
+        <v>109.538</v>
       </c>
       <c r="D19" t="n">
-        <v>27.666</v>
+        <v>56.67599999999999</v>
       </c>
     </row>
     <row r="20">
@@ -721,13 +721,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>12.416</v>
+        <v>32.992</v>
       </c>
       <c r="C20" t="n">
-        <v>46.04600000000001</v>
+        <v>109.538</v>
       </c>
       <c r="D20" t="n">
-        <v>13.833</v>
+        <v>28.338</v>
       </c>
     </row>
     <row r="21">
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.64</v>
+        <v>30.93</v>
       </c>
       <c r="C21" t="n">
-        <v>44.275</v>
+        <v>105.325</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46236</v>
+        <v>38151</v>
       </c>
       <c r="C2" t="n">
-        <v>145469</v>
+        <v>109779</v>
       </c>
       <c r="D2" t="n">
-        <v>384258</v>
+        <v>280452</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20929</v>
+        <v>19721</v>
       </c>
       <c r="C3" t="n">
-        <v>83334</v>
+        <v>70495</v>
       </c>
       <c r="D3" t="n">
-        <v>121736</v>
+        <v>72193</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10384</v>
+        <v>8253</v>
       </c>
       <c r="C4" t="n">
-        <v>43482</v>
+        <v>40131</v>
       </c>
       <c r="D4" t="n">
-        <v>32348</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4566</v>
+        <v>2166</v>
       </c>
       <c r="C5" t="n">
-        <v>22538</v>
+        <v>19333</v>
       </c>
       <c r="D5" t="n">
-        <v>6150</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1499</v>
+        <v>333</v>
       </c>
       <c r="C6" t="n">
-        <v>9217</v>
+        <v>6403</v>
       </c>
       <c r="D6" t="n">
-        <v>1201</v>
+        <v>820</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>375</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>2388</v>
+        <v>1541</v>
       </c>
       <c r="D7" t="n">
-        <v>484</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>486</v>
+        <v>550</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>206</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>321</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="D13" t="n">
-        <v>139</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>115</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="D15" t="n">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1032,13 +1032,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47105</v>
+        <v>33973</v>
       </c>
       <c r="C2" t="n">
-        <v>148045</v>
+        <v>107078</v>
       </c>
       <c r="D2" t="n">
-        <v>385889</v>
+        <v>257615</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21435</v>
+        <v>19288</v>
       </c>
       <c r="C3" t="n">
-        <v>84576</v>
+        <v>72655</v>
       </c>
       <c r="D3" t="n">
-        <v>124361</v>
+        <v>73983</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10594</v>
+        <v>8067</v>
       </c>
       <c r="C4" t="n">
-        <v>44279</v>
+        <v>44345</v>
       </c>
       <c r="D4" t="n">
-        <v>33241</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4682</v>
+        <v>2157</v>
       </c>
       <c r="C5" t="n">
-        <v>22956</v>
+        <v>21712</v>
       </c>
       <c r="D5" t="n">
-        <v>6411</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1560</v>
+        <v>309</v>
       </c>
       <c r="C6" t="n">
-        <v>9483</v>
+        <v>7628</v>
       </c>
       <c r="D6" t="n">
-        <v>1250</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>397</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>2524</v>
+        <v>1936</v>
       </c>
       <c r="D7" t="n">
-        <v>491</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>524</v>
+        <v>603</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>399</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>320</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="D13" t="n">
-        <v>139</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>115</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>139</v>
       </c>
       <c r="D15" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1329,13 +1329,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1343,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47688</v>
+        <v>28969</v>
       </c>
       <c r="C2" t="n">
-        <v>149416</v>
+        <v>181131</v>
       </c>
       <c r="D2" t="n">
-        <v>401636</v>
+        <v>275577</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21691</v>
+        <v>18436</v>
       </c>
       <c r="C3" t="n">
-        <v>85210</v>
+        <v>73849</v>
       </c>
       <c r="D3" t="n">
-        <v>126976</v>
+        <v>73263</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10702</v>
+        <v>7810</v>
       </c>
       <c r="C4" t="n">
-        <v>44681</v>
+        <v>47924</v>
       </c>
       <c r="D4" t="n">
-        <v>34152</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4741</v>
+        <v>2058</v>
       </c>
       <c r="C5" t="n">
-        <v>23169</v>
+        <v>24076</v>
       </c>
       <c r="D5" t="n">
-        <v>6679</v>
+        <v>995</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1591</v>
+        <v>286</v>
       </c>
       <c r="C6" t="n">
-        <v>9617</v>
+        <v>8902</v>
       </c>
       <c r="D6" t="n">
-        <v>1301</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>2593</v>
+        <v>2288</v>
       </c>
       <c r="D7" t="n">
-        <v>498</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>544</v>
+        <v>645</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>214</v>
+        <v>405</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="D13" t="n">
-        <v>139</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>115</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D15" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +1640,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1654,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47968</v>
+        <v>31732</v>
       </c>
       <c r="C2" t="n">
-        <v>153930</v>
+        <v>168376</v>
       </c>
       <c r="D2" t="n">
-        <v>404633</v>
+        <v>269527</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21581</v>
+        <v>17164</v>
       </c>
       <c r="C3" t="n">
-        <v>84804</v>
+        <v>82674</v>
       </c>
       <c r="D3" t="n">
-        <v>126047</v>
+        <v>72738</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10642</v>
+        <v>7339</v>
       </c>
       <c r="C4" t="n">
-        <v>44465</v>
+        <v>49913</v>
       </c>
       <c r="D4" t="n">
-        <v>33877</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4709</v>
+        <v>1865</v>
       </c>
       <c r="C5" t="n">
-        <v>23033</v>
+        <v>26095</v>
       </c>
       <c r="D5" t="n">
-        <v>6625</v>
+        <v>982</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1579</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>9546</v>
+        <v>9992</v>
       </c>
       <c r="D6" t="n">
-        <v>1292</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>2572</v>
+        <v>2568</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>540</v>
+        <v>666</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>213</v>
+        <v>403</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>312</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>250</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>188</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="D13" t="n">
-        <v>138</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>114</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1923,13 +1923,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1937,13 +1937,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1951,13 +1951,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1979,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49543</v>
+        <v>29237</v>
       </c>
       <c r="C2" t="n">
-        <v>157393</v>
+        <v>266888</v>
       </c>
       <c r="D2" t="n">
-        <v>409449</v>
+        <v>238957</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21471</v>
+        <v>16215</v>
       </c>
       <c r="C3" t="n">
-        <v>84400</v>
+        <v>88147</v>
       </c>
       <c r="D3" t="n">
-        <v>125125</v>
+        <v>69318</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10582</v>
+        <v>6743</v>
       </c>
       <c r="C4" t="n">
-        <v>44250</v>
+        <v>52334</v>
       </c>
       <c r="D4" t="n">
-        <v>33604</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4677</v>
+        <v>1693</v>
       </c>
       <c r="C5" t="n">
-        <v>22898</v>
+        <v>27860</v>
       </c>
       <c r="D5" t="n">
-        <v>6571</v>
+        <v>958</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1567</v>
+        <v>235</v>
       </c>
       <c r="C6" t="n">
-        <v>9476</v>
+        <v>11001</v>
       </c>
       <c r="D6" t="n">
-        <v>1284</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>402</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>2551</v>
+        <v>2816</v>
       </c>
       <c r="D7" t="n">
-        <v>494</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>536</v>
+        <v>661</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="D13" t="n">
-        <v>137</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="D14" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2234,13 +2234,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2248,13 +2248,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2276,13 +2276,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2290,13 +2290,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50986</v>
+        <v>30364</v>
       </c>
       <c r="C2" t="n">
-        <v>164490</v>
+        <v>218765</v>
       </c>
       <c r="D2" t="n">
-        <v>412313</v>
+        <v>213830</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21751</v>
+        <v>15176</v>
       </c>
       <c r="C3" t="n">
-        <v>85129</v>
+        <v>101780</v>
       </c>
       <c r="D3" t="n">
-        <v>127968</v>
+        <v>66085</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10690</v>
+        <v>6099</v>
       </c>
       <c r="C4" t="n">
-        <v>44651</v>
+        <v>55185</v>
       </c>
       <c r="D4" t="n">
-        <v>34519</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4736</v>
+        <v>1507</v>
       </c>
       <c r="C5" t="n">
-        <v>23111</v>
+        <v>29192</v>
       </c>
       <c r="D5" t="n">
-        <v>6841</v>
+        <v>942</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1598</v>
+        <v>211</v>
       </c>
       <c r="C6" t="n">
-        <v>9610</v>
+        <v>11635</v>
       </c>
       <c r="D6" t="n">
-        <v>1336</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>2620</v>
+        <v>2988</v>
       </c>
       <c r="D7" t="n">
-        <v>501</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>556</v>
+        <v>654</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="C9" t="n">
-        <v>215</v>
+        <v>396</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>299</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>239</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="D13" t="n">
-        <v>137</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="D14" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2531,13 +2531,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2545,13 +2545,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2573,13 +2573,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2587,13 +2587,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2601,13 +2601,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>51463</v>
+        <v>28602</v>
       </c>
       <c r="C2" t="n">
-        <v>168084</v>
+        <v>318270</v>
       </c>
       <c r="D2" t="n">
-        <v>413369</v>
+        <v>206246</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21640</v>
+        <v>14371</v>
       </c>
       <c r="C3" t="n">
-        <v>84724</v>
+        <v>109916</v>
       </c>
       <c r="D3" t="n">
-        <v>127033</v>
+        <v>62998</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10630</v>
+        <v>5524</v>
       </c>
       <c r="C4" t="n">
-        <v>44435</v>
+        <v>58062</v>
       </c>
       <c r="D4" t="n">
-        <v>34242</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4704</v>
+        <v>1342</v>
       </c>
       <c r="C5" t="n">
-        <v>22975</v>
+        <v>30611</v>
       </c>
       <c r="D5" t="n">
-        <v>6785</v>
+        <v>924</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1586</v>
+        <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>9540</v>
+        <v>12295</v>
       </c>
       <c r="D6" t="n">
-        <v>1327</v>
+        <v>704</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>410</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>2599</v>
+        <v>3175</v>
       </c>
       <c r="D7" t="n">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>552</v>
+        <v>641</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>214</v>
+        <v>392</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>231</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="D13" t="n">
-        <v>136</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="D14" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2828,13 +2828,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="D15" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2842,13 +2842,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2870,13 +2870,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2884,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2898,13 +2898,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2912,13 +2912,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>51763</v>
+        <v>25042</v>
       </c>
       <c r="C2" t="n">
-        <v>171114</v>
+        <v>286653</v>
       </c>
       <c r="D2" t="n">
-        <v>421478</v>
+        <v>188297</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21529</v>
+        <v>13435</v>
       </c>
       <c r="C3" t="n">
-        <v>84321</v>
+        <v>122539</v>
       </c>
       <c r="D3" t="n">
-        <v>126105</v>
+        <v>59446</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10570</v>
+        <v>4733</v>
       </c>
       <c r="C4" t="n">
-        <v>44220</v>
+        <v>61394</v>
       </c>
       <c r="D4" t="n">
-        <v>33967</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4672</v>
+        <v>1186</v>
       </c>
       <c r="C5" t="n">
-        <v>22840</v>
+        <v>31585</v>
       </c>
       <c r="D5" t="n">
-        <v>6730</v>
+        <v>895</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1574</v>
+        <v>169</v>
       </c>
       <c r="C6" t="n">
-        <v>9470</v>
+        <v>12699</v>
       </c>
       <c r="D6" t="n">
-        <v>1318</v>
+        <v>681</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>2578</v>
+        <v>3074</v>
       </c>
       <c r="D7" t="n">
-        <v>497</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>548</v>
+        <v>629</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>213</v>
+        <v>383</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3097,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="D13" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3125,13 +3125,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="D14" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3139,13 +3139,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="D15" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3167,13 +3167,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3181,13 +3181,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3195,13 +3195,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3209,13 +3209,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3223,13 +3223,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>52140</v>
+        <v>22272</v>
       </c>
       <c r="C2" t="n">
-        <v>174523</v>
+        <v>345535</v>
       </c>
       <c r="D2" t="n">
-        <v>429062</v>
+        <v>166150</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21831</v>
+        <v>12488</v>
       </c>
       <c r="C3" t="n">
-        <v>85188</v>
+        <v>131158</v>
       </c>
       <c r="D3" t="n">
-        <v>129058</v>
+        <v>56093</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10679</v>
+        <v>4057</v>
       </c>
       <c r="C4" t="n">
-        <v>44621</v>
+        <v>65402</v>
       </c>
       <c r="D4" t="n">
-        <v>34888</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4730</v>
+        <v>1048</v>
       </c>
       <c r="C5" t="n">
-        <v>23053</v>
+        <v>32662</v>
       </c>
       <c r="D5" t="n">
-        <v>7002</v>
+        <v>867</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1604</v>
+        <v>150</v>
       </c>
       <c r="C6" t="n">
-        <v>9603</v>
+        <v>13111</v>
       </c>
       <c r="D6" t="n">
-        <v>1372</v>
+        <v>656</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>418</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2646</v>
+        <v>2976</v>
       </c>
       <c r="D7" t="n">
-        <v>505</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
-        <v>568</v>
+        <v>618</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>216</v>
+        <v>374</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>285</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3394,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>219</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3408,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="D13" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3436,13 +3436,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="D14" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="D15" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3464,13 +3464,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3478,13 +3478,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3492,13 +3492,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3506,13 +3506,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3520,13 +3520,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3534,13 +3534,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>52350</v>
+        <v>20286</v>
       </c>
       <c r="C2" t="n">
-        <v>177419</v>
+        <v>279074</v>
       </c>
       <c r="D2" t="n">
-        <v>430581</v>
+        <v>153026</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21719</v>
+        <v>11421</v>
       </c>
       <c r="C3" t="n">
-        <v>84782</v>
+        <v>141976</v>
       </c>
       <c r="D3" t="n">
-        <v>128116</v>
+        <v>52950</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10619</v>
+        <v>3455</v>
       </c>
       <c r="C4" t="n">
-        <v>44405</v>
+        <v>69088</v>
       </c>
       <c r="D4" t="n">
-        <v>34609</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4698</v>
+        <v>917</v>
       </c>
       <c r="C5" t="n">
-        <v>22918</v>
+        <v>33553</v>
       </c>
       <c r="D5" t="n">
-        <v>6945</v>
+        <v>846</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1592</v>
+        <v>133</v>
       </c>
       <c r="C6" t="n">
-        <v>9533</v>
+        <v>13249</v>
       </c>
       <c r="D6" t="n">
-        <v>1363</v>
+        <v>622</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>2625</v>
+        <v>2859</v>
       </c>
       <c r="D7" t="n">
-        <v>503</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>564</v>
+        <v>604</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>215</v>
+        <v>365</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3705,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3719,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3733,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="D13" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3747,13 +3747,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="D14" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="D15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3775,13 +3775,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3789,13 +3789,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3803,13 +3803,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3817,13 +3817,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3831,13 +3831,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3845,13 +3845,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11886</v>
+        <v>18459</v>
       </c>
       <c r="C2" t="n">
-        <v>49272</v>
+        <v>32359</v>
       </c>
       <c r="D2" t="n">
-        <v>95944</v>
+        <v>36440</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>439</v>
+        <v>922</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>66</v>
+        <v>252</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="D4" t="n">
-        <v>936</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>138</v>
+        <v>330</v>
       </c>
       <c r="C5" t="n">
-        <v>274</v>
+        <v>583</v>
       </c>
       <c r="D5" t="n">
-        <v>619</v>
+        <v>999</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>111</v>
+        <v>251</v>
       </c>
       <c r="C6" t="n">
-        <v>212</v>
+        <v>489</v>
       </c>
       <c r="D6" t="n">
-        <v>458</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="C7" t="n">
-        <v>178</v>
+        <v>372</v>
       </c>
       <c r="D7" t="n">
-        <v>308</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="C8" t="n">
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="D8" t="n">
-        <v>266</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="C9" t="n">
-        <v>122</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>229</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="C10" t="n">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C11" t="n">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
-        <v>173</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="D12" t="n">
-        <v>137</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="D14" t="n">
-        <v>104</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="D15" t="n">
-        <v>87</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>125</v>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C18" t="n">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C19" t="n">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>187</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>53334</v>
+        <v>16335</v>
       </c>
       <c r="C2" t="n">
-        <v>178545</v>
+        <v>235849</v>
       </c>
       <c r="D2" t="n">
-        <v>435111</v>
+        <v>148260</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21608</v>
+        <v>10601</v>
       </c>
       <c r="C3" t="n">
-        <v>84378</v>
+        <v>146849</v>
       </c>
       <c r="D3" t="n">
-        <v>127180</v>
+        <v>49981</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10559</v>
+        <v>2944</v>
       </c>
       <c r="C4" t="n">
-        <v>44190</v>
+        <v>73212</v>
       </c>
       <c r="D4" t="n">
-        <v>34332</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4666</v>
+        <v>802</v>
       </c>
       <c r="C5" t="n">
-        <v>22784</v>
+        <v>34219</v>
       </c>
       <c r="D5" t="n">
-        <v>6889</v>
+        <v>816</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1580</v>
+        <v>117</v>
       </c>
       <c r="C6" t="n">
-        <v>9463</v>
+        <v>13684</v>
       </c>
       <c r="D6" t="n">
-        <v>1354</v>
+        <v>593</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>54</v>
       </c>
       <c r="C7" t="n">
-        <v>2604</v>
+        <v>2775</v>
       </c>
       <c r="D7" t="n">
-        <v>501</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>560</v>
+        <v>587</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>214</v>
+        <v>360</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>270</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>206</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4355,13 +4355,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="D14" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4383,13 +4383,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="D15" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4397,13 +4397,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4411,13 +4411,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4425,13 +4425,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4439,13 +4439,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4453,13 +4453,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4467,13 +4467,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9842</v>
+        <v>19455</v>
       </c>
       <c r="C2" t="n">
-        <v>23144</v>
+        <v>40762</v>
       </c>
       <c r="D2" t="n">
-        <v>134616</v>
+        <v>160977</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6776</v>
+        <v>5621</v>
       </c>
       <c r="C3" t="n">
-        <v>33504</v>
+        <v>12684</v>
       </c>
       <c r="D3" t="n">
-        <v>22405</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>161</v>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>207</v>
       </c>
       <c r="D4" t="n">
-        <v>831</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>99</v>
+        <v>298</v>
       </c>
       <c r="C5" t="n">
-        <v>149</v>
+        <v>498</v>
       </c>
       <c r="D5" t="n">
-        <v>688</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>126</v>
+        <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>256</v>
+        <v>524</v>
       </c>
       <c r="D6" t="n">
-        <v>498</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>207</v>
       </c>
       <c r="C7" t="n">
-        <v>201</v>
+        <v>420</v>
       </c>
       <c r="D7" t="n">
-        <v>339</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="C8" t="n">
-        <v>163</v>
+        <v>336</v>
       </c>
       <c r="D8" t="n">
-        <v>277</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="C9" t="n">
-        <v>130</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>236</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="C10" t="n">
-        <v>118</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>218</v>
       </c>
       <c r="D11" t="n">
-        <v>185</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>173</v>
       </c>
       <c r="D12" t="n">
-        <v>145</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="D14" t="n">
-        <v>107</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="D15" t="n">
-        <v>89</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C17" t="n">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -4764,13 +4764,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>159</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12501</v>
+        <v>25362</v>
       </c>
       <c r="C2" t="n">
-        <v>39060</v>
+        <v>63139</v>
       </c>
       <c r="D2" t="n">
-        <v>156781</v>
+        <v>163517</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8278</v>
+        <v>8907</v>
       </c>
       <c r="C3" t="n">
-        <v>27391</v>
+        <v>21819</v>
       </c>
       <c r="D3" t="n">
-        <v>44847</v>
+        <v>18065</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3336</v>
+        <v>1587</v>
       </c>
       <c r="C4" t="n">
-        <v>19778</v>
+        <v>5474</v>
       </c>
       <c r="D4" t="n">
-        <v>5145</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
+        <v>260</v>
       </c>
       <c r="C5" t="n">
-        <v>81</v>
+        <v>382</v>
       </c>
       <c r="D5" t="n">
-        <v>723</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>198</v>
+        <v>520</v>
       </c>
       <c r="D6" t="n">
-        <v>534</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>112</v>
+        <v>208</v>
       </c>
       <c r="C7" t="n">
-        <v>233</v>
+        <v>461</v>
       </c>
       <c r="D7" t="n">
-        <v>372</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="C8" t="n">
-        <v>186</v>
+        <v>363</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="C9" t="n">
-        <v>148</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C10" t="n">
-        <v>125</v>
+        <v>281</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>232</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="D12" t="n">
-        <v>151</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C13" t="n">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="D14" t="n">
-        <v>109</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="D15" t="n">
-        <v>91</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C17" t="n">
+        <v>121</v>
+      </c>
+      <c r="D17" t="n">
         <v>53</v>
-      </c>
-      <c r="D17" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C18" t="n">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -5075,13 +5075,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18937</v>
+        <v>38169</v>
       </c>
       <c r="C2" t="n">
-        <v>85677</v>
+        <v>84015</v>
       </c>
       <c r="D2" t="n">
-        <v>245217</v>
+        <v>253691</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10009</v>
+        <v>12159</v>
       </c>
       <c r="C3" t="n">
-        <v>33108</v>
+        <v>34583</v>
       </c>
       <c r="D3" t="n">
-        <v>63875</v>
+        <v>29556</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5395</v>
+        <v>3179</v>
       </c>
       <c r="C4" t="n">
-        <v>23706</v>
+        <v>11846</v>
       </c>
       <c r="D4" t="n">
-        <v>11945</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1375</v>
+        <v>499</v>
       </c>
       <c r="C5" t="n">
-        <v>9537</v>
+        <v>2238</v>
       </c>
       <c r="D5" t="n">
-        <v>1430</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>96</v>
+        <v>257</v>
       </c>
       <c r="C6" t="n">
-        <v>146</v>
+        <v>481</v>
       </c>
       <c r="D6" t="n">
-        <v>569</v>
+        <v>890</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>208</v>
       </c>
       <c r="C7" t="n">
-        <v>219</v>
+        <v>482</v>
       </c>
       <c r="D7" t="n">
-        <v>396</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C8" t="n">
-        <v>208</v>
+        <v>395</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="C9" t="n">
-        <v>165</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C10" t="n">
-        <v>135</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>244</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C12" t="n">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>151</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="D14" t="n">
-        <v>112</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5386,13 +5386,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32258</v>
+        <v>42630</v>
       </c>
       <c r="C2" t="n">
-        <v>114938</v>
+        <v>68620</v>
       </c>
       <c r="D2" t="n">
-        <v>242970</v>
+        <v>225505</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12687</v>
+        <v>16526</v>
       </c>
       <c r="C3" t="n">
-        <v>52032</v>
+        <v>47120</v>
       </c>
       <c r="D3" t="n">
-        <v>85636</v>
+        <v>43758</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6833</v>
+        <v>4603</v>
       </c>
       <c r="C4" t="n">
-        <v>27327</v>
+        <v>19352</v>
       </c>
       <c r="D4" t="n">
-        <v>18176</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2540</v>
+        <v>893</v>
       </c>
       <c r="C5" t="n">
-        <v>14591</v>
+        <v>5185</v>
       </c>
       <c r="D5" t="n">
-        <v>2691</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>467</v>
+        <v>278</v>
       </c>
       <c r="C6" t="n">
-        <v>3340</v>
+        <v>955</v>
       </c>
       <c r="D6" t="n">
-        <v>678</v>
+        <v>874</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="C7" t="n">
-        <v>197</v>
+        <v>486</v>
       </c>
       <c r="D7" t="n">
-        <v>415</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>211</v>
+        <v>421</v>
       </c>
       <c r="D8" t="n">
-        <v>310</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C9" t="n">
-        <v>180</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>68</v>
       </c>
       <c r="C10" t="n">
-        <v>145</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>250</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="D13" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="D14" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>125</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5697,13 +5697,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30775</v>
+        <v>41314</v>
       </c>
       <c r="C2" t="n">
-        <v>127815</v>
+        <v>65068</v>
       </c>
       <c r="D2" t="n">
-        <v>290123</v>
+        <v>214073</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16796</v>
+        <v>19790</v>
       </c>
       <c r="C3" t="n">
-        <v>67758</v>
+        <v>49327</v>
       </c>
       <c r="D3" t="n">
-        <v>99796</v>
+        <v>53795</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>8130</v>
+        <v>6188</v>
       </c>
       <c r="C4" t="n">
-        <v>33776</v>
+        <v>27399</v>
       </c>
       <c r="D4" t="n">
-        <v>24429</v>
+        <v>4599</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3398</v>
+        <v>1308</v>
       </c>
       <c r="C5" t="n">
-        <v>17647</v>
+        <v>8935</v>
       </c>
       <c r="D5" t="n">
-        <v>3929</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>886</v>
+        <v>317</v>
       </c>
       <c r="C6" t="n">
-        <v>6073</v>
+        <v>1983</v>
       </c>
       <c r="D6" t="n">
-        <v>839</v>
+        <v>865</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="C7" t="n">
-        <v>921</v>
+        <v>587</v>
       </c>
       <c r="D7" t="n">
-        <v>436</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="C8" t="n">
-        <v>207</v>
+        <v>436</v>
       </c>
       <c r="D8" t="n">
-        <v>318</v>
+        <v>544</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
-        <v>188</v>
+        <v>355</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>258</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="D13" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="D14" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="D15" t="n">
-        <v>95</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37802</v>
+        <v>38477</v>
       </c>
       <c r="C2" t="n">
-        <v>134131</v>
+        <v>141530</v>
       </c>
       <c r="D2" t="n">
-        <v>350545</v>
+        <v>257131</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18613</v>
+        <v>20935</v>
       </c>
       <c r="C3" t="n">
-        <v>76766</v>
+        <v>49664</v>
       </c>
       <c r="D3" t="n">
-        <v>109312</v>
+        <v>61962</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>9337</v>
+        <v>7558</v>
       </c>
       <c r="C4" t="n">
-        <v>38873</v>
+        <v>32775</v>
       </c>
       <c r="D4" t="n">
-        <v>28197</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3965</v>
+        <v>1728</v>
       </c>
       <c r="C5" t="n">
-        <v>20242</v>
+        <v>13089</v>
       </c>
       <c r="D5" t="n">
-        <v>4954</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1187</v>
+        <v>359</v>
       </c>
       <c r="C6" t="n">
-        <v>7693</v>
+        <v>3414</v>
       </c>
       <c r="D6" t="n">
-        <v>993</v>
+        <v>855</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>195</v>
       </c>
       <c r="C7" t="n">
-        <v>1642</v>
+        <v>825</v>
       </c>
       <c r="D7" t="n">
-        <v>456</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="C8" t="n">
-        <v>309</v>
+        <v>460</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>190</v>
+        <v>367</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>267</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>203</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="D13" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="D14" t="n">
-        <v>115</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="D15" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44293</v>
+        <v>31205</v>
       </c>
       <c r="C2" t="n">
-        <v>130851</v>
+        <v>118036</v>
       </c>
       <c r="D2" t="n">
-        <v>375992</v>
+        <v>287760</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19956</v>
+        <v>20929</v>
       </c>
       <c r="C3" t="n">
-        <v>81355</v>
+        <v>64362</v>
       </c>
       <c r="D3" t="n">
-        <v>116548</v>
+        <v>67839</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>9986</v>
+        <v>8129</v>
       </c>
       <c r="C4" t="n">
-        <v>41904</v>
+        <v>35974</v>
       </c>
       <c r="D4" t="n">
-        <v>30630</v>
+        <v>4215</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4341</v>
+        <v>2034</v>
       </c>
       <c r="C5" t="n">
-        <v>21732</v>
+        <v>16533</v>
       </c>
       <c r="D5" t="n">
-        <v>5651</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1381</v>
+        <v>355</v>
       </c>
       <c r="C6" t="n">
-        <v>8696</v>
+        <v>4921</v>
       </c>
       <c r="D6" t="n">
-        <v>1111</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>330</v>
+        <v>185</v>
       </c>
       <c r="C7" t="n">
-        <v>2126</v>
+        <v>1162</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>418</v>
+        <v>500</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>376</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>317</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="D13" t="n">
-        <v>138</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>115</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
+        <v>22</v>
+      </c>
+      <c r="C15" t="n">
+        <v>141</v>
+      </c>
+      <c r="D15" t="n">
         <v>15</v>
-      </c>
-      <c r="C15" t="n">
-        <v>65</v>
-      </c>
-      <c r="D15" t="n">
-        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_growth_param_0.5.xlsx
+++ b/output/yearly_population_growth_param_0.5.xlsx
@@ -27,6 +27,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_17" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_18" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_19" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="year_20" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,13 +470,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>12.728</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="D2" t="n">
-        <v>552.63</v>
+        <v>52084.648</v>
       </c>
     </row>
     <row r="3">
@@ -483,13 +484,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>71.38500000000001</v>
+        <v>71.55199999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="D3" t="n">
-        <v>715.585</v>
+        <v>27071.352</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +498,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>904.21</v>
+        <v>80.84</v>
       </c>
       <c r="C4" t="n">
-        <v>2285.25</v>
+        <v>251</v>
       </c>
       <c r="D4" t="n">
-        <v>1657.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -511,13 +512,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>751.922</v>
+        <v>51.256</v>
       </c>
       <c r="C5" t="n">
-        <v>1662</v>
+        <v>109</v>
       </c>
       <c r="D5" t="n">
-        <v>729.755</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -525,13 +526,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>556.803</v>
+        <v>39.904</v>
       </c>
       <c r="C6" t="n">
-        <v>1551.2</v>
+        <v>82</v>
       </c>
       <c r="D6" t="n">
-        <v>687.245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -539,13 +540,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>475.9</v>
+        <v>28.552</v>
       </c>
       <c r="C7" t="n">
-        <v>1024.9</v>
+        <v>54</v>
       </c>
       <c r="D7" t="n">
-        <v>410.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +554,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>394.9970000000001</v>
+        <v>21.672</v>
       </c>
       <c r="C8" t="n">
-        <v>997.2</v>
+        <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>403.845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +568,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>314.094</v>
+        <v>14.792</v>
       </c>
       <c r="C9" t="n">
-        <v>831</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>332.995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +582,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>233.191</v>
+        <v>8.256</v>
       </c>
       <c r="C10" t="n">
-        <v>886.4</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>375.505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -595,13 +596,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>152.288</v>
+        <v>1.376</v>
       </c>
       <c r="C11" t="n">
-        <v>595.55</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>233.805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +610,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>118.975</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>526.3</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>205.465</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -623,13 +624,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>99.93899999999999</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>429.35</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>177.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +638,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>95.18000000000001</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>415.5</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>155.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -651,13 +652,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>95.18000000000001</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>415.5</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>127.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -665,13 +666,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>90.42100000000001</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>401.65</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>106.275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -679,13 +680,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>90.42100000000001</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>387.8</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>85.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -693,13 +694,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>85.66200000000001</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>373.95</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>63.765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -707,13 +708,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>85.66200000000001</v>
+        <v>2.064</v>
       </c>
       <c r="C19" t="n">
-        <v>360.1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>42.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -721,13 +722,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.14400000000001</v>
+        <v>4.472</v>
       </c>
       <c r="C20" t="n">
-        <v>360.1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>21.255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -735,10 +736,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>71.38500000000001</v>
+        <v>6.88</v>
       </c>
       <c r="C21" t="n">
-        <v>346.25</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +781,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>111539</v>
+        <v>3461</v>
       </c>
       <c r="C2" t="n">
-        <v>683773</v>
+        <v>309</v>
       </c>
       <c r="D2" t="n">
-        <v>548012</v>
+        <v>22235</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>178</v>
+        <v>1803</v>
       </c>
       <c r="C3" t="n">
-        <v>532</v>
+        <v>275</v>
       </c>
       <c r="D3" t="n">
-        <v>1005</v>
+        <v>19666</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +809,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>323</v>
+        <v>1141</v>
       </c>
       <c r="C4" t="n">
-        <v>1658</v>
+        <v>228</v>
       </c>
       <c r="D4" t="n">
-        <v>980</v>
+        <v>6909</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +823,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>361</v>
+        <v>739</v>
       </c>
       <c r="C5" t="n">
-        <v>1311</v>
+        <v>178</v>
       </c>
       <c r="D5" t="n">
-        <v>586</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>267</v>
+        <v>478</v>
       </c>
       <c r="C6" t="n">
-        <v>1205</v>
+        <v>139</v>
       </c>
       <c r="D6" t="n">
-        <v>499</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +851,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>194</v>
+        <v>277</v>
       </c>
       <c r="C7" t="n">
-        <v>941</v>
+        <v>95</v>
       </c>
       <c r="D7" t="n">
-        <v>389</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +865,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>838</v>
+        <v>62</v>
       </c>
       <c r="D8" t="n">
-        <v>317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +879,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>709</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +893,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>567</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +907,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>452</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +921,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +935,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +949,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +963,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -976,10 +977,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -990,10 +991,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1007,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1021,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1035,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1046,7 +1047,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1091,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>96067</v>
+        <v>3824</v>
       </c>
       <c r="C2" t="n">
-        <v>638894</v>
+        <v>256</v>
       </c>
       <c r="D2" t="n">
-        <v>515164</v>
+        <v>19845</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1106,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>168</v>
+        <v>2127</v>
       </c>
       <c r="C3" t="n">
-        <v>564</v>
+        <v>261</v>
       </c>
       <c r="D3" t="n">
-        <v>1001</v>
+        <v>18835</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1120,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>293</v>
+        <v>1252</v>
       </c>
       <c r="C4" t="n">
-        <v>1603</v>
+        <v>227</v>
       </c>
       <c r="D4" t="n">
-        <v>934</v>
+        <v>7122</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1134,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>332</v>
+        <v>832</v>
       </c>
       <c r="C5" t="n">
-        <v>1277</v>
+        <v>177</v>
       </c>
       <c r="D5" t="n">
-        <v>571</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1148,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>242</v>
+        <v>554</v>
       </c>
       <c r="C6" t="n">
-        <v>1178</v>
+        <v>142</v>
       </c>
       <c r="D6" t="n">
-        <v>488</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1162,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>342</v>
       </c>
       <c r="C7" t="n">
-        <v>928</v>
+        <v>98</v>
       </c>
       <c r="D7" t="n">
-        <v>377</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1176,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>819</v>
+        <v>65</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1190,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>686</v>
+        <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1204,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>546</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1218,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>442</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1232,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1246,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1260,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1274,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1288,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1304,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1318,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1332,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1346,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1402,13 +1403,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>78444</v>
+        <v>4171</v>
       </c>
       <c r="C2" t="n">
-        <v>774266</v>
+        <v>296</v>
       </c>
       <c r="D2" t="n">
-        <v>561087</v>
+        <v>20729</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1417,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>158</v>
+        <v>2373</v>
       </c>
       <c r="C3" t="n">
-        <v>592</v>
+        <v>244</v>
       </c>
       <c r="D3" t="n">
-        <v>993</v>
+        <v>17993</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1431,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>267</v>
+        <v>1412</v>
       </c>
       <c r="C4" t="n">
-        <v>1550</v>
+        <v>224</v>
       </c>
       <c r="D4" t="n">
-        <v>892</v>
+        <v>7355</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1445,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>304</v>
+        <v>907</v>
       </c>
       <c r="C5" t="n">
-        <v>1244</v>
+        <v>176</v>
       </c>
       <c r="D5" t="n">
-        <v>557</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1459,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>218</v>
+        <v>632</v>
       </c>
       <c r="C6" t="n">
-        <v>1153</v>
+        <v>143</v>
       </c>
       <c r="D6" t="n">
-        <v>477</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1473,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>152</v>
+        <v>399</v>
       </c>
       <c r="C7" t="n">
-        <v>914</v>
+        <v>102</v>
       </c>
       <c r="D7" t="n">
-        <v>364</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1487,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>228</v>
       </c>
       <c r="C8" t="n">
-        <v>800</v>
+        <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1501,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C9" t="n">
-        <v>663</v>
+        <v>42</v>
       </c>
       <c r="D9" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1515,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>527</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1529,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>433</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1543,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1557,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1571,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1585,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1599,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1615,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1629,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1643,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1657,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1713,13 +1714,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>73808</v>
+        <v>4712</v>
       </c>
       <c r="C2" t="n">
-        <v>725950</v>
+        <v>246</v>
       </c>
       <c r="D2" t="n">
-        <v>570271</v>
+        <v>20244</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1728,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>148</v>
+        <v>2574</v>
       </c>
       <c r="C3" t="n">
-        <v>616</v>
+        <v>234</v>
       </c>
       <c r="D3" t="n">
-        <v>982</v>
+        <v>17252</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1742,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>243</v>
+        <v>1558</v>
       </c>
       <c r="C4" t="n">
-        <v>1500</v>
+        <v>219</v>
       </c>
       <c r="D4" t="n">
-        <v>854</v>
+        <v>7367</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1756,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>278</v>
+        <v>996</v>
       </c>
       <c r="C5" t="n">
-        <v>1212</v>
+        <v>174</v>
       </c>
       <c r="D5" t="n">
-        <v>544</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1770,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>196</v>
+        <v>697</v>
       </c>
       <c r="C6" t="n">
-        <v>1129</v>
+        <v>143</v>
       </c>
       <c r="D6" t="n">
-        <v>465</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1784,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
+        <v>454</v>
       </c>
       <c r="C7" t="n">
-        <v>900</v>
+        <v>105</v>
       </c>
       <c r="D7" t="n">
-        <v>349</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1798,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>271</v>
       </c>
       <c r="C8" t="n">
-        <v>780</v>
+        <v>69</v>
       </c>
       <c r="D8" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1812,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>142</v>
       </c>
       <c r="C9" t="n">
-        <v>641</v>
+        <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1826,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>510</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1840,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>425</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1854,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>410</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1868,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1882,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1896,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1912,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1926,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1940,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1954,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1968,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2024,13 +2025,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>61594</v>
+        <v>4975</v>
       </c>
       <c r="C2" t="n">
-        <v>918377</v>
+        <v>291</v>
       </c>
       <c r="D2" t="n">
-        <v>513784</v>
+        <v>17576</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2039,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>138</v>
+        <v>2807</v>
       </c>
       <c r="C3" t="n">
-        <v>637</v>
+        <v>221</v>
       </c>
       <c r="D3" t="n">
-        <v>969</v>
+        <v>16550</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2053,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>221</v>
+        <v>1678</v>
       </c>
       <c r="C4" t="n">
-        <v>1452</v>
+        <v>211</v>
       </c>
       <c r="D4" t="n">
-        <v>819</v>
+        <v>7357</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2067,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>254</v>
+        <v>1084</v>
       </c>
       <c r="C5" t="n">
-        <v>1182</v>
+        <v>173</v>
       </c>
       <c r="D5" t="n">
-        <v>531</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2081,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>176</v>
+        <v>752</v>
       </c>
       <c r="C6" t="n">
-        <v>1106</v>
+        <v>143</v>
       </c>
       <c r="D6" t="n">
-        <v>452</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2095,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>508</v>
       </c>
       <c r="C7" t="n">
-        <v>885</v>
+        <v>106</v>
       </c>
       <c r="D7" t="n">
-        <v>334</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2109,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="C8" t="n">
-        <v>760</v>
+        <v>72</v>
       </c>
       <c r="D8" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2123,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="C9" t="n">
-        <v>620</v>
+        <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2137,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="C10" t="n">
-        <v>494</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2151,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>417</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2165,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>406</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2179,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2193,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2210,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -2223,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2237,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2251,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2265,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2279,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2335,13 +2336,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>54992</v>
+        <v>5348</v>
       </c>
       <c r="C2" t="n">
-        <v>806418</v>
+        <v>227</v>
       </c>
       <c r="D2" t="n">
-        <v>468221</v>
+        <v>15618</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2350,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>128</v>
+        <v>2979</v>
       </c>
       <c r="C3" t="n">
-        <v>655</v>
+        <v>214</v>
       </c>
       <c r="D3" t="n">
-        <v>954</v>
+        <v>15833</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2364,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>201</v>
+        <v>1799</v>
       </c>
       <c r="C4" t="n">
-        <v>1406</v>
+        <v>203</v>
       </c>
       <c r="D4" t="n">
-        <v>786</v>
+        <v>7327</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2378,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>231</v>
+        <v>1165</v>
       </c>
       <c r="C5" t="n">
-        <v>1153</v>
+        <v>170</v>
       </c>
       <c r="D5" t="n">
-        <v>518</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2392,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>157</v>
+        <v>809</v>
       </c>
       <c r="C6" t="n">
-        <v>1083</v>
+        <v>144</v>
       </c>
       <c r="D6" t="n">
-        <v>438</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2406,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>104</v>
+        <v>555</v>
       </c>
       <c r="C7" t="n">
-        <v>869</v>
+        <v>107</v>
       </c>
       <c r="D7" t="n">
-        <v>318</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2420,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>347</v>
       </c>
       <c r="C8" t="n">
-        <v>740</v>
+        <v>73</v>
       </c>
       <c r="D8" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2434,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>199</v>
       </c>
       <c r="C9" t="n">
-        <v>599</v>
+        <v>47</v>
       </c>
       <c r="D9" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2448,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C10" t="n">
-        <v>480</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2462,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>410</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2476,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>402</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2490,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2503,10 +2504,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -2517,10 +2518,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -2534,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2548,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2562,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2576,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2646,13 +2647,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44952</v>
+        <v>5503</v>
       </c>
       <c r="C2" t="n">
-        <v>982284</v>
+        <v>255</v>
       </c>
       <c r="D2" t="n">
-        <v>463603</v>
+        <v>15282</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2661,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>119</v>
+        <v>3147</v>
       </c>
       <c r="C3" t="n">
-        <v>670</v>
+        <v>202</v>
       </c>
       <c r="D3" t="n">
-        <v>937</v>
+        <v>15118</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2675,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>183</v>
+        <v>1899</v>
       </c>
       <c r="C4" t="n">
-        <v>1362</v>
+        <v>197</v>
       </c>
       <c r="D4" t="n">
-        <v>756</v>
+        <v>7278</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2689,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>210</v>
+        <v>1242</v>
       </c>
       <c r="C5" t="n">
-        <v>1125</v>
+        <v>166</v>
       </c>
       <c r="D5" t="n">
-        <v>504</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2703,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>140</v>
+        <v>863</v>
       </c>
       <c r="C6" t="n">
-        <v>1061</v>
+        <v>143</v>
       </c>
       <c r="D6" t="n">
-        <v>423</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2717,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>598</v>
       </c>
       <c r="C7" t="n">
-        <v>853</v>
+        <v>109</v>
       </c>
       <c r="D7" t="n">
-        <v>302</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2731,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>381</v>
       </c>
       <c r="C8" t="n">
-        <v>720</v>
+        <v>74</v>
       </c>
       <c r="D8" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2745,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
+        <v>225</v>
+      </c>
+      <c r="C9" t="n">
         <v>48</v>
       </c>
-      <c r="C9" t="n">
-        <v>580</v>
-      </c>
       <c r="D9" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2759,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="C10" t="n">
-        <v>467</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2773,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>404</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2786,13 +2787,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>398</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2801,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2814,10 +2815,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -2828,10 +2829,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -2845,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2859,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2873,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2887,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2957,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31523</v>
+        <v>5505</v>
       </c>
       <c r="C2" t="n">
-        <v>911305</v>
+        <v>212</v>
       </c>
       <c r="D2" t="n">
-        <v>433520</v>
+        <v>14066</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2972,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>110</v>
+        <v>3249</v>
       </c>
       <c r="C3" t="n">
-        <v>682</v>
+        <v>194</v>
       </c>
       <c r="D3" t="n">
-        <v>919</v>
+        <v>14444</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2986,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>167</v>
+        <v>1985</v>
       </c>
       <c r="C4" t="n">
-        <v>1320</v>
+        <v>189</v>
       </c>
       <c r="D4" t="n">
-        <v>728</v>
+        <v>7212</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +3000,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>190</v>
+        <v>1309</v>
       </c>
       <c r="C5" t="n">
-        <v>1098</v>
+        <v>163</v>
       </c>
       <c r="D5" t="n">
-        <v>490</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3014,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>125</v>
+        <v>913</v>
       </c>
       <c r="C6" t="n">
-        <v>1040</v>
+        <v>141</v>
       </c>
       <c r="D6" t="n">
-        <v>407</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3028,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81</v>
+        <v>637</v>
       </c>
       <c r="C7" t="n">
-        <v>837</v>
+        <v>109</v>
       </c>
       <c r="D7" t="n">
-        <v>285</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3042,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>411</v>
       </c>
       <c r="C8" t="n">
-        <v>700</v>
+        <v>76</v>
       </c>
       <c r="D8" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3056,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>248</v>
       </c>
       <c r="C9" t="n">
-        <v>562</v>
+        <v>49</v>
       </c>
       <c r="D9" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3070,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="C10" t="n">
-        <v>455</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3084,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C11" t="n">
-        <v>398</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3097,13 +3098,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>393</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3111,10 +3112,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -3125,10 +3126,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -3139,10 +3140,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3156,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3170,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3184,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3198,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3268,13 +3269,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19863</v>
+        <v>5535</v>
       </c>
       <c r="C2" t="n">
-        <v>1005974</v>
+        <v>214</v>
       </c>
       <c r="D2" t="n">
-        <v>387791</v>
+        <v>12373</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3283,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>101</v>
+        <v>3275</v>
       </c>
       <c r="C3" t="n">
-        <v>692</v>
+        <v>184</v>
       </c>
       <c r="D3" t="n">
-        <v>901</v>
+        <v>13787</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3297,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>152</v>
+        <v>2041</v>
       </c>
       <c r="C4" t="n">
-        <v>1279</v>
+        <v>181</v>
       </c>
       <c r="D4" t="n">
-        <v>701</v>
+        <v>7201</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3311,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>172</v>
+        <v>1366</v>
       </c>
       <c r="C5" t="n">
-        <v>1072</v>
+        <v>158</v>
       </c>
       <c r="D5" t="n">
-        <v>476</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3325,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>111</v>
+        <v>958</v>
       </c>
       <c r="C6" t="n">
-        <v>1019</v>
+        <v>139</v>
       </c>
       <c r="D6" t="n">
-        <v>391</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3339,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>665</v>
       </c>
       <c r="C7" t="n">
-        <v>820</v>
+        <v>110</v>
       </c>
       <c r="D7" t="n">
-        <v>268</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3353,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>439</v>
       </c>
       <c r="C8" t="n">
-        <v>680</v>
+        <v>77</v>
       </c>
       <c r="D8" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3367,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>270</v>
       </c>
       <c r="C9" t="n">
-        <v>544</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3381,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="C10" t="n">
-        <v>444</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3395,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="C11" t="n">
-        <v>393</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3408,13 +3409,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>388</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3422,10 +3423,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -3436,10 +3437,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -3450,10 +3451,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3467,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3481,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3495,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3509,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3579,13 +3580,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9111</v>
+        <v>5608</v>
       </c>
       <c r="C2" t="n">
-        <v>860847</v>
+        <v>165</v>
       </c>
       <c r="D2" t="n">
-        <v>365851</v>
+        <v>11802</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3594,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>93</v>
+        <v>3265</v>
       </c>
       <c r="C3" t="n">
-        <v>700</v>
+        <v>176</v>
       </c>
       <c r="D3" t="n">
-        <v>882</v>
+        <v>13168</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3608,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>138</v>
+        <v>2061</v>
       </c>
       <c r="C4" t="n">
-        <v>1240</v>
+        <v>174</v>
       </c>
       <c r="D4" t="n">
-        <v>676</v>
+        <v>7039</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3622,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>155</v>
+        <v>1395</v>
       </c>
       <c r="C5" t="n">
-        <v>1047</v>
+        <v>153</v>
       </c>
       <c r="D5" t="n">
-        <v>461</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3636,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>99</v>
+        <v>999</v>
       </c>
       <c r="C6" t="n">
-        <v>999</v>
+        <v>138</v>
       </c>
       <c r="D6" t="n">
-        <v>374</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3650,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>693</v>
       </c>
       <c r="C7" t="n">
-        <v>803</v>
+        <v>110</v>
       </c>
       <c r="D7" t="n">
-        <v>250</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3664,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>463</v>
       </c>
       <c r="C8" t="n">
-        <v>661</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3678,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="C9" t="n">
-        <v>528</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3692,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>168</v>
       </c>
       <c r="C10" t="n">
-        <v>434</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3705,13 +3706,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="C11" t="n">
-        <v>388</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3719,13 +3720,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C12" t="n">
-        <v>383</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3733,10 +3734,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -3747,10 +3748,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -3761,10 +3762,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3778,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3792,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3806,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3820,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3890,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9660</v>
+        <v>915</v>
       </c>
       <c r="C2" t="n">
-        <v>19623</v>
+        <v>380</v>
       </c>
       <c r="D2" t="n">
-        <v>165792</v>
+        <v>41866</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3905,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>87</v>
+        <v>235</v>
       </c>
       <c r="D3" t="n">
-        <v>795</v>
+        <v>26772</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3919,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>791</v>
+        <v>64</v>
       </c>
       <c r="C4" t="n">
-        <v>2201</v>
+        <v>249</v>
       </c>
       <c r="D4" t="n">
-        <v>1546</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3933,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>691</v>
+        <v>63</v>
       </c>
       <c r="C5" t="n">
-        <v>1621</v>
+        <v>134</v>
       </c>
       <c r="D5" t="n">
-        <v>723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3947,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>519</v>
+        <v>45</v>
       </c>
       <c r="C6" t="n">
-        <v>1499</v>
+        <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3961,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="C7" t="n">
-        <v>1021</v>
+        <v>58</v>
       </c>
       <c r="D7" t="n">
-        <v>416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3975,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>360</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>973</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3989,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>276</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>839</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4003,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>195</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>834</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4017,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>576</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4031,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4045,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>426</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4059,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4073,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4087,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4101,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4115,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4129,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4143,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4156,7 +4157,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -4201,13 +4202,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>5526</v>
       </c>
       <c r="C2" t="n">
-        <v>746480</v>
+        <v>131</v>
       </c>
       <c r="D2" t="n">
-        <v>364266</v>
+        <v>11988</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4216,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>85</v>
+        <v>3259</v>
       </c>
       <c r="C3" t="n">
-        <v>706</v>
+        <v>165</v>
       </c>
       <c r="D3" t="n">
-        <v>862</v>
+        <v>12577</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4230,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>125</v>
+        <v>2060</v>
       </c>
       <c r="C4" t="n">
-        <v>1203</v>
+        <v>168</v>
       </c>
       <c r="D4" t="n">
-        <v>652</v>
+        <v>6875</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4244,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>140</v>
+        <v>1427</v>
       </c>
       <c r="C5" t="n">
-        <v>1023</v>
+        <v>148</v>
       </c>
       <c r="D5" t="n">
-        <v>446</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4258,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>88</v>
+        <v>1018</v>
       </c>
       <c r="C6" t="n">
-        <v>979</v>
+        <v>136</v>
       </c>
       <c r="D6" t="n">
-        <v>356</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4272,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>720</v>
       </c>
       <c r="C7" t="n">
-        <v>785</v>
+        <v>109</v>
       </c>
       <c r="D7" t="n">
-        <v>232</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4286,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>485</v>
       </c>
       <c r="C8" t="n">
-        <v>642</v>
+        <v>79</v>
       </c>
       <c r="D8" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4300,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>309</v>
       </c>
       <c r="C9" t="n">
-        <v>513</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4314,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="C10" t="n">
-        <v>425</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4327,13 +4328,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C11" t="n">
-        <v>383</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4341,13 +4342,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="C12" t="n">
-        <v>377</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4355,10 +4356,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -4369,10 +4370,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -4383,10 +4384,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -4400,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4414,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -4428,7 +4429,318 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Branching</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Foliose</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>5561</v>
+      </c>
+      <c r="C2" t="n">
+        <v>118</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12918</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3220</v>
+      </c>
+      <c r="C3" t="n">
+        <v>154</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12024</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2048</v>
+      </c>
+      <c r="C4" t="n">
+        <v>161</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6709</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1432</v>
+      </c>
+      <c r="C5" t="n">
+        <v>143</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1048</v>
+      </c>
+      <c r="C6" t="n">
+        <v>133</v>
+      </c>
+      <c r="D6" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>740</v>
+      </c>
+      <c r="C7" t="n">
+        <v>110</v>
+      </c>
+      <c r="D7" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>504</v>
+      </c>
+      <c r="C8" t="n">
+        <v>79</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>325</v>
+      </c>
+      <c r="C9" t="n">
+        <v>51</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>195</v>
+      </c>
+      <c r="C10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>107</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
         <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>53</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>23</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -4512,13 +4824,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31288</v>
+        <v>1014</v>
       </c>
       <c r="C2" t="n">
-        <v>203478</v>
+        <v>372</v>
       </c>
       <c r="D2" t="n">
-        <v>368007</v>
+        <v>38843</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4838,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>163</v>
+        <v>525</v>
       </c>
       <c r="C3" t="n">
-        <v>166</v>
+        <v>242</v>
       </c>
       <c r="D3" t="n">
-        <v>858</v>
+        <v>26090</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4852,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>696</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>2121</v>
+        <v>236</v>
       </c>
       <c r="D4" t="n">
-        <v>1447</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4866,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>637</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>1580</v>
+        <v>153</v>
       </c>
       <c r="D5" t="n">
-        <v>710</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4880,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>483</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
-        <v>1451</v>
+        <v>93</v>
       </c>
       <c r="D6" t="n">
-        <v>611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4894,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>402</v>
+        <v>38</v>
       </c>
       <c r="C7" t="n">
-        <v>1014</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
-        <v>417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4908,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>325</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>954</v>
+        <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4922,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>837</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4936,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>788</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4950,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>557</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4964,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4978,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4992,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +5006,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +5020,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +5034,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +5048,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +5062,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4764,10 +5076,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4778,7 +5090,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -4823,13 +5135,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>63924</v>
+        <v>1173</v>
       </c>
       <c r="C2" t="n">
-        <v>398359</v>
+        <v>451</v>
       </c>
       <c r="D2" t="n">
-        <v>369562</v>
+        <v>32087</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +5149,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>185</v>
+        <v>694</v>
       </c>
       <c r="C3" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D3" t="n">
-        <v>907</v>
+        <v>25347</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +5163,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>616</v>
+        <v>313</v>
       </c>
       <c r="C4" t="n">
-        <v>2045</v>
+        <v>230</v>
       </c>
       <c r="D4" t="n">
-        <v>1359</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +5177,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>587</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>1539</v>
+        <v>164</v>
       </c>
       <c r="D5" t="n">
-        <v>693</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +5191,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>448</v>
+        <v>51</v>
       </c>
       <c r="C6" t="n">
-        <v>1407</v>
+        <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>584</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +5205,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>368</v>
+        <v>44</v>
       </c>
       <c r="C7" t="n">
-        <v>1006</v>
+        <v>66</v>
       </c>
       <c r="D7" t="n">
-        <v>418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +5219,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>291</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>937</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +5233,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>206</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>828</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +5247,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>746</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +5261,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>104</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>538</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +5275,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +5289,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +5303,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5317,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5331,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5345,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5359,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5373,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>406</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5075,10 +5387,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5089,7 +5401,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -5134,13 +5446,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>112418</v>
+        <v>1546</v>
       </c>
       <c r="C2" t="n">
-        <v>580368</v>
+        <v>514</v>
       </c>
       <c r="D2" t="n">
-        <v>493935</v>
+        <v>31700</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5460,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>196</v>
+        <v>820</v>
       </c>
       <c r="C3" t="n">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="D3" t="n">
-        <v>944</v>
+        <v>24399</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5474,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>548</v>
+        <v>486</v>
       </c>
       <c r="C4" t="n">
-        <v>1973</v>
+        <v>226</v>
       </c>
       <c r="D4" t="n">
-        <v>1280</v>
+        <v>4412</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5488,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>542</v>
+        <v>183</v>
       </c>
       <c r="C5" t="n">
-        <v>1499</v>
+        <v>169</v>
       </c>
       <c r="D5" t="n">
-        <v>675</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5502,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>414</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>1367</v>
+        <v>111</v>
       </c>
       <c r="D6" t="n">
-        <v>563</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5516,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>45</v>
       </c>
       <c r="C7" t="n">
-        <v>997</v>
+        <v>70</v>
       </c>
       <c r="D7" t="n">
-        <v>418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5530,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>258</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>921</v>
+        <v>48</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5544,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>814</v>
+        <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5558,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>709</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5572,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>520</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5586,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>463</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5600,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>417</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5614,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5628,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5642,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5656,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5670,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5372,10 +5684,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -5386,10 +5698,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5400,7 +5712,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -5445,13 +5757,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>136040</v>
+        <v>1803</v>
       </c>
       <c r="C2" t="n">
-        <v>577705</v>
+        <v>425</v>
       </c>
       <c r="D2" t="n">
-        <v>454564</v>
+        <v>26173</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5771,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>200</v>
+        <v>1037</v>
       </c>
       <c r="C3" t="n">
-        <v>358</v>
+        <v>281</v>
       </c>
       <c r="D3" t="n">
-        <v>971</v>
+        <v>23519</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5785,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>489</v>
+        <v>601</v>
       </c>
       <c r="C4" t="n">
-        <v>1904</v>
+        <v>223</v>
       </c>
       <c r="D4" t="n">
-        <v>1208</v>
+        <v>5194</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5799,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>500</v>
+        <v>321</v>
       </c>
       <c r="C5" t="n">
-        <v>1459</v>
+        <v>174</v>
       </c>
       <c r="D5" t="n">
-        <v>656</v>
+        <v>513</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5813,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>382</v>
+        <v>115</v>
       </c>
       <c r="C6" t="n">
-        <v>1330</v>
+        <v>119</v>
       </c>
       <c r="D6" t="n">
-        <v>546</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5827,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>39</v>
       </c>
       <c r="C7" t="n">
-        <v>987</v>
+        <v>75</v>
       </c>
       <c r="D7" t="n">
-        <v>417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5841,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>227</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>905</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5855,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>797</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5869,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>675</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5883,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>504</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5897,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>453</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5911,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5925,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5939,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5953,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5967,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5981,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5683,10 +5995,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -5700,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5711,7 +6023,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -5756,13 +6068,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>138653</v>
+        <v>2076</v>
       </c>
       <c r="C2" t="n">
-        <v>564430</v>
+        <v>357</v>
       </c>
       <c r="D2" t="n">
-        <v>433720</v>
+        <v>22547</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +6082,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>199</v>
+        <v>1224</v>
       </c>
       <c r="C3" t="n">
-        <v>409</v>
+        <v>282</v>
       </c>
       <c r="D3" t="n">
-        <v>989</v>
+        <v>22496</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +6096,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>439</v>
+        <v>748</v>
       </c>
       <c r="C4" t="n">
-        <v>1838</v>
+        <v>224</v>
       </c>
       <c r="D4" t="n">
-        <v>1143</v>
+        <v>5915</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +6110,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="C5" t="n">
-        <v>1420</v>
+        <v>177</v>
       </c>
       <c r="D5" t="n">
-        <v>637</v>
+        <v>672</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +6124,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>351</v>
+        <v>216</v>
       </c>
       <c r="C6" t="n">
-        <v>1295</v>
+        <v>125</v>
       </c>
       <c r="D6" t="n">
-        <v>532</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +6138,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>274</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>976</v>
+        <v>81</v>
       </c>
       <c r="D7" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +6152,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>199</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>889</v>
+        <v>53</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +6166,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>777</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +6180,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>644</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +6194,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>489</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +6208,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>444</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +6222,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +6236,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +6250,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +6264,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +6278,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +6292,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -5994,10 +6306,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6011,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -6022,7 +6334,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -6067,13 +6379,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>130528</v>
+        <v>2428</v>
       </c>
       <c r="C2" t="n">
-        <v>785521</v>
+        <v>476</v>
       </c>
       <c r="D2" t="n">
-        <v>494870</v>
+        <v>23226</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6393,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>194</v>
+        <v>1401</v>
       </c>
       <c r="C3" t="n">
-        <v>455</v>
+        <v>273</v>
       </c>
       <c r="D3" t="n">
-        <v>1000</v>
+        <v>21453</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6407,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>395</v>
+        <v>885</v>
       </c>
       <c r="C4" t="n">
-        <v>1775</v>
+        <v>227</v>
       </c>
       <c r="D4" t="n">
-        <v>1084</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6421,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>425</v>
+        <v>539</v>
       </c>
       <c r="C5" t="n">
-        <v>1382</v>
+        <v>179</v>
       </c>
       <c r="D5" t="n">
-        <v>619</v>
+        <v>846</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6435,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>1263</v>
+        <v>130</v>
       </c>
       <c r="D6" t="n">
-        <v>520</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6449,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>245</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>965</v>
+        <v>87</v>
       </c>
       <c r="D7" t="n">
-        <v>408</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6463,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>873</v>
+        <v>56</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6477,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>755</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6491,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>616</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6505,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>475</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6519,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6533,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6547,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6561,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6575,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -6277,10 +6589,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -6291,10 +6603,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -6308,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6322,7 +6634,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -6333,7 +6645,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -6378,13 +6690,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>108081</v>
+        <v>2757</v>
       </c>
       <c r="C2" t="n">
-        <v>728815</v>
+        <v>377</v>
       </c>
       <c r="D2" t="n">
-        <v>549203</v>
+        <v>23789</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6704,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>187</v>
+        <v>1605</v>
       </c>
       <c r="C3" t="n">
-        <v>496</v>
+        <v>282</v>
       </c>
       <c r="D3" t="n">
-        <v>1005</v>
+        <v>20514</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6718,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>357</v>
+        <v>1010</v>
       </c>
       <c r="C4" t="n">
-        <v>1715</v>
+        <v>227</v>
       </c>
       <c r="D4" t="n">
-        <v>1030</v>
+        <v>6643</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6732,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>392</v>
+        <v>643</v>
       </c>
       <c r="C5" t="n">
-        <v>1346</v>
+        <v>179</v>
       </c>
       <c r="D5" t="n">
-        <v>602</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6746,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>294</v>
+        <v>395</v>
       </c>
       <c r="C6" t="n">
-        <v>1233</v>
+        <v>135</v>
       </c>
       <c r="D6" t="n">
-        <v>509</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6760,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C7" t="n">
-        <v>953</v>
+        <v>91</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6774,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>856</v>
+        <v>59</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6788,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>732</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6802,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>590</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6816,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>463</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6830,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6844,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6858,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6872,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6886,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -6588,10 +6900,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -6605,7 +6917,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -6619,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6633,7 +6945,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -6644,7 +6956,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
